--- a/noticias/piura/excel/noticias_piura_20260914_20260921.xlsx
+++ b/noticias/piura/excel/noticias_piura_20260914_20260921.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -495,10 +495,70 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Senamhi prevé lluvias desde septiembre en el norte y anticipa un escenario para el verano 2027</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó sobre la posibilidad de lluvias en la costa norte durante los próximos días, principalmente en Tumbes y Piura, en el marco del inicio de la primavera de 2026. Yuri Escajadillo, subdirector de Predicción Climática del Senamhi, explicó que se esperan precipitaciones ligeras alrededor del 22 y 23 de septiembre, un periodo en el que normalmente no se presentan lluvias en la costa norte. Según explicó el especialista, Tumbes y parte de Piura podrían registrar lluvias ligeras desde el 22 y 23 de septiembre. “Este es un inicio, podemos mencionarlo como adelanto de lluvias, porque en esta temporada no hay lluvias en la costa norte, pero las vamos a tener”, mencionó. El subdirector de Predicción Climática del Senamhi precisó que se trata de un escenario inicial y que las condiciones deberán continuar siendo monitoreadas durante las próximas semanas. El panorama podría cambiar conforme avance la primavera. Escajadillo señaló que hacia noviembre y diciembre podrían presentarse lluvias moderadas e incluso de fuerte intensidad en algunas zonas del norte. “Pero hacia noviembre y diciembre ya pudiésemos tener lluvias moderadas, incluso de fuerte intensidad, ¿no? Eso hay que seguir monitoreando, pero depende mucho de cómo las condiciones atmosféricas también se den”, remarcó. El especialista remarcó que la intensidad de las precipitaciones dependerá de la evolución de las condiciones atmosféricas, por lo que el escenario continuará siendo evaluado por el Senamhi. De acuerdo con la explicación de Yuri Escajadillo, el escenario previsto para el verano 2027 contempla una mayor probabilidad de precipitaciones por encima de los valores habituales en sectores de la costa norte. Entre las regiones mencionadas se encuentran Tumbes, Piura, Lambayeque y La Libertad, además de otros sectores de la costa peruana. “Toda la coloración verde más oscura es aquellas regiones donde es más probable que se superen las lluvias que normalmente esperamos en verano”, sostuvo. El periodo de verano comprende aproximadamente desde finales de diciembre hasta marzo. Sin embargo, el especialista aclaró que se trata de un escenario que deberá ser monitoreado conforme evolucionen las condiciones meteorológicas. Durante sus declaraciones, el subdirector de Predicción Climática del Senamhi señaló que el patrón previsto está relacionado con un calentamiento generalizado del Pacífico ecuatorial, asociado a condiciones de El Niño. En contraste, el escenario para algunas zonas de la sierra sur sería diferente. Puno, las zonas altas de Cusco, Apurímac y Ayacucho aparecen entre los sectores donde se contempla una mayor probabilidad de lluvias por debajo de sus valores habituales durante el periodo analizado.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/lima/senamhi-preve-lluvias-desde-septiembre-en-el-norte-y-anticipa-un-escenario-para-el-verano-2027-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lluvias ligeras en Tumbes y Piura pronostica el Senamhi entre el 22 y 25 de septiembre</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Especialistas del Senamhi explican que este escenario estará asociado al incremento de la humedad en la zona costera norte y al aumento de la temperatura superficial del mar (TSM) debido a El Niño Costero 2026-2027.
+Estas condiciones favorecerán una mayor cobertura nubosa y el desarrollo de precipitaciones, principalmente durante las noches y madrugadas.
+Este episodio podría marcar el inicio de un periodo de mayor frecuencia de lluvias en la costa norte, cuya evolución dependerá de la variabilidad de las condiciones atmosféricas y oceánicas durante los próximos días.
+Lea también: ¿En qué se diferencian El Niño Costero y El Niño global?, ¿Cómo afectan al Perú? ¿Dónde se esperan los mayores acumulados de lluvia? De acuerdo con las condiciones previstas, los mayores acumulados de precipitación se registrarían en sectores de la sierra de Piura, principalmente en la provincia de Ayabaca, con valores de hasta 10milímetros (mm).
+En la costa de Piura, específicamente en la provincia de Sullana, se estiman acumulados de hasta 5 mm, mientras que en Tumbes, en las provincias de Tumbes y Zarumilla se prevén valores próximos a 10 mm.
+A partir del 27 de septiembre, se estima un incremento en la intensidad de las lluvias, principalmente en sectores de Piura y Tumbes, con acumulados superiores a los previstos inicialmente .
+Asimismo, la cabecera de la cuenca del río Tumbes presentará lluvias que podrían superar los 20 mm, lo que propiciaría un ligero incremento del caudal.
+El Senamhi recomienda mantenerse informado a través de la página web y las redes sociales oficiales de la institución.
+Más en Andina: Senamhi prevé radiación UV "extremadamente alta" en verano por fenómeno El Niño.
+Especialista pide no exponerse más de 10 minutos al sol cuando se presenten estas condiciones.
+?? https://t.co/0WLc6uDoiY pic.twitter.com/ttmu40Y6gb — Agencia Andina (@Agencia_Andina) September 20, 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-lluvias-ligeras-tumbes-y-piura-pronostica-senamhi-entre-22-y-25-septiembre-1092585.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Fenómeno El Niño: Inabif entrega kits de emergencia a menores vulnerables de Piura</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Gracias al compromiso de la empresa aliada “Solidez Empresarial”, se concretó la entrega de mochilas, botas, kits de higiene personal y otros implementos destinados a fortalecer la preparación de los menores ante posibles situaciones de emergencia.
 Asimismo, los participantes recibieron obsequios que acompañaron las dinámicas recreativas y lúdicas desarrolladas durante la jornada.
@@ -517,27 +577,85 @@
 Más en Andina:</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-fenomeno-nino-inabif-entrega-kits-emergencia-a-menores-vulnerables-piura-1092606.aspx</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>46286</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Moquegua: transfieren tecnologías a productores de olivo para afrontar efectos de El Niño</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>La entidad adscrita al Ministerio de Desarrollo Agrario y Riego (Midagri) busca con ello que los agricultores reduzcan aproximadamente en un 50 % el impacto que puedan generar las altas temperaturas derivadas del mencionado evento climatológico en las plantas del cultivo.
+Otro objetivo es que los productores de olivo de la Comisión de Usuario de Moquegua conserven la calidad nutritiva del suelo e incrementar en un más de un 40 % los niveles de cosecha.
+[Lea también: 100,000 devotos asistirán a misa que se celebrará en Santa Cruz ] Las tecnologías transferidas fueron desarrolladas en la Estación Experimental Agraria Moquegua.
+Estas tienen que ver con el uso de microorganismos benéficos, selección de materia orgánica de campo, producción de plantones élite de olivo, monitoreo y control de plagas, así como el análisis de la fertilidad del suelo y elaboración de abono orgánico.
+Asimismo, el INIA en Moquegua trabaja en la conservación del cultivo del olivo mediante capacitaciones técnicas y transferencia de tecnología orientadas a los productores olivícolas, entre las que figura el análisis de la calidad del suelo, el manejo integrado de plagas y enfermedades que afectan a los olivos, así como técnicas de uso eficiente de agroquímicos.
+Jornada de capacitación La transferencia de estas tecnologías se realizó durante una jornada de capacitación donde también tomaron parte especialistas del Senasa, Agro Rural y la Autoridad Local del Agua de Moquegua.
+Durante la jornada se abordaron temas relacionados con el manejo integrado de plagas, el uso de abonos orgánicos y la identificación de puntos críticos ante los posibles efectos del Fenómeno El Niño.
+[Lea también: Inabif entrega kits de emergencia a menores vulnerables de Piura ] Estas acciones forman parte de la estrategia que impulsa el Gobierno, a través del Midagri, para hacer frente al referido evento climatológico.
+En ese contexto, se promueve la construcción de cochas, reservorios y zanjas de infiltración, descolmatación de ríos, la transferencia de paquetes tecnológicos de producción de forraje hidropónico y pellets que aseguren la alimentación del ganado, así como el uso de semillas de papa, quinua y avena de alta calidad que toleren el estrés hídrico.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-moquegua-transfieren-tecnologias-a-productores-olivo-para-afrontar-efectos-de-nino-1092614.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hasta 2 mil soles vale una vida para un sicario</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hasta S/2 mil pueden llegar a pagar las organizaciones criminales por un asesinato, según advirtió el coronel PNP en retiro Máximo Vargas Hugo , exjefe de la Región Policial Piura, al analizar el avance de la violencia criminal en la región. Puedes Leer | Piura supera los 10 mil casos de dengue y refuerzan llamado a completar vacunación El oficial en retiro sostuvo que los sicarios constituyen el “brazo armado” de las organizaciones delictivas y que son contratados para ejecutar asesinatos. Según su declaración, los montos pueden oscilar entre S/500 y S/2 mil, dependiendo del encargo criminal. Vargas Hugo también alertó sobre el poder de estas organizaciones. Afirmó que utilizan armamento moderno y que parte de este llegaría desde Ecuador, debido al poder económico generado por actividades ilícitas como la extorsión, minería ilegal y trata de personas. Por ello, consideró necesario reforzar los controles en la zona fronteriza. El exjefe policial señaló además que ocho de cada diez homicidios en Piura se cometen con armas de fuego y que en algunos ataques las víctimas reciben múltiples disparos, pues a veces se contabilizan hasta más de 40 casquillos de bala en el lugar del crimen. Esta tendencia coincide con los 109 homicidios que se han registrado en lo que va del año en la región Piura, de los cuales 84 fueron ocasionados por proyectiles de arma de fuego. Armas modernas Asimismo, cuestionó que las bandas puedan disponer de tecnología y armas modernas, mientras que, según su apreciación, parte del equipamiento policial es antiguo. También mencionó el uso de drones por organizaciones criminales en otros puntos del país como muestra de la incorporación de nuevas tecnologías al delito. La problemática se suma a la presencia de estructuras dedicadas a extorsiones, sicariato y otros delitos. Fortalecer Inteligencia Policial La Policía ha señalado que una parte importante de los homicidios está relacionada con disputas entre organizaciones criminales por control territorial y cobro de cupos. Ante este escenario, el exjefe policial planteó fortalecer las labores de inteligencia e investigación criminal y reforzar la vigilancia en la frontera para impedir el ingreso ilegal de armas.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/hasta-2-mil-soles-vale-una-vida-para-un-sicario/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Autoridad Nacional del Agua destrabó 78 proyectos por casi US$ 1,200 millones [Entrevista]</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Para conocer más sobre este tema el Suplemento Económika del Diario El Peruano entrevistó al presidente ejecutivo de la institución, Juan Carlos Castro.
 Estamos atravesando por una coyuntura complicada, especialmente marcada por la presencia del fenómeno El Niño.
@@ -616,126 +734,16 @@
 ?? https://t.co/BZ6z7LcOeK pic.twitter.com/RITSfJ3fBO — Agencia Andina (@Agencia_Andina) September 20, 2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-autoridad-nacional-del-agua-destrabo-78-proyectos-casi-1200-millones-entrevista-1092569.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hasta 2 mil soles vale una vida para un sicario</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hasta S/2 mil pueden llegar a pagar las organizaciones criminales por un asesinato, según advirtió el coronel PNP en retiro Máximo Vargas Hugo , exjefe de la Región Policial Piura, al analizar el avance de la violencia criminal en la región. Puedes Leer | Piura supera los 10 mil casos de dengue y refuerzan llamado a completar vacunación El oficial en retiro sostuvo que los sicarios constituyen el “brazo armado” de las organizaciones delictivas y que son contratados para ejecutar asesinatos. Según su declaración, los montos pueden oscilar entre S/500 y S/2 mil, dependiendo del encargo criminal. Vargas Hugo también alertó sobre el poder de estas organizaciones. Afirmó que utilizan armamento moderno y que parte de este llegaría desde Ecuador, debido al poder económico generado por actividades ilícitas como la extorsión, minería ilegal y trata de personas. Por ello, consideró necesario reforzar los controles en la zona fronteriza. El exjefe policial señaló además que ocho de cada diez homicidios en Piura se cometen con armas de fuego y que en algunos ataques las víctimas reciben múltiples disparos, pues a veces se contabilizan hasta más de 40 casquillos de bala en el lugar del crimen. Esta tendencia coincide con los 109 homicidios que se han registrado en lo que va del año en la región Piura, de los cuales 84 fueron ocasionados por proyectiles de arma de fuego. Armas modernas Asimismo, cuestionó que las bandas puedan disponer de tecnología y armas modernas, mientras que, según su apreciación, parte del equipamiento policial es antiguo. También mencionó el uso de drones por organizaciones criminales en otros puntos del país como muestra de la incorporación de nuevas tecnologías al delito. La problemática se suma a la presencia de estructuras dedicadas a extorsiones, sicariato y otros delitos. Fortalecer Inteligencia Policial La Policía ha señalado que una parte importante de los homicidios está relacionada con disputas entre organizaciones criminales por control territorial y cobro de cupos. Ante este escenario, el exjefe policial planteó fortalecer las labores de inteligencia e investigación criminal y reforzar la vigilancia en la frontera para impedir el ingreso ilegal de armas.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/hasta-2-mil-soles-vale-una-vida-para-un-sicario/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lluvias ligeras en Tumbes y Piura pronostica el Senamhi entre el 22 y 25 de septiembre</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Especialistas del Senamhi explican que este escenario estará asociado al incremento de la humedad en la zona costera norte y al aumento de la temperatura superficial del mar (TSM) debido a El Niño Costero 2026-2027.
-Estas condiciones favorecerán una mayor cobertura nubosa y el desarrollo de precipitaciones, principalmente durante las noches y madrugadas.
-Este episodio podría marcar el inicio de un periodo de mayor frecuencia de lluvias en la costa norte, cuya evolución dependerá de la variabilidad de las condiciones atmosféricas y oceánicas durante los próximos días.
-Lea también: ¿En qué se diferencian El Niño Costero y El Niño global?, ¿Cómo afectan al Perú? ¿Dónde se esperan los mayores acumulados de lluvia? De acuerdo con las condiciones previstas, los mayores acumulados de precipitación se registrarían en sectores de la sierra de Piura, principalmente en la provincia de Ayabaca, con valores de hasta 10milímetros (mm).
-En la costa de Piura, específicamente en la provincia de Sullana, se estiman acumulados de hasta 5 mm, mientras que en Tumbes, en las provincias de Tumbes y Zarumilla se prevén valores próximos a 10 mm.
-A partir del 27 de septiembre, se estima un incremento en la intensidad de las lluvias, principalmente en sectores de Piura y Tumbes, con acumulados superiores a los previstos inicialmente .
-Asimismo, la cabecera de la cuenca del río Tumbes presentará lluvias que podrían superar los 20 mm, lo que propiciaría un ligero incremento del caudal.
-El Senamhi recomienda mantenerse informado a través de la página web y las redes sociales oficiales de la institución.
-Más en Andina: Senamhi prevé radiación UV "extremadamente alta" en verano por fenómeno El Niño.
-Especialista pide no exponerse más de 10 minutos al sol cuando se presenten estas condiciones.
-?? https://t.co/0WLc6uDoiY pic.twitter.com/ttmu40Y6gb — Agencia Andina (@Agencia_Andina) September 20, 2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-lluvias-ligeras-tumbes-y-piura-pronostica-senamhi-entre-22-y-25-septiembre-1092585.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sechura: Ganaderos se organizan frente a la ola de abigeato</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Un clima de creciente preocupación, enfrentan los ganaderos del desierto de Sechura tras una serie de robos de ganado vacuno, ovino y caprino registrados bajo una misma modalidad en diversos sectores de la zona. PUEDES LEER ► Dos crímenes en un día: violencia en el Bajo Piura y Talara Alta Como medida de prevención, los propios afectados se han organizado con sus propios vehículos para realizar patrullajes en distintos sectores. Asimismo, solicitaron a las autoridades y a los vecinos comunicar de inmediato cualquier presencia o movimiento sospechoso que pueda estar relacionado con el robo de ganado. Según declaró el comunero José Miguel Chunga Pasache, presidente de la Asociación José Cayetano de Illescas , los delincuentes trasladan el ganado desde el sector de Huaquilla, pasando por Zapayal, hasta llegar frente a Belisario. En este tramo, de aproximadamente un kilómetro , una loma ubicada cerca de la carretera facilitaría que los delincuentes carguen continuamente los animales en motos furgones para luego trasladarlos y ocultarlos en un refugio ubicado en el caserío Mala Vida. Hace unos días, los propietarios encontraron en dicho lugar huellas y rastros que correspondían a sus animales. Sin embargo, las vacas ya habían sido comercializadas durante la noche. Pese a que el ganado no pudo ser recuperado, las acciones emprendidas por los afectados permitieron la captura de dos sospechosos, quienes habrían admitido su participación y asegurado que pagarían el valor económico de las reses vendidas. Ante la falta de seguridad en el campo, donde el ganado permanece suelto, José Miguel Chunga Pasache hizo un llamado urgente a las autoridades.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/sechura-ganaderos-se-organizan-frente-a-la-ola-de-abigeato/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>¡Que Dios nos ayude!</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Cauce del río Piura avanza a un ritmo demasiado lento y la intervención del canal Chutuque no se haría en el lugar correcto para facilitar una salida más rápida hacia las lagunas cercanas al mar. PUEDES LEER ► Asesinan a una candidata al Gobierno Regional Bajo este panorama, el futuro de la ciudad y del Bajo Piura queda otra vez a merced de la naturaleza y de que el río Piura no traiga un caudal extraordinario por encima de los 3.000 metros sobre el nivel del mar. Sobre la descolmatación, en la actualidad se interviene en dos puntos específicos. El primero es el tramo entre la presa Los Ejidos y aguas abajo del puente Bolognesi. La maquinaria de la Autoridad Nacional del Agua (ANA) extrae material del centro del cauce y acumula el sedimento a la espera de volquetes para llevarse la arena. El otro sector es entre el puente Grau y el puente Independencia. Aquí los trabajos están a cargo del Ministerio de Defensa. En ambos casos, la maquinaria remueve la arena y la acumula en el mismo cauce por falta de más volquetes para retirarla. Van lento Al respecto, el decano del Colegio de Ingenieros, Manuel Asmat Córdova, consideró que con el actual ritmo de trabajo no se cumplirá la meta de retirar todo el material del cauce para darle mayor capacidad al río. “La cantidad de volumen de material que hay que remover es ingente. Es muchísimo material y dada la poca disponibilidad de maquinaria que se tiene, consideramos que no va a alcanzar para remover la cantidad de material necesaria para tener por lo menos un caudal de 3.000 m3/seg y pueda resistir el cauce del río”, sostuvo Asmat Córdova. La situación se agrava si se toma en cuenta, añade el decano, que los expertos mencionan que se esperarían caudales superiores a este nivel. “La situación es crítica y no se ve realmente un avance importante. Como siempre he dicho, lo único que podemos hacer ahorita es la descolmatación y ésta no está avanzando a un ritmo adecuado. Las metas que se han planteado no nos protegerían de una avenida extraordinaria, porque se anuncia que podrían venir avenidas de 3500 a 4000 metros cúbicos por segundo y ante eso no estaríamos preparados”, indicó Asmat. ¿Quién responde? Frente a lo que podría suceder, el representante de los ingenieros resaltó que será momento para establecer responsabilidades por lo que no se hizo después de la inundación del año 2017. “Ya no hay tiempo para hacer otra cosa [que descolmatación]. Lamentablemente, tenemos que decirlo [...] en su momento tendrán que verse responsabilidades. Se tuvo una ARCC (Autoridad para la Reconstrucción con Cambios) y ahora una ANIN (Autoridad Nacional de Infraestructura) que prácticamente en 9 años no avanzaron casi nada. Ahora se podría tener una represa, infraestructura natural (reforestación en parte alta) o una posible salida al mar; pero no tenemos absolutamente nada del proyecto definitivo. Esa es realmente la causa por la cual estamos en esta situación”, finalizó Asmat. No es nada De otro lado, el ingeniero y especialista en hidráulica, César Alvarado Ancieta, cuestionó los trabajos de descolmatación porque se trataría de una cantidad ínfima que no se compara a lo que existe en el cauce y que se fue acumulando durante años. “El medio millón de metros cúbicos de sedimento es una meta ridícula. En el cauce existen 65 millones de metros cúbicos, que es 120 veces más de lo que se quiere sacar”, declaró el especialista. Alvarado toma como referencia la meta de 500 mil metros cúbicos que se pretende retirar en el tramo desde la presa Los Ejidos y el puente Bolognesi. Agrega que la Autoridad Nacional del Agua (ANA) ha hecho un mal cálculo para establecer que luego de la descolmatación, el río podría resistir caudales de 3.000 m3/seg. Fuente: El Tiempo Semanario</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/que-dios-nos-ayude/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -743,24 +751,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Piura supera los 10 mil casos de dengue y refuerzan llamado a completar vacunación</t>
+          <t>Inician acciones de conservación para proteger los petroglifos de Samanga, en Ayabaca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Piura registra 10,009 casos de dengue y seis fallecidos en lo que va de 2026 , según la actualización de las autoridades sanitarias. A nivel nacional, el acumulado alcanza los 52,395 casos y 63 muertes. El epidemiólogo del Ministerio de Salud, Ciro Adolfo García Vilela, advirtió que la transmisión del dengue continúa durante el segundo semestre del año y presenta un comportamiento distinto al observado en temporadas anteriores, cuando los contagios se concentraban principalmente durante los primeros meses. El especialista explicó que las temperaturas elevadas favorecen el desarrollo del Aedes aegypti , mosquito transmisor del dengue. Bajo estas condiciones, el ciclo de reproducción del vector puede acortarse de unos siete días a entre cuatro y cinco, lo que permite que aumente rápidamente su población. PUEDES LEER ► Desaparecen más de 100 mil mypes de comercio Eliminación de criaderos es clave para frenar el dengue García señaló que el tratamiento de las personas enfermas permite atender las consecuencias de la infección, pero que la prevención debe centrarse también en reducir la presencia del mosquito. Por ello, recomendó evitar la acumulación de agua en recipientes y mantener correctamente cerrados los depósitos utilizados para almacenar este recurso. También pidió retirar objetos que puedan convertirse en criaderos del mosquito. Piura mantiene baja cobertura de vacunación Ante el incremento de casos, el Ministerio de Salud mantiene la vacunación contra el dengue dirigida a niños, adolescentes y jóvenes de 10 a 20 años de las zonas priorizadas. El esquema contempla dos dosis, administradas con un intervalo de tres meses . El objetivo de esta estrategia es disminuir el riesgo de hospitalización y complicaciones asociadas a la enfermedad. Sin embargo, la cobertura en Piura continúa siendo baja. Un reporte con información actualizada al 3 de septiembre señaló que apenas 6.9 % de la población objetivo había recibido la primera dosis , mientras que solo el 1.9 % había completado la segunda . Minsa reporta disponibilidad de vacunas En agosto, el Ministerio de Salud informó que recibió 444,780 dosis destinadas a fortalecer la vacunación en las regiones priorizadas, entre ellas Piura. En ese mismo periodo, el sector salud indicó que la región contaba con más de 140 mil dosis disponibles , las cuales son aplicadas en establecimientos de salud y mediante campañas desarrolladas en instituciones educativas. Las autoridades sanitarias exhortan a las familias de los distritos incluidos en la estrategia a consultar en los establecimientos de salud sobre los criterios de vacunación y autorizar la inmunización de los menores que formen parte de la población objetivo. Quienes ya recibieron la primera dosis deben acudir cuando corresponda para completar el esquema establecido. La vacunación, además, debe acompañarse de medidas para eliminar los criaderos del Aedes aegypti , como tapar los depósitos de agua, retirar recipientes que acumulen agua y facilitar el trabajo de las brigadas de control vectorial.</t>
+          <t>Hasta este rincón fronterizo, ubicada a más de 2,300 metros sobre el nivel del mar, llegó una expedición científica integrada por el Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) y la Dirección Desconcentrada de Cultura (DDC) de Piura, decidida a frenar el deterioro de este tesoro asociado a la cultura Ayahuanca, con entre 4,000 y 3,000 años de antigüedad.
+La misión, nacida en el marco del convenio institucional, respaldado por la rectora de la UPAO, Yolanda Peralta Chávez, y el titular de la DDC Piura, Juval Córdova Palacios, puso en marcha el proyecto “Recuperación y difusión visual de los petroglifos de Samanga mediante fotografía digital”.
+El objetivo en campo fue claro: registrar, geolocalizar e intervenir sin violencia las rocas para devolverles la visibilidad que los siglos les han ido arrebatando.
+Símbolos del Formativo bajo la lupa Las evaluaciones preliminares de los arqueólogos sitúan a estos grabados en el Periodo Formativo o Horizonte Temprano.
+Aplicando una técnica de abrasión profunda, los antiguos habitantes de la zona trazaron sobre la piedra figuras antropomorfas, serpientes sinuosas, formas geométricas, espirales y claras representaciones del cactus San Pedro, asociado a antiguos ritos de sanación y tránsito espiritual.
+Los investigadores hallaron también pocitos, cavidades semiesféricas talladas en la cima de los bloques que habrían servido para depositar ofrendas o colectar agua ritual.
+Sin embargo, el diagnóstico de conservación encendió las alarmas.
+La exfoliación microespacial de la roca, la colonización de pátinas de líquenes y la constante erosión hídrica amenazan con borrar los trazos de los bloques más emblemáticos, como la Piedra de Los Angelitos, la Piedra del Rey y la Piedra del Sol.
+Ante este escenario, el conservador Alex Clavo Cruz y los arqueólogos André Vidal, Lilian Villacorta, Irwin Bocanegra y Evelyn Mendoza aplicaron protocolos inmediatos de limpieza no invasiva, empleando únicamente agua simple y cepillado blando para retirar la materia orgánica sin alterar el grabado original.
+Tecnología y comunidad para devolver la memoria El trabajo de campo combinó la arqueología tradicional con el lenguaje audiovisual.
+El fotógrafo Erick Aquino Montoro y el docente Rolando Sosa Alzamora volaron drones sobre el complejo para generar fotogrametría de alta precisión y un levantamiento georeferencial completo.
+Esta información permitirá procesar los datos en el Sistema de Información Geográfica en Arqueología (SIGDA), paso técnico indispensable para iniciar el expediente de declaratoria formal como patrimonio cultural de la Nación.
+El proyecto no busca quedarse en el gabinete.
+La estrategia incluye talleres de sensibilización con los comuneros de El Toldo para convertir la conservación en una herramienta de turismo sostenible gestionada por los propios pobladores.
+Como cierre de esta ruta de rescate, la UPAO y la DDC Piura organizarán a finales de año una exposición fotográfica y museográfica orientada a acercar la riqueza de Samanga a toda la ciudadanía.
+Más en Andina:</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-supera-los-10-mil-casos-de-dengue-y-refuerzan-llamado-a-completar-vacunacion/</t>
+          <t>https://andina.pe/agencia/noticia-inician-acciones-conservacion-para-proteger-los-petroglifos-samanga-ayabaca-1092361.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -768,10 +791,85 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>¡Que Dios nos ayude!</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cauce del río Piura avanza a un ritmo demasiado lento y la intervención del canal Chutuque no se haría en el lugar correcto para facilitar una salida más rápida hacia las lagunas cercanas al mar. PUEDES LEER ► Asesinan a una candidata al Gobierno Regional Bajo este panorama, el futuro de la ciudad y del Bajo Piura queda otra vez a merced de la naturaleza y de que el río Piura no traiga un caudal extraordinario por encima de los 3.000 metros sobre el nivel del mar. Sobre la descolmatación, en la actualidad se interviene en dos puntos específicos. El primero es el tramo entre la presa Los Ejidos y aguas abajo del puente Bolognesi. La maquinaria de la Autoridad Nacional del Agua (ANA) extrae material del centro del cauce y acumula el sedimento a la espera de volquetes para llevarse la arena. El otro sector es entre el puente Grau y el puente Independencia. Aquí los trabajos están a cargo del Ministerio de Defensa. En ambos casos, la maquinaria remueve la arena y la acumula en el mismo cauce por falta de más volquetes para retirarla. Van lento Al respecto, el decano del Colegio de Ingenieros, Manuel Asmat Córdova, consideró que con el actual ritmo de trabajo no se cumplirá la meta de retirar todo el material del cauce para darle mayor capacidad al río. “La cantidad de volumen de material que hay que remover es ingente. Es muchísimo material y dada la poca disponibilidad de maquinaria que se tiene, consideramos que no va a alcanzar para remover la cantidad de material necesaria para tener por lo menos un caudal de 3.000 m3/seg y pueda resistir el cauce del río”, sostuvo Asmat Córdova. La situación se agrava si se toma en cuenta, añade el decano, que los expertos mencionan que se esperarían caudales superiores a este nivel. “La situación es crítica y no se ve realmente un avance importante. Como siempre he dicho, lo único que podemos hacer ahorita es la descolmatación y ésta no está avanzando a un ritmo adecuado. Las metas que se han planteado no nos protegerían de una avenida extraordinaria, porque se anuncia que podrían venir avenidas de 3500 a 4000 metros cúbicos por segundo y ante eso no estaríamos preparados”, indicó Asmat. ¿Quién responde? Frente a lo que podría suceder, el representante de los ingenieros resaltó que será momento para establecer responsabilidades por lo que no se hizo después de la inundación del año 2017. “Ya no hay tiempo para hacer otra cosa [que descolmatación]. Lamentablemente, tenemos que decirlo [...] en su momento tendrán que verse responsabilidades. Se tuvo una ARCC (Autoridad para la Reconstrucción con Cambios) y ahora una ANIN (Autoridad Nacional de Infraestructura) que prácticamente en 9 años no avanzaron casi nada. Ahora se podría tener una represa, infraestructura natural (reforestación en parte alta) o una posible salida al mar; pero no tenemos absolutamente nada del proyecto definitivo. Esa es realmente la causa por la cual estamos en esta situación”, finalizó Asmat. No es nada De otro lado, el ingeniero y especialista en hidráulica, César Alvarado Ancieta, cuestionó los trabajos de descolmatación porque se trataría de una cantidad ínfima que no se compara a lo que existe en el cauce y que se fue acumulando durante años. “El medio millón de metros cúbicos de sedimento es una meta ridícula. En el cauce existen 65 millones de metros cúbicos, que es 120 veces más de lo que se quiere sacar”, declaró el especialista. Alvarado toma como referencia la meta de 500 mil metros cúbicos que se pretende retirar en el tramo desde la presa Los Ejidos y el puente Bolognesi. Agrega que la Autoridad Nacional del Agua (ANA) ha hecho un mal cálculo para establecer que luego de la descolmatación, el río podría resistir caudales de 3.000 m3/seg. Fuente: El Tiempo Semanario</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/que-dios-nos-ayude/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gestión</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>El Niño acorta crecimiento de Perú para 2026 y 2027: ¿qué espera ahora Piura?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>El impacto del fenómeno de El Niño (FEN) en la economía peruana ya se siente y una región que vive de cerca esta amenaza es Piura. La región, que ya es “experta” en enfrentar esta clase de fenómenos climáticos, conoce muy bien el peligro: reducción de productividad en sectores clave, caída del empleo y peores servicios brindados a su población. ¿Cuánto golpeará el FEN su producción en este y el próximo año? Para responder a esa pregunta, primero hay que tener el panorama completo. Si bien diversos analistas privados han dado sus estimaciones, ya se tienen aproximaciones oficiales. En el más reciente Marco Macroeconómico Multianual (MMM) 2027-2030, el Ministerio de Economía y Finanzas (MEF) ya precisó cuál sería el retroceso en el peor escenario del FEN, que tendrá su mayor efecto en los últimos meses del 2026 y el primer trimestre del 2027. De acuerdo con el ministerio, un FEN extraordinario, como se prevé, reduciría el crecimiento del Perú en 0.7 puntos porcentuales (p.p.) en 2026 y 0.6 p.p. en 2027. Así, el país crecería 2.7% y 2.8% este y el próximo año, respectivamente. Además, el Banco Central de Reserva del Perú acaba de revelar sus nuevas proyecciones para este y el próximo año. Las cifras se ajustaron ligeramente a la baja justamente por los impactos esperados de El Niño sobre la economía. ¿Qué tanto de esas caídas totales se explicará por el impacto en Piura? La interrogante es válida, mas si se recuerda que, tras Lima, la ciudad del norte es la segunda más habitada del Perú, con 2.1 millones de habitantes, de acuerdo al Censo Nacional 2025 del Instituto Nacional de Estadística e Informática (INEI). Al respecto Stephani Maita, economista senior del Instituto Peruano de Economía (IPE), puntualizó que, al cierre del primer trimestre, Piura creció 4.3%, aunque en el segundo trimestre ya se siente una desaceleración. “[Hacia adelante], nuestra perspectiva es que se empeore un poco porque buena parte de los productos principales de Piura se cosechan hacia fin del año. Hablo de las paltas y uvas, que fueron de los más golpeados en 2023″, sostuvo. A ello, Gabriela Espinar, economista de la Red de Estudios para el Desarrollo (Redes), sumó que desde 2015 el crecimiento de Piura ha sido muy frágil e inestable. “En los últimos 10 años ha crecido 2.5% en promedio, menor al promedio nacional. Tiene algunos picos y recesiones muy marcadas. Eso pasó en 2017, con el FEN, donde su economía retrocedió 2.4%”, indicó. En el MMM el MEF es bastante claro: los sectores primarios de la economía son los que sufrirán peores resultados gracias al FEN, sobre todo pesca; y en el área no primaria comercio, junto a servicios y manufactura también serían perjudicados. Precisamente todos esos son los principales motores productivos de Piura. Según el INEI, el rubro “otras actividades”, que incluye a otros servicios, pesca y acuicultura, representó el 23.8% del Valor Agregado Bruto (VAB) de la región en 2025. Le siguen, por encima del 10%, la manufactura, el comercio, y la agricultura. Tanto Maita como Espinar indicaron que, de recrudecer el FEN, el sector agropecuario servirá de referencia para medir las consecuencias económicas para la región. “El FEN genera dos tipos de costos, uno es el daño a la infraestructura, pero el otro es que se cae el empleo. Agricultura es fuerte en mano de obra en Piura. Cuando cae, golpea severamente los ingresos de las personas. Eso ya pasó en 2023 y 2017″, advirtió Espinar. Vinculado a ello, Maita recordó que Piura se ubicó en el puesto 17 entre los 25 departamentos en el Índice de Competitividad Regional (INCORE) 2026, lo que marca la baja calidad de los servicios que tiene. “En su caso hemos visto un deterioro sobre todo en los pilares de infraestructura y salud. En Piura ha crecido la anemia y los hogares no tienen acceso al agua por más de 12 horas. La región tiene un gran potencial, por ejemplo, en hidrocarburos, pero hay obras paralizadas”, lamentó. Piura es “experta” en recibir al FEN. Tanto Maita como Espinar recordaron los resultados que tuvo la región, en términos de PBI, en los años de sus últimas visitas: 2017 y 2023. Estos sirven de referencia para anticipar lo que podría resultar este 2026. En 2017, como ya dijo Espinar, Piura estuvo entre las regiones con mayores retrocesos del Perú, principalmente por la caída de su sector agropecuario, a consecuencia del embate del FEN Costero ese año especialmente el primer trimestre. Ello, vale decir, no evitó que el país crezca 2.5%. En 2023, donde aparte del FEN ocurrió el Ciclón Yaku, Piura creció 1%, mientras que Perú como país cayó en recesión (-0.55%). Esta tasa también tiene matices, puntualizan las economistas. El mundo dejaba atrás al Covid-19 y no todos sus sectores crecieron. ¿Qué escenario podría vivirse ahora? Las expertas consultadas por Gestión apuestan porque sea lo más similar al 2023: que Piura crezca, aunque sea poco. “Hay obras de prevención en desarrollo, con apoyo de la Autoridad Nacional del Agua (ANA). Eso es crucial, pero será importante una estrategia para aminorar impactos indirectos, nuevamente, en empleo, por ejemplo”, consideró Maita. Espinar agregó que hace falta que el Gobierno de Keiko Fujimori plantee otro plan para “recuperar” lo más posible a los rubros que ya han sufrido paras por el FEN. “La descolmatación es importante, pero también las medidas de apoyo a sectores vulnerables. Se deben proteger las hectáreas, pero también al agricultor, ¿saben qué hacer en épocas de crisis? Igual los pescadores, ¿hay espacio o no para continuar las capturas?“, preguntó.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://gestion.pe/economia/el-nino-acorta-crecimiento-de-peru-para-2026-y-2027-que-espera-ahora-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sechura: Ganaderos se organizan frente a la ola de abigeato</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Un clima de creciente preocupación, enfrentan los ganaderos del desierto de Sechura tras una serie de robos de ganado vacuno, ovino y caprino registrados bajo una misma modalidad en diversos sectores de la zona. PUEDES LEER ► Dos crímenes en un día: violencia en el Bajo Piura y Talara Alta Como medida de prevención, los propios afectados se han organizado con sus propios vehículos para realizar patrullajes en distintos sectores. Asimismo, solicitaron a las autoridades y a los vecinos comunicar de inmediato cualquier presencia o movimiento sospechoso que pueda estar relacionado con el robo de ganado. Según declaró el comunero José Miguel Chunga Pasache, presidente de la Asociación José Cayetano de Illescas , los delincuentes trasladan el ganado desde el sector de Huaquilla, pasando por Zapayal, hasta llegar frente a Belisario. En este tramo, de aproximadamente un kilómetro , una loma ubicada cerca de la carretera facilitaría que los delincuentes carguen continuamente los animales en motos furgones para luego trasladarlos y ocultarlos en un refugio ubicado en el caserío Mala Vida. Hace unos días, los propietarios encontraron en dicho lugar huellas y rastros que correspondían a sus animales. Sin embargo, las vacas ya habían sido comercializadas durante la noche. Pese a que el ganado no pudo ser recuperado, las acciones emprendidas por los afectados permitieron la captura de dos sospechosos, quienes habrían admitido su participación y asegurado que pagarían el valor económico de las reses vendidas. Ante la falta de seguridad en el campo, donde el ganado permanece suelto, José Miguel Chunga Pasache hizo un llamado urgente a las autoridades.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sechura-ganaderos-se-organizan-frente-a-la-ola-de-abigeato/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>ERM 2026: Capacitación a miembros de mesa se realizó en 4000 locales educativos</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>El jefe (i) de la Oficina Nacional de Procesos Electorales (ONPE), Bernardo Pachas Serrano , estuvo supervisando en Lima Metropolitana el desarrollo de esta actividad, que es parte de la labor de capacitación que lleva a cabo el organismo electoral, de manera presencial y virtual, desde el 5 de setiembre.
 “Es importante que los miembros de mesa se capaciten y así conozcan los procedimientos y los materiales; en particular, la elaboración del acta de escrutinio, para evitar errores materiales que llevarían a que un acta sea observada” , afirmó Bernardo Pachas Serrano.
@@ -794,84 +892,9 @@
 El jefe (i) de la ONPE supervisó la partida de vehículos cuyos trayectos tomarán 2 o 3 días, transportando material destinado a zonas de Cusco, Ayacucho, Apurímac, La Libertad, Junín, Cajamarca, Tumbes y Piura.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-erm-2026-capacitacion-a-miembros-mesa-se-realizo-4000-locales-educativos-1092566.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ayabaca: Un muerto y tres heridos deja caída de camioneta al abismo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sigue la tragedia en las carreteras de la región. Esta vez, la ruta rural Pacaipampa-Huancabamba-San Ignacio fue escenario de un trágico accidente, que dejó el saldo de un fallecido y tres heridos, uno de ellos un menor de edad. El suceso ocurrió cerca de las cinco de la mañana de ayer, cuando una camioneta de placa Z3R-773, conducida por Walter Huancas Facundo, de 24 años, cubría la mencionada ruta tuvo un percance, luego de despistarse y caer a un abismo. PUEDES LEER ► EsSalud permitirá que pacientes hospitalizados permanezcan acompañados por un familiar las 24 horas DAMAS Y NIÑO SE SALVAN Como consecuencia del aparatoso accidente, el conductor perdió la vida en el lugar. De acuerdo con la información preliminar, el fallecido era natural de Mitupampa, distrito de Sondorillo. Se desconoce las causas que provocaron el lamentable accidente. Asimismo, dos mujeres y un menor de edad resultaron heridos. Las damas presentarían fracturas en distintas partes del cuerpo por lo que fueron trasladadas de emergencia al nosocomio de la zona para su posterior traslado a Piura. RESCATE EN EL ABISMO Personal de salud de Jicate y Huancacarpa acudió para brindar atención y trasladar a los heridos hacia el E.S. I-4 Huancabamba. En la agreste zona también llegaron integrantes del grupo de rescate Virgen del Carmen , quienes participan en las labores para recuperar el vehículo siniestrado. La partida del joven transportista Walter Huancas ha causado consternación entre sus familiares, parientes y amigos, los mismos que señalan que conducía desde hace más de cuatro años por las rutas de la sierra altoandina. Sus restos fueron trasladados al nosocomio para las diligencias de rigor.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/ayabaca-un-muerto-y-tres-heridos-deja-caida-de-camioneta-al-abismo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Gestión</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>El Niño acorta crecimiento de Perú para 2026 y 2027: ¿qué espera ahora Piura?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>El impacto del fenómeno de El Niño (FEN) en la economía peruana ya se siente y una región que vive de cerca esta amenaza es Piura. La región, que ya es “experta” en enfrentar esta clase de fenómenos climáticos, conoce muy bien el peligro: reducción de productividad en sectores clave, caída del empleo y peores servicios brindados a su población. ¿Cuánto golpeará el FEN su producción en este y el próximo año? Para responder a esa pregunta, primero hay que tener el panorama completo. Si bien diversos analistas privados han dado sus estimaciones, ya se tienen aproximaciones oficiales. En el más reciente Marco Macroeconómico Multianual (MMM) 2027-2030, el Ministerio de Economía y Finanzas (MEF) ya precisó cuál sería el retroceso en el peor escenario del FEN, que tendrá su mayor efecto en los últimos meses del 2026 y el primer trimestre del 2027. De acuerdo con el ministerio, un FEN extraordinario, como se prevé, reduciría el crecimiento del Perú en 0.7 puntos porcentuales (p.p.) en 2026 y 0.6 p.p. en 2027. Así, el país crecería 2.7% y 2.8% este y el próximo año, respectivamente. Además, el Banco Central de Reserva del Perú acaba de revelar sus nuevas proyecciones para este y el próximo año. Las cifras se ajustaron ligeramente a la baja justamente por los impactos esperados de El Niño sobre la economía. ¿Qué tanto de esas caídas totales se explicará por el impacto en Piura? La interrogante es válida, mas si se recuerda que, tras Lima, la ciudad del norte es la segunda más habitada del Perú, con 2.1 millones de habitantes, de acuerdo al Censo Nacional 2025 del Instituto Nacional de Estadística e Informática (INEI). Al respecto Stephani Maita, economista senior del Instituto Peruano de Economía (IPE), puntualizó que, al cierre del primer trimestre, Piura creció 4.3%, aunque en el segundo trimestre ya se siente una desaceleración. “[Hacia adelante], nuestra perspectiva es que se empeore un poco porque buena parte de los productos principales de Piura se cosechan hacia fin del año. Hablo de las paltas y uvas, que fueron de los más golpeados en 2023″, sostuvo. A ello, Gabriela Espinar, economista de la Red de Estudios para el Desarrollo (Redes), sumó que desde 2015 el crecimiento de Piura ha sido muy frágil e inestable. “En los últimos 10 años ha crecido 2.5% en promedio, menor al promedio nacional. Tiene algunos picos y recesiones muy marcadas. Eso pasó en 2017, con el FEN, donde su economía retrocedió 2.4%”, indicó. En el MMM el MEF es bastante claro: los sectores primarios de la economía son los que sufrirán peores resultados gracias al FEN, sobre todo pesca; y en el área no primaria comercio, junto a servicios y manufactura también serían perjudicados. Precisamente todos esos son los principales motores productivos de Piura. Según el INEI, el rubro “otras actividades”, que incluye a otros servicios, pesca y acuicultura, representó el 23.8% del Valor Agregado Bruto (VAB) de la región en 2025. Le siguen, por encima del 10%, la manufactura, el comercio, y la agricultura. Tanto Maita como Espinar indicaron que, de recrudecer el FEN, el sector agropecuario servirá de referencia para medir las consecuencias económicas para la región. “El FEN genera dos tipos de costos, uno es el daño a la infraestructura, pero el otro es que se cae el empleo. Agricultura es fuerte en mano de obra en Piura. Cuando cae, golpea severamente los ingresos de las personas. Eso ya pasó en 2023 y 2017″, advirtió Espinar. Vinculado a ello, Maita recordó que Piura se ubicó en el puesto 17 entre los 25 departamentos en el Índice de Competitividad Regional (INCORE) 2026, lo que marca la baja calidad de los servicios que tiene. “En su caso hemos visto un deterioro sobre todo en los pilares de infraestructura y salud. En Piura ha crecido la anemia y los hogares no tienen acceso al agua por más de 12 horas. La región tiene un gran potencial, por ejemplo, en hidrocarburos, pero hay obras paralizadas”, lamentó. Piura es “experta” en recibir al FEN. Tanto Maita como Espinar recordaron los resultados que tuvo la región, en términos de PBI, en los años de sus últimas visitas: 2017 y 2023. Estos sirven de referencia para anticipar lo que podría resultar este 2026. En 2017, como ya dijo Espinar, Piura estuvo entre las regiones con mayores retrocesos del Perú, principalmente por la caída de su sector agropecuario, a consecuencia del embate del FEN Costero ese año especialmente el primer trimestre. Ello, vale decir, no evitó que el país crezca 2.5%. En 2023, donde aparte del FEN ocurrió el Ciclón Yaku, Piura creció 1%, mientras que Perú como país cayó en recesión (-0.55%). Esta tasa también tiene matices, puntualizan las economistas. El mundo dejaba atrás al Covid-19 y no todos sus sectores crecieron. ¿Qué escenario podría vivirse ahora? Las expertas consultadas por Gestión apuestan porque sea lo más similar al 2023: que Piura crezca, aunque sea poco. “Hay obras de prevención en desarrollo, con apoyo de la Autoridad Nacional del Agua (ANA). Eso es crucial, pero será importante una estrategia para aminorar impactos indirectos, nuevamente, en empleo, por ejemplo”, consideró Maita. Espinar agregó que hace falta que el Gobierno de Keiko Fujimori plantee otro plan para “recuperar” lo más posible a los rubros que ya han sufrido paras por el FEN. “La descolmatación es importante, pero también las medidas de apoyo a sectores vulnerables. Se deben proteger las hectáreas, pero también al agricultor, ¿saben qué hacer en épocas de crisis? Igual los pescadores, ¿hay espacio o no para continuar las capturas?“, preguntó.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://gestion.pe/economia/el-nino-acorta-crecimiento-de-peru-para-2026-y-2027-que-espera-ahora-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>¡Alerta en Piura! Bandas buscan infiltrarse en la Policía</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Alerta en Piura. El crimen organizado estaría intentando dar un paso más allá de las calles para penetrar una de las instituciones encargadas de combatirlo. Expertos en seguridad advirtieron que organizaciones criminales buscarían infiltrarse en la Policía Nacional desde las escuelas de formación, mediante la captación de jóvenes que posteriormente podrían convertirse en agentes al servicio de estructuras delictivas. La advertencia cobra especial importancia para Piura, una de las regiones del norte donde la criminalidad mantiene en alerta a las autoridades. El especialista en seguridad ciudadana Pedro Yaranga, explicó que el mecanismo de captación podría comenzar desde la etapa escolar. Según señaló, las estructuras criminales podrían financiar los estudios de menores y acompañar su preparación hasta que culminen la secundaria. Posteriormente, de acuerdo con su versión, recurrirían al pago de coimas para facilitar el ingreso de estos jóvenes a las escuelas de formación de la Policía Nacional. Una vez convertidos en suboficiales, podrían terminar trabajando para las organizaciones que financiaron su preparación. El objetivo sería contar con personal entrenado dentro de la institución policial, capaz de proteger los negocios ilícitos de las bandas y, eventualmente, proporcionar información que permita anticiparse a las acciones de las fuerzas del orden. En ese sentido, las bandas criminales no solo reclutan sicarios para ejecutar ataques, sino también reclutan policías, los forman. Yaranga, docente en Ciencia Política, consultor y analista en seguridad integral y gestión de riesgos, sostuvo que Trujillo se ha convertido en uno de los principales focos de criminalidad del país, pero advirtió que la problemática también alcanza a Tumbes y Piura. En ese contexto, llamó la atención sobre las escuelas policiales existentes en el norte y planteó la necesidad de revisar cuidadosamente quiénes ingresan a estos centros de formación. La preocupación no se limita al proceso de admisión. Una persona vinculada con una organización criminal que consiga convertirse en policía podría acceder a conocimientos, entrenamiento e información sensible durante su carrera. De acuerdo con el planteamiento de Yaranga, un agente infiltrado podría convertirse en una pieza estratégica para una banda, al conocer movimientos policiales, operativos, investigaciones y acciones de inteligencia. Esto permitiría a las estructuras criminales anticiparse o evadir los golpes de las autoridades. INFORMACIÓN POLICIAL La alerta también fue planteada por el exministro del Interior Ricardo Valdés, quien sostuvo que las organizaciones criminales muchas veces buscan infiltrarse en la Policía Nacional precisamente para asegurar información policial. Valdés señaló que esta estrategia no correspondería únicamente a una determinada banda, sino que podría ser utilizada por distintas organizaciones. Mencionó, entre otras, a “Los Pulpos” y “La Jauría”, aunque remarcó que se trata de un problema de alcance más amplio. Según el exministro, una de las vías para conseguirlo sería incorporar a las escuelas policiales a jóvenes, familiares o personas relacionadas con organizaciones criminales. La advertencia representa un nuevo desafío para Piura, donde la lucha contra homicidios, extorsiones y otras manifestaciones del crimen organizado exige reforzar la capacidad de respuesta de la Policía. FORTALECER FILTROS Para los especialistas, resulta fundamental fortalecer los filtros de ingreso, los controles durante la formación y los mecanismos de inteligencia interna. La prevención, sostienen, debe comenzar antes de que los futuros agentes reciban el uniforme y tengan acceso a información policial. El riesgo, finalmente, no estaría únicamente en las calles. Las bandas criminales buscarían entrar a las instituciones para convertir a futuros agentes del orden en piezas estratégicas de sus propias estructuras. Crimen organizado financiaría a postulantes a Policía El crimen organizado estaría encontrando una peligrosa puerta de entrada a la Policía Nacional: financiar a jóvenes de escasos recursos para que puedan ingresar a las escuelas de formación de suboficiales y, posteriormente, convertirse en agentes con acceso a información privilegiada. La advertencia fue formulada por el exviceministro del Interior Julio Corcuera, quien sostuvo que organizaciones criminales habrían comenzado a colocar a jóvenes vinculados con sus estructuras dentro de las escuelas policiales. Según explicó, el mecanismo aprovecharía las dificultades económicas que enfrentan algunas familias para cubrir los gastos exigidos durante la formación. Corcuera señaló que las denominadas garantías para los estudiantes pueden alcanzar entre 7 mil y 10 mil soles, monto que representaría una barrera para muchos postulantes provenientes de sectores populares. En ese escenario, las organizaciones criminales podrían asumir esos costos con la finalidad de obtener, a futuro, favores o información desde el interior de la institución. El exfuncionario consideró urgente reforzar los filtros de ingreso y revisar exhaustivamente los antecedentes familiares y las relaciones de los postulantes. También advirtió sobre policías cuyos bienes no guardarían correspondencia con sus ingresos y mencionó como ejemplo al agente Orlando Santos, a quien atribuyó la adquisición de costosas camionetas pese a percibir unos 2,900 soles mensuales. Este señalamiento requiere ser acreditado mediante una investigación oficial. Para Corcuera, no se trata de toda la Policía, sino de un sector que podría estar siendo contaminado por el poder económico del crimen organizado. La alerta cobra mayor importancia ante la expansión del crimen transnacional en Piura y Tumbes. “Hay una contaminación de la presencia del crimen transnacional organizado en el Perú. Un país tan lejano como Albania tiene presencia en Piura y Tumbes; como operan con narcotráfico en Ecuador lavan su dinero en Tumbes y Piura”, refirió.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/alerta-en-piura-bandas-buscan-infiltrarse-en-la-policia/</t>
         </is>
       </c>
     </row>
@@ -882,46 +905,58 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Identifican 13 cuencas ciegas ante eventual Fenómeno El Niño</t>
+          <t>Ayabaca: Un muerto y tres heridos deja caída de camioneta al abismo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>La Universidad Nacional de Piura (UNP), a nivel interno y externo, ha trazado una línea de acciones sobre las medidas de prevención ante el anunciado fenómeno de El Niño, cuya posible magnitud extraordinaria ha sido advertida por organismos nacionales e internacionales. El rector encargado de la UNP, Adolfo Zeta Vite señaló que ya se realizó un diagnóstico interno y se identificó una situación de alta vulnerabilidad debido a la acumulación de agua dentro del campus. El diagnóstico permitió identificar 13 cuencas ciegas distribuidas en diferentes instalaciones, entre ellas las facultades de Administración, Contabilidad, Ingeniería Civil, Ingeniería Industrial y Medicina, además del rectorado, Idepunp, la Escuela Tecnológica, el Hospital Universitario y locales de posgrado y Responsabilidad Social Universitaria. FALTA DE DRENAJE Uno de los principales problemas es la falta de drenaje adecuado hacia el río Piura, situación que se habría agravado con la construcción de la carretera. Según explicó la autoridad universitaria, antes el agua podía discurrir hacia el río o ser bombeada con mayor facilidad, pero actualmente existe riesgo de acumulación de aguas dentro del campus. La autoridad universitaria detalló que también se gestiona proteger laboratorios e infraestructura valorizada en millones de soles. Entre las alternativas planteadas figura la construcción de pozas de percolación para enfrentar la acumulación de agua; sin embargo, señala que existen limitaciones presupuestales debido a que los recursos de emergencia gestionados ante el Ministerio de Educación están destinados principalmente a servicios de mitigación y no a nuevas obras. AJUSTES EN PRESUPUESTO Ante esta situación, la universidad realiza ajustes internos a su presupuesto y gestiona apoyo ante el Minedu, el Ministerio de Economía y Finanzas (MEF) y representantes del Congreso. La comunidad universitaria está conformada por aproximadamente 15 mil estudiantes y 500 docentes, quienes podrían verse afectados si las lluvias dificultan el acceso al campus o interrumpen las actividades académicas. Además, se evalúa la implementación de clases virtuales si las condiciones impiden continuar con la enseñanza presencial, aunque esta alternativa también enfrenta dificultades por problemas de energía, conectividad y acceso a equipos. BRIGADAS Adolfo Zeta, pese a las dificultades presupuestarias, analiza asimismo la conformación de brigadas de apoyo a poblaciones vulnerables, con participación de estudiantes y profesionales de Medicina, Ingeniería Civil y Arquitectura, los mismos que participarían activamente en algunas emergencias que se puedan presentar por la caída de intensas lluvias en la región.</t>
+          <t>Sigue la tragedia en las carreteras de la región. Esta vez, la ruta rural Pacaipampa-Huancabamba-San Ignacio fue escenario de un trágico accidente, que dejó el saldo de un fallecido y tres heridos, uno de ellos un menor de edad. El suceso ocurrió cerca de las cinco de la mañana de ayer, cuando una camioneta de placa Z3R-773, conducida por Walter Huancas Facundo, de 24 años, cubría la mencionada ruta tuvo un percance, luego de despistarse y caer a un abismo. PUEDES LEER ► EsSalud permitirá que pacientes hospitalizados permanezcan acompañados por un familiar las 24 horas DAMAS Y NIÑO SE SALVAN Como consecuencia del aparatoso accidente, el conductor perdió la vida en el lugar. De acuerdo con la información preliminar, el fallecido era natural de Mitupampa, distrito de Sondorillo. Se desconoce las causas que provocaron el lamentable accidente. Asimismo, dos mujeres y un menor de edad resultaron heridos. Las damas presentarían fracturas en distintas partes del cuerpo por lo que fueron trasladadas de emergencia al nosocomio de la zona para su posterior traslado a Piura. RESCATE EN EL ABISMO Personal de salud de Jicate y Huancacarpa acudió para brindar atención y trasladar a los heridos hacia el E.S. I-4 Huancabamba. En la agreste zona también llegaron integrantes del grupo de rescate Virgen del Carmen , quienes participan en las labores para recuperar el vehículo siniestrado. La partida del joven transportista Walter Huancas ha causado consternación entre sus familiares, parientes y amigos, los mismos que señalan que conducía desde hace más de cuatro años por las rutas de la sierra altoandina. Sus restos fueron trasladados al nosocomio para las diligencias de rigor.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/identifican-13-cuencas-ciegas-ante-eventual-fenomeno-el-nino/</t>
+          <t>https://eltiempo.pe/local/ayabaca-un-muerto-y-tres-heridos-deja-caida-de-camioneta-al-abismo/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANGR advierte paralización de proyectos por recorte presupuestal</t>
+          <t>Senamhi: calor diurno llegará a 36 °C en costa norte y a 31 °C en la sierra desde hoy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>El presidente de la Asamblea Nacional de Gobiernos Regionales (ANGR) y gobernador regional de Piura, Luis Neyra, advirtió que el recorte del 20% en el presupuesto inicial para el 2027 pone en riesgo la continuidad de proyectos de infraestructura a nivel nacional. La postura fue expresada tras la reunión de trabajo sostenida entre el consejo directivo de la ANGR, el presidente del Consejo de Ministros, Luis Galarreta, y el titular del Ministerio de Economía y Finanzas, Elmer Cuba. El titular de la ANGR exigió al Ejecutivo restituir los fondos asignados a los gobiernos regionales, destacando que en los últimos 4 años las regiones lideraron la eficiencia en ejecución de inversiones, superando al gobierno central y a los municipios. «Dejamos en claro que cualquier proyecto que se paralice el próximo año, la culpa no será de estas gestiones, sino de la falta de presupuesto que se dejó de otorgar por el Ministerio de Economía», afirmó Neyra. Defensa de fondos para las autoridades electas en octubre El representante regional remarcó que las autoridades en funciones deben asegurar los recursos para las gestiones que serán elegidas en los comicios del 4 de octubre, o en una eventual segunda vuelta, evitando el incremento de obras paralizadas. Las regiones demandan que el Ministerio de Economía y Finanzas respete el principio de presupuesto por resultados y mantenga, como mínimo, el Presupuesto Inicial de Apertura otorgado en ejercicios anteriores.</t>
+          <t>Según el aviso meteorológico 373 , con nivel de alerta rojo, del Senamhi, se prevén temperaturas máximas entre 25 °C y 36 °C en la costa norte, entre 24 °C y 30 °C en la costa central, y entre 22 °C y 30 °C en la costa sur.
+????? #Aviso #Minam #Senamhi Del 20 al 22 de setiembre, continuará el incremento de la temperatura diurna en la costa y en la sierra del país.
+?Se prevé escasa nubosidad hacia el mediodía, aumento de radiación UV y ráfagas de viento.
+?? https://t.co/vGrK6VkLIs pic.twitter.com/CH7YefyZ8y — Senamhi (@Senamhiperu) September 19, 2026 Asimismo, se esperan temperaturas máximas entre 25 °C y 31 °C en la sierra norte, entre 24 °C y 29 °C en la sierra central, y registros entre 15 °C y 29 °C en la sierra sur.
+También se prevé escasa nubosidad hacia el mediodía, lo que contribuirá al aumento de los niveles de radiación ultravioleta (UV).
+Igualmente, se esperan ráfagas de viento con velocidades cercanas a los 40 km/h, principalmente durante horas de la tarde.
+No se descartan lluvias dispersas en la costa norte.
+Los departamentos comprendidos en este aviso meteorológico son Amazonas, Áncash, Apurímac, Arequipa, Ayacucho, Cajamarca, Callao, Huancavelica, Huánuco, Ica, Junin, La Libertad, Lambayeque, Lima, Pasco, Piura, Puno y Tumbes.
+Preparación y prevención Ante esta situación, el Instituto Nacional de Defensa Civil (Indeci) recomienda a la población aplicarse bloqueador y/o protector solar, si está expuesto a la radiación solar, así como usar sombreros de ala ancha y gafas con filtro ultravioleta.
+Asimismo, se sugiere beber abundante líquido, no ingerir comidas y refrescos que no tengan refrigeración, ni exponerse de forma directa a los rayos de sol.
+Del mismo modo, se debe asegurar que los pescados, mariscos y carnes rojas se encuentren frescos para evitar intoxicación.
+También se recomienda mantener una ventilación adecuada en casa y centro de labores, así como utilizar colores claros en la ropa, evitar las actividades físicas entre las 10:00 y las 17:00 horas, y procurar tener en casa sobres de suero oral.
+El Indeci, a través del Centro de Operaciones de Emergencia Nacional (COEN), monitorea los departamentos alertados y coordina con las autoridades regionales y locales los efectos de este fenómeno meteorológico.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/angr-advierte-paralizacion-de-proyectos-por-recorte-presupuestal/</t>
+          <t>https://andina.pe/agencia/noticia-senamhi-calor-diurno-llegara-a-36-°c-costa-norte-y-a-31-°c-la-sierra-desde-hoy-1092504.aspx</t>
         </is>
       </c>
     </row>
@@ -932,21 +967,21 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Más de 123 mil habitantes de Talara en riesgo de desabastecimiento de agua potable por mal estado de línea de conducción</t>
+          <t>Piura supera los 10 mil casos de dengue y refuerzan llamado a completar vacunación</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La Contraloría General constató que la línea de conducción de agua potable Paita-Talara, así como el equipamiento electromecánico e infraestructura que se encuentra a lo largo de su recorrido, presenta evidente deterioro y otras deficiencias técnicas en su operación, lo cual ha sido omitido como trabajos de mantenimiento necesarios en el plan de gestión reactiva aprobado por la EPS Grau S.A. Dicha situación podría afectar el abastecimiento continuo de más de 123 000 habitantes de la provincia de Talara y se agravaría con la llegada de un eventual Fenómeno El Niño. Según el Informe de Visita de Control N° 020-2026-OCI/3470-SVC, (periodo de evaluación del 18 al 28 de agosto de 2026), la línea de conducción se extiende desde la Planta de Tratamiento de Agua Potable (PTAP) EI Arenal-Paita hasta la cámara de válvulas T-5 (Talara), con una longitud total de 56.30 km y un diámetro de 600 mm. El material de la tubería está constituido principalmente por hierro dúctil. A lo largo de su recorrido, esta línea integra la estación de bombeo n.° 1, estación de bombeo n.° 2 y la cámara de carga. En la estación de bombeo n.° 1, se verificó que la infraestructura carece de cerco perimétrico. Esta estación fue diseñada para operar con cuatro electrobombas, de las cuales solo dos permanecen operativas. Incluso, los equipos en servicio funcionan de forma continua desde 1996, año en que reemplazaron a las bombas instaladas en 1979. También se advirtió que los manómetros se encuentran inoperativos y los ejes de los equipos en funcionamiento no cuentan con protección, lo cual representa un riesgo para los operadores. Del mismo modo, el sistema instalado para la medición del nivel de la cisterna se encuentra inoperativo y actualmente se ejecuta esa acción de forma manual. Asimismo, se constató una fuga de agua en la tubería conectada al tanque antiariete (recipiente que protege las tuberías al absorber las ondas de presión y los golpes de energía), la cual está socavando la base de la estructura de la línea de conducción, así como el dado de concreto que le sirve de apoyo. Además, se observó que la válvula de la línea de descarga carece de volante de accionamiento, por lo que su manipulación se viene realizando de manera provisional mediante una llave. A ello se suman las fisuras y grietas en los muros y en la base de la sala de máquinas. Tampoco cuentan con grupo electrógeno o fuente de electrificación alterna. Incluso, durante el periodo lluvioso, deben colocar sacos de arena, a fin de que el agua que discurre de las partes altas no golpee el portón, situado en la parte posterior de la estación, y se corre el riesgo de afectar el equipamiento electromecánico. También, se observó que la línea de conducción, entre ambas estaciones, cuenta con un tramo junto al cual se ha construido una carretera, alterando el cauce natural de una quebrada, que se sitúa entre la vía y la línea de conducción. En tiempo de lluvias, al discurrir las aguas por la quebrada, se han ido socavando los soportes de concreto de la tubería, así como la cimentación de los dados de apoyo de la misma. En relación a la estación de bombeo n.° 2, se verificó que no posee cerco perimétrico y, al igual que la estación anterior, viene funcionando con dos electrobombas, una de las cuales tiene una antigüedad cercana a los 50 años. Respecto a la cámara de carga, una estructura de concreto de 1000 m3 de capacidad que al estar ubicada en el punto más alto de la línea debería brindar la presión necesaria para el abastecimiento, solo funciona como elemento de paso. Está abandonada, sin cerco ni escalera y tanto la válvula de ingreso y salida no cuenta con protección, estando actualmente expuestas a manipulaciones y riesgos sanitarios. Además, se identificó que en un drenaje de la línea existen diversas conexiones directas a la línea de distribución. La línea de conducción atraviesa diferentes quebradas como La Débora, mediante tubería subterránea de fibra de vidrio enterrada en el cauce, y El Acholado, a través de una estructura de pase aéreo. Una eventual activación de quebradas configura un escenario de alto riesgo para la línea de conducción, debido al deterioro de los soportes de la misma a lo largo de su recorrido, así como en la estructura del pase aéreo, la cual presenta un deterioro significativo e incluso la falta de elementos estructurales.</t>
+          <t>Piura registra 10,009 casos de dengue y seis fallecidos en lo que va de 2026 , según la actualización de las autoridades sanitarias. A nivel nacional, el acumulado alcanza los 52,395 casos y 63 muertes. El epidemiólogo del Ministerio de Salud, Ciro Adolfo García Vilela, advirtió que la transmisión del dengue continúa durante el segundo semestre del año y presenta un comportamiento distinto al observado en temporadas anteriores, cuando los contagios se concentraban principalmente durante los primeros meses. El especialista explicó que las temperaturas elevadas favorecen el desarrollo del Aedes aegypti , mosquito transmisor del dengue. Bajo estas condiciones, el ciclo de reproducción del vector puede acortarse de unos siete días a entre cuatro y cinco, lo que permite que aumente rápidamente su población. PUEDES LEER ► Desaparecen más de 100 mil mypes de comercio Eliminación de criaderos es clave para frenar el dengue García señaló que el tratamiento de las personas enfermas permite atender las consecuencias de la infección, pero que la prevención debe centrarse también en reducir la presencia del mosquito. Por ello, recomendó evitar la acumulación de agua en recipientes y mantener correctamente cerrados los depósitos utilizados para almacenar este recurso. También pidió retirar objetos que puedan convertirse en criaderos del mosquito. Piura mantiene baja cobertura de vacunación Ante el incremento de casos, el Ministerio de Salud mantiene la vacunación contra el dengue dirigida a niños, adolescentes y jóvenes de 10 a 20 años de las zonas priorizadas. El esquema contempla dos dosis, administradas con un intervalo de tres meses . El objetivo de esta estrategia es disminuir el riesgo de hospitalización y complicaciones asociadas a la enfermedad. Sin embargo, la cobertura en Piura continúa siendo baja. Un reporte con información actualizada al 3 de septiembre señaló que apenas 6.9 % de la población objetivo había recibido la primera dosis , mientras que solo el 1.9 % había completado la segunda . Minsa reporta disponibilidad de vacunas En agosto, el Ministerio de Salud informó que recibió 444,780 dosis destinadas a fortalecer la vacunación en las regiones priorizadas, entre ellas Piura. En ese mismo periodo, el sector salud indicó que la región contaba con más de 140 mil dosis disponibles , las cuales son aplicadas en establecimientos de salud y mediante campañas desarrolladas en instituciones educativas. Las autoridades sanitarias exhortan a las familias de los distritos incluidos en la estrategia a consultar en los establecimientos de salud sobre los criterios de vacunación y autorizar la inmunización de los menores que formen parte de la población objetivo. Quienes ya recibieron la primera dosis deben acudir cuando corresponda para completar el esquema establecido. La vacunación, además, debe acompañarse de medidas para eliminar los criaderos del Aedes aegypti , como tapar los depósitos de agua, retirar recipientes que acumulen agua y facilitar el trabajo de las brigadas de control vectorial.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/mas-de-123-mil-habitantes-de-talara-en-riesgo-de-desabastecimiento-de-agua-potable-por-mal-estado-de-linea-de-conduccion/</t>
+          <t>https://eltiempo.pe/local/piura-supera-los-10-mil-casos-de-dengue-y-refuerzan-llamado-a-completar-vacunacion/</t>
         </is>
       </c>
     </row>
@@ -961,17 +996,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piura: mar frente a Paita registra hasta 7 °C más de temperatura de lo normal</t>
+          <t>Cuestionan estado de obras y proyectos en Catacaos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>La temperatura del mar frente a Piura continúa muy por encima de sus valores habituales para esta época del año. Frente a Paita, el agua del océano registra actualmente entre 24 y 25 °C, cuando lo normal durante este periodo sería encontrar valores de aproximadamente 17 a 18 °C. La diferencia representa una anomalía positiva de entre 6 y 7 °C , una condición que viene siendo observada con atención debido a sus posibles efectos sobre el comportamiento climático de los próximos meses y, especialmente, sobre el escenario de lluvias que podría presentarse durante el verano de 2027. El dato fue dado a conocer por Rodolfo Rodríguez Arisméndiz, especialista de la Universidad de Piura (UDEP) y director de la Estación Científica Ramón Mugica. Según explicó, las actuales condiciones del mar constituyen una señal que debe ser monitoreada ante la posibilidad de un periodo de precipitaciones intensas en el norte del país. La UDEP informó el 17 de septiembre que el mar frente a Paita se encontraba entre 24 y 25 °C, frente a los 17 y 18 °C habituales para esta época. El especialista precisó que, cuando la temperatura supera los 25 °C, se configura un ambiente más favorable para la formación de lluvias, aunque la intensidad y ocurrencia de estas precipitaciones dependen también de otros factores atmosféricos. ¿Por qué preocupa la temperatura del mar frente a Paita? El océano cumple un papel importante en la evolución del clima de la costa norte peruana. Cuando las aguas superficiales presentan temperaturas superiores a las habituales, aumenta la disponibilidad de humedad y energía que puede contribuir al desarrollo de sistemas de lluvias. Sin embargo, una temperatura elevada del mar no significa por sí sola que necesariamente se produzcan lluvias intensas. De acuerdo con Rodríguez, deben considerarse también las condiciones de la atmósfera y otros elementos que intervienen en la evolución del clima. El escenario adquiere especial relevancia porque el calentamiento se mantiene durante el invierno. El especialista explicó que el ingreso del verano podría sumar el calentamiento natural propio de la temporada a las actuales condiciones cálidas del océano. “Probablemente tengamos lluvias fuertes, principalmente en los meses del verano del 2027”, señaló Rodríguez, según la información difundida por la Universidad de Piura. Piura y las señales de un mar anormalmente cálido Los registros recientes del Instituto del Mar del Perú (IMARPE) también muestran que el calentamiento frente a la costa norte viene siendo persistente durante 2026. En uno de sus boletines de agosto, IMARPE reportó frente a Paita valores de anomalía de la temperatura superficial del mar de hasta +7,41 °C , mientras que el promedio de la anomalía a lo largo de la costa peruana alcanzó +4,37 °C. El comportamiento no es completamente reciente. En junio, el monitoreo de IMARPE ya había identificado condiciones cálidas de fuerte intensidad frente a Paita, con anomalías que aumentaban hacia la zona oceánica y alcanzaban valores de hasta +8 °C en determinados puntos y profundidades. Estos registros permiten observar que el calentamiento del mar frente al norte peruano ha presentado variaciones importantes durante el año y que Paita se encuentra entre las zonas que han mostrado las anomalías térmicas más destacadas. ¿Qué relación existe entre el mar caliente y las lluvias? Una temperatura del mar superior a los 25 °C puede favorecer una mayor disponibilidad de humedad para la atmósfera. En el caso de la costa norte, esto puede convertirse en un factor relevante para la formación de precipitaciones cuando coincide con determinadas condiciones atmosféricas. Rodríguez explicó que superar ese umbral genera condiciones más favorables para las lluvias, pero remarcó que no constituye por sí mismo una garantía de precipitaciones fuertes. Por ello, la evolución de la temperatura marina durante las próximas semanas será uno de los elementos que deberán seguirse para conocer con mayor precisión el escenario climático del verano. ¿Qué podría ocurrir durante el verano de 2027? El especialista de la UDEP advirtió que el comportamiento actual debe considerarse una señal de alerta y seguimiento. Si las temperaturas elevadas del océano persisten hasta el verano, podrían coincidir con el incremento térmico habitual de esa estación. En ese escenario, Piura y otras zonas del norte peruano podrían enfrentar condiciones favorables para la ocurrencia de lluvias de mayor intensidad. No obstante, determinar su magnitud y distribución requerirá observar la evolución de los indicadores oceánicos y atmosféricos. La experiencia de años anteriores ha mostrado que las lluvias intensas pueden generar impactos importantes en ciudades, vías, sistemas de drenaje, infraestructura y zonas cercanas a ríos y quebradas. Por esa razón, el seguimiento temprano de las condiciones del océano resulta relevante para la planificación de medidas preventivas. Preparación ante posibles lluvias intensas en Piura Rodríguez sostuvo que las autoridades no deberían limitarse al diagnóstico de las condiciones climáticas, sino avanzar también en acciones de prevención y mitigación. Según el especialista, la preparación debería involucrar a distintos niveles de gobierno y a la población. Esto incluye acciones a nivel vecinal, municipal, regional y nacional destinadas a reducir los posibles efectos de un periodo de lluvias intensas. En una región como Piura, donde las precipitaciones extraordinarias pueden generar rápidamente problemas de drenaje, desbordes y afectaciones en infraestructura, la anticipación resulta especialmente importante. ¿Qué se debe monitorear en las próximas semanas? Uno de los principales indicadores será la evolución de la temperatura superficial del mar frente a Paita . También será necesario observar las condiciones atmosféricas, los vientos, la humedad y otros factores que pueden modificar el comportamiento de las lluvias. IMARPE mantiene un seguimiento permanente de las condiciones oceanográficas frente a la costa peruana. Sus boletines permiten identificar cambios en la temperatura del mar y otros indicadores asociados al comportamiento del océano. Para Piura , las próximas semanas serán importantes. El comportamiento del mar permitirá conocer si el actual calentamiento disminuye, se mantiene o continúa intensificándose antes del inicio del verano de 2027. Mientras tanto, la recomendación planteada por el especialista de la UDEP apunta a mantener la vigilancia y avanzar con anticipación en medidas de prevención frente a un posible escenario de lluvias fuertes.</t>
+          <t>Ciudadanos formularon cuestionamientos sobre el estado de diversas obras y proyectos municipales frente al alcalde de Catacaos, Jhonny Cruz Flores, junto a sus regidores y funcionarios. Durante la jornada, Carla Palacios, representante de la Asociación Catacaos Unidos, cuestionó la situación actual de la Alameda Lucas Cutivalú, señalando que el espacio se encuentra deteriorado, sin iluminación y en aparente estado de abandono, pese a que, según manifestó, se habría destinado aproximadamente 360 mil soles para su mejoramiento e iluminación. Palacios también pidió explicaciones sobre el proyecto de seguridad ciudadana, ejecutado bajo la modalidad de obras por impuestos y con una inversión aproximada de 12 millones de soles. Cuestionó que la empresa contratista no habría cumplido con el expediente técnico y preguntó por las medidas adoptadas por la municipalidad frente a esta situación. Ante los cuestionamientos, el gerente de Infraestructura de la Municipalidad de Catacaos, Aldo García, explicó que la recepción de los trabajos de la Alameda Lucas Cutivalú se realizó hasta el punto donde fue posible culminar la intervención, debido a una interferencia con la ejecución de una obra de alcantarillado de BPO.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-mar-frente-a-paita-registra-hasta-7-c-mas-de-temperatura-de-lo-normal/</t>
+          <t>https://eltiempo.pe/local/cuestionan-estado-de-obras-y-proyectos-en-catacaos/</t>
         </is>
       </c>
     </row>
@@ -986,10 +1021,73 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Piura: Ministro de Vivienda y senadores verifican funcionamiento de SARES ante El Niño</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Durante la reunión, el titular del sector anunció que, entre setiembre y diciembre de este año, se realizarán 44 intervenciones de limpieza y descolmatación en las provincias de Huancabamba, Sullana y Morropón, que abarcarán 39,8 kilómetros de ríos y canales , en beneficio de más de 162 mil ciudadanos .
+Asimismo, informó que el 19 de octubre se desarrollará un simulacro de lluvias intensas e inundaciones en Piura , con el propósito de fortalecer la preparación y capacidad de respuesta frente a posibles emergencias.
+En ese sentido, resaltó la importancia del trabajo articulado entre los tres niveles de gobierno para proteger la vida y salud de las familias piuranas.
+“ Es importante conocer la capacidad que tienen todos los sectores, como EPS Grau, el Gobierno Regional y las municipalidades.
+Esta reunión ha sido muy importante porque nos ha permitido conocer de primera mano todo lo que se viene realizando de cara al fenómeno El Niño ”, señaló el ministro Mauricio Arnillas.
+Supervisión de SARES Como parte de su agenda de trabajo, el ministro supervisó el funcionamiento de los Sistemas Alternativos de Recolección y Evacuación de Aguas de Lluvia o Pluviales (SAREs) El Chilcal e Ignacio Merino , infraestructura clave para reducir el riesgo de inundaciones durante la temporada de lluvias y proteger a las familias piuranas.
+El Ministerio de Vivienda ha implementado nueve SARES en la región Piura : ocho en la provincia de Piura (Cinco Esquinas, La Molina II, Nuevo Amanecer, Ignacio Merino, El Chilcal, Gullman, Tacna e Irazola) y uno en la provincia de Sullana (Villa Primavera).
+En la inspección participaron los senadores Karla Schaefer y Nilson Flores; el diputado Eduardo Castillo; el alcalde de Piura, Juan Cevallos; y el gerente de EPS Grau.
+Limpieza y descolmatación en el dren Simbalá El titular del sector también llegó a Catacaos para supervisar los trabajos de limpieza y descolmatación en el dren Simbalá, donde la maquinaria del Ministerio de Vivienda viene trabajando para reducir el riesgo de inundaciones ante las lluvias intensas.
+La intervención contempla la remoción de material sedimentado en el cauce, mediante el uso de una excavadora, un cargador frontal y dos volquetes, contribuyendo a proteger a cerca de 1,400 pobladores de la zona.
+Además, junto a la senadora Karla Schaefer, el ministro visitó el dique Viduque para verificar las acciones preventivas que se desarrollan ante el fenómeno El Niño .
+“ En lo que va del año, el sector ejecutó 27 intervenciones de limpieza y descolmatación en 49 km de ríos y canales, retirando 152 mil m³ de sedimentos para proteger a 114 mil pobladores de seis provincias.
+Un canal o un dren puede salvar vidas; por eso, es fundamental que la población contribuya a su cuidado y conservación”, destacó el titular del sector.
+Finalmente, el ministro sostuvo una reunión con representantes de EPS Grau e inspeccionó la Planta de Tratamiento de Agua Potable (PTAP) Curumuy , que abastece de este servicio básico a los distritos de Piura, Castilla y Veintiséis de Octubre.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-piura-ministro-vivienda-y-senadores-verifican-funcionamiento-sares-ante-nino-1092506.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Piura: mar frente a Paita registra hasta 7 °C más de temperatura de lo normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>La temperatura del mar frente a Piura continúa muy por encima de sus valores habituales para esta época del año. Frente a Paita, el agua del océano registra actualmente entre 24 y 25 °C, cuando lo normal durante este periodo sería encontrar valores de aproximadamente 17 a 18 °C. La diferencia representa una anomalía positiva de entre 6 y 7 °C , una condición que viene siendo observada con atención debido a sus posibles efectos sobre el comportamiento climático de los próximos meses y, especialmente, sobre el escenario de lluvias que podría presentarse durante el verano de 2027. El dato fue dado a conocer por Rodolfo Rodríguez Arisméndiz, especialista de la Universidad de Piura (UDEP) y director de la Estación Científica Ramón Mugica. Según explicó, las actuales condiciones del mar constituyen una señal que debe ser monitoreada ante la posibilidad de un periodo de precipitaciones intensas en el norte del país. La UDEP informó el 17 de septiembre que el mar frente a Paita se encontraba entre 24 y 25 °C, frente a los 17 y 18 °C habituales para esta época. El especialista precisó que, cuando la temperatura supera los 25 °C, se configura un ambiente más favorable para la formación de lluvias, aunque la intensidad y ocurrencia de estas precipitaciones dependen también de otros factores atmosféricos. ¿Por qué preocupa la temperatura del mar frente a Paita? El océano cumple un papel importante en la evolución del clima de la costa norte peruana. Cuando las aguas superficiales presentan temperaturas superiores a las habituales, aumenta la disponibilidad de humedad y energía que puede contribuir al desarrollo de sistemas de lluvias. Sin embargo, una temperatura elevada del mar no significa por sí sola que necesariamente se produzcan lluvias intensas. De acuerdo con Rodríguez, deben considerarse también las condiciones de la atmósfera y otros elementos que intervienen en la evolución del clima. El escenario adquiere especial relevancia porque el calentamiento se mantiene durante el invierno. El especialista explicó que el ingreso del verano podría sumar el calentamiento natural propio de la temporada a las actuales condiciones cálidas del océano. “Probablemente tengamos lluvias fuertes, principalmente en los meses del verano del 2027”, señaló Rodríguez, según la información difundida por la Universidad de Piura. Piura y las señales de un mar anormalmente cálido Los registros recientes del Instituto del Mar del Perú (IMARPE) también muestran que el calentamiento frente a la costa norte viene siendo persistente durante 2026. En uno de sus boletines de agosto, IMARPE reportó frente a Paita valores de anomalía de la temperatura superficial del mar de hasta +7,41 °C , mientras que el promedio de la anomalía a lo largo de la costa peruana alcanzó +4,37 °C. El comportamiento no es completamente reciente. En junio, el monitoreo de IMARPE ya había identificado condiciones cálidas de fuerte intensidad frente a Paita, con anomalías que aumentaban hacia la zona oceánica y alcanzaban valores de hasta +8 °C en determinados puntos y profundidades. Estos registros permiten observar que el calentamiento del mar frente al norte peruano ha presentado variaciones importantes durante el año y que Paita se encuentra entre las zonas que han mostrado las anomalías térmicas más destacadas. ¿Qué relación existe entre el mar caliente y las lluvias? Una temperatura del mar superior a los 25 °C puede favorecer una mayor disponibilidad de humedad para la atmósfera. En el caso de la costa norte, esto puede convertirse en un factor relevante para la formación de precipitaciones cuando coincide con determinadas condiciones atmosféricas. Rodríguez explicó que superar ese umbral genera condiciones más favorables para las lluvias, pero remarcó que no constituye por sí mismo una garantía de precipitaciones fuertes. Por ello, la evolución de la temperatura marina durante las próximas semanas será uno de los elementos que deberán seguirse para conocer con mayor precisión el escenario climático del verano. ¿Qué podría ocurrir durante el verano de 2027? El especialista de la UDEP advirtió que el comportamiento actual debe considerarse una señal de alerta y seguimiento. Si las temperaturas elevadas del océano persisten hasta el verano, podrían coincidir con el incremento térmico habitual de esa estación. En ese escenario, Piura y otras zonas del norte peruano podrían enfrentar condiciones favorables para la ocurrencia de lluvias de mayor intensidad. No obstante, determinar su magnitud y distribución requerirá observar la evolución de los indicadores oceánicos y atmosféricos. La experiencia de años anteriores ha mostrado que las lluvias intensas pueden generar impactos importantes en ciudades, vías, sistemas de drenaje, infraestructura y zonas cercanas a ríos y quebradas. Por esa razón, el seguimiento temprano de las condiciones del océano resulta relevante para la planificación de medidas preventivas. Preparación ante posibles lluvias intensas en Piura Rodríguez sostuvo que las autoridades no deberían limitarse al diagnóstico de las condiciones climáticas, sino avanzar también en acciones de prevención y mitigación. Según el especialista, la preparación debería involucrar a distintos niveles de gobierno y a la población. Esto incluye acciones a nivel vecinal, municipal, regional y nacional destinadas a reducir los posibles efectos de un periodo de lluvias intensas. En una región como Piura, donde las precipitaciones extraordinarias pueden generar rápidamente problemas de drenaje, desbordes y afectaciones en infraestructura, la anticipación resulta especialmente importante. ¿Qué se debe monitorear en las próximas semanas? Uno de los principales indicadores será la evolución de la temperatura superficial del mar frente a Paita . También será necesario observar las condiciones atmosféricas, los vientos, la humedad y otros factores que pueden modificar el comportamiento de las lluvias. IMARPE mantiene un seguimiento permanente de las condiciones oceanográficas frente a la costa peruana. Sus boletines permiten identificar cambios en la temperatura del mar y otros indicadores asociados al comportamiento del océano. Para Piura , las próximas semanas serán importantes. El comportamiento del mar permitirá conocer si el actual calentamiento disminuye, se mantiene o continúa intensificándose antes del inicio del verano de 2027. Mientras tanto, la recomendación planteada por el especialista de la UDEP apunta a mantener la vigilancia y avanzar con anticipación en medidas de prevención frente a un posible escenario de lluvias fuertes.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-mar-frente-a-paita-registra-hasta-7-c-mas-de-temperatura-de-lo-normal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Saber reconocer los síntomas de la apendicitis puede evitar complicaciones graves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>El Dr.
 Héctor Shibao, cirujanogeneral y especialista en coloproctología, afirmó que para evitar complicaciones hay que saber reconocer los síntomas de esta enfermedad, entre ellos la aparición de dolor abdominal intenso y progresivo, especialmente si comienza alrededor del ombligo y se desplaza hacia la parte inferior derecha.
@@ -1004,84 +1102,34 @@
 El tratamiento habitual es la apendicectomía o una intervención para retirar el apéndice, mediante cirugía laparoscópica o cirugía abierta</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-saber-reconocer-los-sintomas-de-apendicitis-puede-evitar-complicaciones-graves-1092509.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Cuestionan estado de obras y proyectos en Catacaos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ciudadanos formularon cuestionamientos sobre el estado de diversas obras y proyectos municipales frente al alcalde de Catacaos, Jhonny Cruz Flores, junto a sus regidores y funcionarios. Durante la jornada, Carla Palacios, representante de la Asociación Catacaos Unidos, cuestionó la situación actual de la Alameda Lucas Cutivalú, señalando que el espacio se encuentra deteriorado, sin iluminación y en aparente estado de abandono, pese a que, según manifestó, se habría destinado aproximadamente 360 mil soles para su mejoramiento e iluminación. Palacios también pidió explicaciones sobre el proyecto de seguridad ciudadana, ejecutado bajo la modalidad de obras por impuestos y con una inversión aproximada de 12 millones de soles. Cuestionó que la empresa contratista no habría cumplido con el expediente técnico y preguntó por las medidas adoptadas por la municipalidad frente a esta situación. Ante los cuestionamientos, el gerente de Infraestructura de la Municipalidad de Catacaos, Aldo García, explicó que la recepción de los trabajos de la Alameda Lucas Cutivalú se realizó hasta el punto donde fue posible culminar la intervención, debido a una interferencia con la ejecución de una obra de alcantarillado de BPO.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/cuestionan-estado-de-obras-y-proyectos-en-catacaos/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Piura implementará medidas para proteger a turistas ante posibles impactos del fenómeno El Niño</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>La Red de Protección al Turista de Piura acordó implementar una serie de medidas para proteger el flujo de visitantes y reducir los posibles impactos del fenómeno El Niño en la región. La estrategia es encabezada por el Gobierno Regional de Piura, a través de la Dirección Regional de Comercio Exterior y Turismo (Dircetur). Entre las acciones previstas se encuentra un plan de respuesta sanitaria coordinado con la Dirección Regional de Salud (Diresa), que permitirá atender eventuales emergencias asociadas al fenómeno climático. También se implementará un sistema de comunicación oficial por provincias, con información diferenciada entre eventos climáticos estacionales y alertas nacionales. En materia de seguridad, se contempla la activación de brigadas de rescate rápido para atender emergencias y reforzar la protección de visitantes nacionales y extranjeros. Además, la Dirección de Aeródromos y Puertos y la Capitanía de Puerto participarán en la supervisión de las embarcaciones que operan en las zonas balnearias. La Policía de Turismo y la Policía Nacional del Perú incrementarán la vigilancia en muelles, corredores turísticos y principales atractivos de la región. Estas acciones se complementarán con medidas para fortalecer la seguridad marítima. Otro de los ejes será la formalización y certificación de los servicios turísticos. Para ello, se iniciará un proceso de capacitación dirigido a los gremios de transporte local y se entregarán distintivos oficiales a los operadores que cumplan con los estándares establecidos de seguridad y atención. Asimismo, se habilitará un directorio público, tanto físico como digital, con información de los operadores turísticos e intermediarios formales. La herramienta permitirá a los visitantes identificar los servicios disponibles en la región. La Red también acordó reforzar los mecanismos de fiscalización y recepción en los puntos de ingreso a Piura, con especial atención al mercado ecuatoriano, uno de los mercados emisores relevantes para el turismo receptivo de la región. La medida busca contribuir a mantener el flujo de visitantes procedentes de Ecuador y brindar condiciones de seguridad durante su ingreso y permanencia. Por su parte, la Diresa tendrá a su cargo la difusión de alertas sanitarias verificadas y la coordinación para garantizar atención médica ante eventuales contingencias relacionadas con el fenómeno El Niño. También se implementará un directorio de emergencias disponible las 24 horas y un canal digital oficial con información verificada por provincia. Finalmente, la Red de Protección al Turista acordó ampliar su convocatoria a las cámaras de comercio locales, municipalidades provinciales, la Junta de Fiscales Superiores y gremios privados. La finalidad es establecer mesas de trabajo técnicas para atender las necesidades específicas de cada zona turística de Piura.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-piura-implementara-medidas-para-proteger-a-turistas-ante-posibles-impactos-ultimas-noticia/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La zona más calurosa del Perú: emblemática localidad del norte rozó los 40 °C por El Niño Costero</t>
+          <t>Más de 123 mil habitantes de Talara en riesgo de desabastecimiento de agua potable por mal estado de línea de conducción</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>En Perú, diversos distritos de Lima y otras regiones experimentan altas temperaturas con presencia de humedad, lloviznas y fuertes vientos vinculados al Fenómeno El Niño. Así, en medio del impacto de este evento climático, el Centro Nacional de Estimación, Prevención y Reducción del Riesgo de Desastres (Cenepred) alertó que más de 20 millones de peruanos se encuentran en grave riesgo ante posibles desastres que podrían arrasar con viviendas y otras infraestructuras. En ese sentido, el Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que una zona costera del país registró una temperatura máxima y con una mayor exposición a la radiación ultravioleta que puso en alerta a tanto a las autoridades locales como a los pobladores. En el desarrollo de esta nota, te contamos mayores detalles al respecto. A través de sus plataformas oficiales, el Servicio Nacional de Meteorología e Hidrología del Perú anunció que la ciudad de Chulucanas, en Piura, registró el pasado 15 de septiembre temperaturas de hasta 38 °C, asociadas a la presencia del Fenómeno El Niño. De hecho, durante una jornada marcada por un calor extremo, otras regiones como Tumbes, Piura, Lambayeque, La Libertad, Áncash, Lima, Ica, Arequipa y Moquegua también registraron altas temperaturas. Así, de acuerdo con el Senamhi, las temperaturas diurnas elevadas se mantendrán hasta el sábado 19 de septiembre, con niveles de moderados a extremos de 29 °C y 36 °C en la costa y de moderados a fuertes en la sierra. A través del Decreto Supremo n.° 124-2026-PCM, publicado en el diario oficial El Peruano, el Poder Ejecutivo aprobó el estado de emergencia en 893 distritos del país ante el riesgo de intensas lluvias asociadas al Fenómeno El Niño. Esta medida, que tendrá una vigencia de 60 días calendario, responde a las evaluaciones del ENFEN, que proyectan un escenario con características similares a las registradas durante el fenómeno de 1997. En este contexto, se espera que las precipitaciones alcancen niveles críticos en la costa y la sierra entre noviembre y diciembre de este año. Por consiguiente, la declaratoria comprende a distritos de Amazonas, Áncash, Apurímac, Arequipa, Ayacucho, Cajamarca, Huancavelica, Huánuco, Ica, Junín, La Libertad, Lambayeque, Lima, Loreto, Madre de Dios, Moquegua, Pasco, Piura, San Martín, Tacna, Tumbes, Ucayali y Callao. Así, durante el periodo que dure la emergencia, las autoridades regionales y locales del país podrán implementar medidas destinadas a reducir los riesgos y atender eventuales daños. Según el decreto, estas acciones serán financiadas con sus propios presupuestos, sin contar con recursos adicionales provenientes del Tesoro Público, conforme comparte Perú 21.</t>
+          <t>La Contraloría General constató que la línea de conducción de agua potable Paita-Talara, así como el equipamiento electromecánico e infraestructura que se encuentra a lo largo de su recorrido, presenta evidente deterioro y otras deficiencias técnicas en su operación, lo cual ha sido omitido como trabajos de mantenimiento necesarios en el plan de gestión reactiva aprobado por la EPS Grau S.A. Dicha situación podría afectar el abastecimiento continuo de más de 123 000 habitantes de la provincia de Talara y se agravaría con la llegada de un eventual Fenómeno El Niño. Según el Informe de Visita de Control N° 020-2026-OCI/3470-SVC, (periodo de evaluación del 18 al 28 de agosto de 2026), la línea de conducción se extiende desde la Planta de Tratamiento de Agua Potable (PTAP) EI Arenal-Paita hasta la cámara de válvulas T-5 (Talara), con una longitud total de 56.30 km y un diámetro de 600 mm. El material de la tubería está constituido principalmente por hierro dúctil. A lo largo de su recorrido, esta línea integra la estación de bombeo n.° 1, estación de bombeo n.° 2 y la cámara de carga. En la estación de bombeo n.° 1, se verificó que la infraestructura carece de cerco perimétrico. Esta estación fue diseñada para operar con cuatro electrobombas, de las cuales solo dos permanecen operativas. Incluso, los equipos en servicio funcionan de forma continua desde 1996, año en que reemplazaron a las bombas instaladas en 1979. También se advirtió que los manómetros se encuentran inoperativos y los ejes de los equipos en funcionamiento no cuentan con protección, lo cual representa un riesgo para los operadores. Del mismo modo, el sistema instalado para la medición del nivel de la cisterna se encuentra inoperativo y actualmente se ejecuta esa acción de forma manual. Asimismo, se constató una fuga de agua en la tubería conectada al tanque antiariete (recipiente que protege las tuberías al absorber las ondas de presión y los golpes de energía), la cual está socavando la base de la estructura de la línea de conducción, así como el dado de concreto que le sirve de apoyo. Además, se observó que la válvula de la línea de descarga carece de volante de accionamiento, por lo que su manipulación se viene realizando de manera provisional mediante una llave. A ello se suman las fisuras y grietas en los muros y en la base de la sala de máquinas. Tampoco cuentan con grupo electrógeno o fuente de electrificación alterna. Incluso, durante el periodo lluvioso, deben colocar sacos de arena, a fin de que el agua que discurre de las partes altas no golpee el portón, situado en la parte posterior de la estación, y se corre el riesgo de afectar el equipamiento electromecánico. También, se observó que la línea de conducción, entre ambas estaciones, cuenta con un tramo junto al cual se ha construido una carretera, alterando el cauce natural de una quebrada, que se sitúa entre la vía y la línea de conducción. En tiempo de lluvias, al discurrir las aguas por la quebrada, se han ido socavando los soportes de concreto de la tubería, así como la cimentación de los dados de apoyo de la misma. En relación a la estación de bombeo n.° 2, se verificó que no posee cerco perimétrico y, al igual que la estación anterior, viene funcionando con dos electrobombas, una de las cuales tiene una antigüedad cercana a los 50 años. Respecto a la cámara de carga, una estructura de concreto de 1000 m3 de capacidad que al estar ubicada en el punto más alto de la línea debería brindar la presión necesaria para el abastecimiento, solo funciona como elemento de paso. Está abandonada, sin cerco ni escalera y tanto la válvula de ingreso y salida no cuenta con protección, estando actualmente expuestas a manipulaciones y riesgos sanitarios. Además, se identificó que en un drenaje de la línea existen diversas conexiones directas a la línea de distribución. La línea de conducción atraviesa diferentes quebradas como La Débora, mediante tubería subterránea de fibra de vidrio enterrada en el cauce, y El Acholado, a través de una estructura de pase aéreo. Una eventual activación de quebradas configura un escenario de alto riesgo para la línea de conducción, debido al deterioro de los soportes de la misma a lo largo de su recorrido, así como en la estructura del pase aéreo, la cual presenta un deterioro significativo e incluso la falta de elementos estructurales.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/respuestas/donde/la-zona-mas-calurosa-del-peru-emblematica-localidad-del-norte-rozo-los-40-c-por-el-nino-costero-tdpe-noticia/</t>
+          <t>https://eltiempo.pe/local/mas-de-123-mil-habitantes-de-talara-en-riesgo-de-desabastecimiento-de-agua-potable-por-mal-estado-de-linea-de-conduccion/</t>
         </is>
       </c>
     </row>
@@ -1092,121 +1140,167 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cura Mori exige obras de emergencia: responsabilizarán a autoridades de daños</t>
+          <t>Identifican 13 cuencas ciegas ante eventual Fenómeno El Niño</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ante la falta de obras de mitigación y el riesgo existente por posibles inundaciones, la Plataforma Distrital de Defensa Civil de Cura Mori, así como el Grupo de trabajo de gestión del riesgo de desastres y la sociedad civil emitieron un pronunciamiento público para denunciar que los trabajos de descolmatación y protección del río Piura continúan siendo insuficientes en puntos críticos del Bajo Piura, especialmente en Cura Mori. Advierten que los sectores de la margen izquierda del río Piura se encuentran en peligro debido al colapso y deterioro de las geobolsas instaladas anteriormente y a la falta de reforzamiento de las defensas ribereñas. Por ello exigen una intervención integral e inmediata para proteger a la población, “incluyendo descolmatación” en puntos críticos, reforzamiento de la margen izquierda; y ampliación y recuperación de la caja hidráulica del cauce, entre otras demandas. Finalmente advierten que de producirse daños y pérdidas humanas por la falta de atención oportuna, evaluarán el inicio de acciones legales contra las autoridades responsables.</t>
+          <t>La Universidad Nacional de Piura (UNP), a nivel interno y externo, ha trazado una línea de acciones sobre las medidas de prevención ante el anunciado fenómeno de El Niño, cuya posible magnitud extraordinaria ha sido advertida por organismos nacionales e internacionales. El rector encargado de la UNP, Adolfo Zeta Vite señaló que ya se realizó un diagnóstico interno y se identificó una situación de alta vulnerabilidad debido a la acumulación de agua dentro del campus. El diagnóstico permitió identificar 13 cuencas ciegas distribuidas en diferentes instalaciones, entre ellas las facultades de Administración, Contabilidad, Ingeniería Civil, Ingeniería Industrial y Medicina, además del rectorado, Idepunp, la Escuela Tecnológica, el Hospital Universitario y locales de posgrado y Responsabilidad Social Universitaria. FALTA DE DRENAJE Uno de los principales problemas es la falta de drenaje adecuado hacia el río Piura, situación que se habría agravado con la construcción de la carretera. Según explicó la autoridad universitaria, antes el agua podía discurrir hacia el río o ser bombeada con mayor facilidad, pero actualmente existe riesgo de acumulación de aguas dentro del campus. La autoridad universitaria detalló que también se gestiona proteger laboratorios e infraestructura valorizada en millones de soles. Entre las alternativas planteadas figura la construcción de pozas de percolación para enfrentar la acumulación de agua; sin embargo, señala que existen limitaciones presupuestales debido a que los recursos de emergencia gestionados ante el Ministerio de Educación están destinados principalmente a servicios de mitigación y no a nuevas obras. AJUSTES EN PRESUPUESTO Ante esta situación, la universidad realiza ajustes internos a su presupuesto y gestiona apoyo ante el Minedu, el Ministerio de Economía y Finanzas (MEF) y representantes del Congreso. La comunidad universitaria está conformada por aproximadamente 15 mil estudiantes y 500 docentes, quienes podrían verse afectados si las lluvias dificultan el acceso al campus o interrumpen las actividades académicas. Además, se evalúa la implementación de clases virtuales si las condiciones impiden continuar con la enseñanza presencial, aunque esta alternativa también enfrenta dificultades por problemas de energía, conectividad y acceso a equipos. BRIGADAS Adolfo Zeta, pese a las dificultades presupuestarias, analiza asimismo la conformación de brigadas de apoyo a poblaciones vulnerables, con participación de estudiantes y profesionales de Medicina, Ingeniería Civil y Arquitectura, los mismos que participarían activamente en algunas emergencias que se puedan presentar por la caída de intensas lluvias en la región.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/cura-mori-exige-obras-de-emergencia-responsabilizaran-a-autoridades-de-danos/</t>
+          <t>https://eltiempo.pe/local/identifican-13-cuencas-ciegas-ante-eventual-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Niño: mar frente a Paita registra hasta 7 °C más de temperatura de lo normal</t>
+          <t>ANGR advierte paralización de proyectos por recorte presupuestal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Las consecuencias de El Fenómeno de El Niño ya se sienten en Piura. La temperatura del mar frente a Paita continúa por encima de sus valores normales y genera preocupación por el escenario de lluvias que podría enfrentar el norte del país durante el próximo verano. Rodolfo Rodríguez Arisméndiz, especialista de la Universidad de Piura (UDEP) y director de la Estación Científica Ramón Mugica, informó a la Agencia Andina que actualmente el mar frente a Paita registra entre 24 °C y 25 °C, cuando lo habitual para esta época del año es encontrar temperaturas de entre 17 °C y 18 °C. Esto representa una anomalía positiva de entre 6 y 7 grados, una diferencia considerable que, de mantenerse, podría tener efectos sobre las condiciones climáticas de los próximos meses. Según explicó el especialista, cuando la temperatura del mar supera los 25 °C se genera un escenario más favorable para la formación de lluvias, aunque la ocurrencia e intensidad de las precipitaciones también depende de otros factores atmosféricos. El punto de preocupación está en que estas temperaturas elevadas se están registrando todavía durante el invierno. Rodríguez advirtió que, con la llegada del verano, el calentamiento propio de la temporada podría sumarse a las actuales condiciones del mar y elevar aún más las anomalías. “Probablemente tengamos lluvias fuertes, principalmente en los meses del verano del 2027”, señaló. El especialista explicó que el comportamiento actual debe ser tomado como una señal de alerta y seguimiento frente a un posible escenario de lluvias intensas asociado a las condiciones cálidas del mar propias del desarrollo del Fenómeno El Niño. Rodríguez consideró que las autoridades ya no deberían concentrarse únicamente en el diagnóstico, sino avanzar en medidas de prevención y mitigación a los efectos adversos de intensas lluvias. En su opinión, la preparación debe involucrar acciones a nivel vecinal, municipal, Gobierno Regional y Gobierno Nacional, con acciones destinadas a reducir los posibles impactos de un periodo lluvioso intenso. La preocupación también se refleja en la sensación térmica que experimenta la población. Piura viene atravesando un invierno inusualmente cálido, con temperaturas que generan una sensación más propia de los meses de verano. Sostuvo que las próximas semanas serán importantes para conocer cómo evoluciona la temperatura del mar y, con ello, evaluar con mayor precisión el escenario que podría presentarse durante el verano de 2027.</t>
+          <t>El presidente de la Asamblea Nacional de Gobiernos Regionales (ANGR) y gobernador regional de Piura, Luis Neyra, advirtió que el recorte del 20% en el presupuesto inicial para el 2027 pone en riesgo la continuidad de proyectos de infraestructura a nivel nacional. La postura fue expresada tras la reunión de trabajo sostenida entre el consejo directivo de la ANGR, el presidente del Consejo de Ministros, Luis Galarreta, y el titular del Ministerio de Economía y Finanzas, Elmer Cuba. El titular de la ANGR exigió al Ejecutivo restituir los fondos asignados a los gobiernos regionales, destacando que en los últimos 4 años las regiones lideraron la eficiencia en ejecución de inversiones, superando al gobierno central y a los municipios. «Dejamos en claro que cualquier proyecto que se paralice el próximo año, la culpa no será de estas gestiones, sino de la falta de presupuesto que se dejó de otorgar por el Ministerio de Economía», afirmó Neyra. Defensa de fondos para las autoridades electas en octubre El representante regional remarcó que las autoridades en funciones deben asegurar los recursos para las gestiones que serán elegidas en los comicios del 4 de octubre, o en una eventual segunda vuelta, evitando el incremento de obras paralizadas. Las regiones demandan que el Ministerio de Economía y Finanzas respete el principio de presupuesto por resultados y mantenga, como mínimo, el Presupuesto Inicial de Apertura otorgado en ejercicios anteriores.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://gestion.pe/peru/el-nino-en-piura-mar-frente-a-paita-registra-hasta-7-c-mas-de-temperatura-de-lo-normal-noticia/</t>
+          <t>https://eltiempo.pe/local/angr-advierte-paralizacion-de-proyectos-por-recorte-presupuestal/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piura es la tercera región del país con más violencia escolar con 135 casos</t>
+          <t>El Niño: ANA fortalece acciones para proteger la faja marginal de laguna Coscomba en Piura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>La presunta agresión sexual que habría sufrido un escolar de 16 años en un colegio de Lima, con implicación de diez compañeros del quinto de secundaria, ha encendido las alertas en diversas regiones: Piura, por ejemplo, se encuentra entre las tres regiones de todo el país con más casos de violencia sexual y escolar. El diputado por Piura, Miguel Huamán Cornejo, informó que entre enero a agosto de 2026, según el reporte del sistema SíseVe del Ministerio de Educación, en Piura se han registrado 692 reportes de violencia escolar, ubicándola en el tercer lugar nacional, después de Lima Metropolitana y Arequipa. El diputado señala que estas cifras corresponden a reportes registrados en la plataforma y no necesariamente equivalen al mismo número de víctimas o hechos distintos. Advierte también sobre los 135 reportes de violencia sexual escolar registrados en Piura durante el mismo periodo, de acuerdo con las cifras proporcionadas. “135 reportes de violencia sexual contra escolares no pueden convertirse en una estadística más. Detrás de cada denuncia existe un menor que necesita protección y una respuesta inmediata del Estado. Tenemos que saber dónde están ocurriendo estos hechos, qué protocolos se están aplicando y si realmente están funcionando”, señaló. PIDE INFORMES Ante esta situación, el diputado anunció que solicitará información oficial a la Dirección Regional de Educación y a las UGEL Piura sobre las instituciones educativas con mayor incidencia de reportes, los protocolos activados, las medidas de prevención implementadas y el seguimiento de los casos. Asimismo, planteó fortalecer la articulación entre el Ministerio de Educación (Minedu), Ministerio de Salud (Minsa) y Ministerio de la Mujer y Poblaciones Vulnerables (MIMP)para reforzar la prevención y atención de la violencia contra niños y adolescentes. “Lo ocurrido en Lima podría estar ocurriendo también en algún colegio de Piura sin que todavía lo sepamos. Ningún estudiante debe sentirse desprotegido dentro de una institución educativa. Los colegios tienen que ser espacios seguros, no lugares donde el miedo y el silencio terminen protegiendo la violencia”, enfatizó Miguel Huamán Cornejo.</t>
+          <t>El encuentro se desarrolló en el marco de la Resolución Directoral N.° 0046-2026-ANA-AAA.JZ, que aprueba el estudio de delimitación de la faja marginal de la laguna Coscomba, ubicada en el distrito, provincia y departamento de Piura.
+La medida busca contribuir a la protección de la población y prevenir afectaciones a viviendas y bienes ubicados en zonas expuestas, especialmente ante eventuales escenarios asociados al Fenómeno El Niño.
+En la reunión participaron representantes de la Municipalidad Provincial de Piura, la Superintendencia Nacional de los Registros Públicos (Sunarp), la Fiscalía de Prevención del Delito, el Organismo de Formalización de la Propiedad Informal (Cofopri) y el Centro Nacional de Estimación, Prevención y Reducción del Riesgo de Desastres (Cenepred).
+Entre los principales acuerdos, la ALA Medio y Bajo Piura solicitará a Sunarp la incorporación del polígono de la faja marginal de la laguna Coscomba en su base gráfica registral, de acuerdo con la delimitación aprobada por la ANA.
+Asimismo, trasladará a la Municipalidad Provincial de Piura la conducción de las acciones destinadas a preservar la intangibilidad de esta zona, conforme a lo establecido en la resolución directoral.
+Por su parte, la Municipalidad Provincial de Piura solicitará a la Sunarp ampliar el análisis jurídico de los derechos inscritos que se encuentren comprendidos en el área del cuerpo de agua y la faja marginal.
+También elaborará, de manera coordinada con las instituciones participantes, la ficha definitiva para identificar las viviendas ubicadas dentro de la faja marginal.
+La ANA continuará impulsando el trabajo articulado entre las entidades competentes para prevenir la ocupación de zonas vulnerables y fortalecer las acciones de prevención y gestión del riesgo en el ámbito de la laguna Coscomba, contribuyendo así a la seguridad de la población y la protección de este espacio natural.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/reportan-135-casos-de-violencia-sexual-escolar-en-piura/</t>
+          <t>https://andina.pe/agencia/noticia-el-nino-ana-fortalece-acciones-para-proteger-faja-marginal-laguna-coscomba-piura-1092476.aspx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Se realiza Simulacro de incendio forestal en Santa Julia</t>
+          <t>Caso Liceo Naval: Pronacej ejecutará medidas que determine el Poder Judicial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>La Oficina Regional de Seguridad y Defensa Nacional anunció que hoy se realizará el segundo simulacro regional de incendio forestal a partir de las 11:00 en Santa Julia. Informaron que este simulacro tiene como propósito sensibilizar a la población que vive en sectores aledaños a la zona cero, respecto al tratamiento y quema de basura y la contaminación que genera al ecosistema. Cabe señalar que la ejecución de este ejercicio está normado por la resolución N° 001-2025 de la Secretaría de Gestión del Riesgo de Desastres de la PCM, que establece que durante los años 2025 – 2027, los gobiernos regionales deben programar dos simulacros regionales para la ocurrencia de un incendio forestal. ECOSISTEMA FRÁGIL Los humedales de Santa Julia, ubicados en el distrito Veintiséis de Octubre, son un ecosistema costero frágil caracterizado por la presencia de uno o varios espejos de agua, abundante vegetación, así como una alta diversidad de aves. Se estima que un incendio en esta zona afectaría la flora, la fauna el medio ambiente así como a las familias que han levantado sus viviendas en las zonas adyacentes.</t>
+          <t>“ Nosotros somos receptores y vamos a hacer cumplir lo que el juez dispone ”, señaló al explicar que la medida socioeducativa es determinada exclusivamente por el Poder Judicial, mientras que el Pronacej tiene a su cargo la ejecución y el desarrollo de las intervenciones destinadas a la rehabilitación de los adolescentes.
+Lee también: Caso Liceo Naval: dictan 4 meses de internamiento preventivo para 6 escolares denunciados Vega precisó que los seis adolescentes que ingresaron recientemente al Centro Juvenil de Diagnóstico y Rehabilitación de Lima, conocido como Maranguita fueron incorporados al Programa de Nivel 1 y serán evaluados por los equipos técnicos de los centros juveniles, conformados por psicólogos, trabajadores sociales y abogados.
+Añadió que, además de los certificados emitidos por Medicina Legal, los adolescentes pasan por una evaluación médica clínica propia del centro juvenil.
+“ El día de hoy, a las 8:15 aproximadamente, los jóvenes, después de tomar el desayuno como todos los jóvenes que se tienen en el centro juvenil, pasaron la evaluación médica propia del centro juvenil ”, indicó.
+El director ejecutivo del Pronacej explicó que los adolescentes son sometidos a una evaluación integral y permanente, cuyos resultados permitirán determinar si corresponde su permanencia en el programa asignado o su eventual traslado a otro centro juvenil.
+“ De estos jóvenes que han llegado ayer en un número de nueve, aún no han sido evaluados.
+Los van a evaluar los equipos técnicos el día lunes y, en base a ello, en una constante evaluación determinarán a qué programa, de qué nivel van a ser trasladados ”, señaló.
+Precisó que, normativamente, un adolescente puede ser trasladado a otro centro juvenil, pero esta decisión dependerá de las causales previstas en la normativa y será adoptada por el equipo técnico y el director del establecimiento.
+Vega aclaró, además, que el anexo 2 del penal de Ancón está destinado exclusivamente a infractores que ya son mayores de edad y que representan un nivel de riesgo alto dentro del sistema juvenil.
+Lee también: Violencia entre adolescentes puede dejar huellas emocionales: cómo prevenir y actuar Visitas familiares Respecto al régimen de visitas, informó que la primera visita de los familiares de los adolescentes que ingresaron recientemente se realizará durante la primera semana de octubre, de acuerdo con la directiva vigente .
+El funcionario indicó que las visitas familiares están previstas dos veces al mes y que los equipos técnicos se comunicarán directamente con los parientes de los nuevos internos para explicarles el procedimiento.
+“ Los trabajadores sociales, el equipo técnico, el día lunes o martes deben estar comunicándose con la familia de los jóvenes que han llegado ”, dijo.
+Vega señaló que este procedimiento es el mismo que se aplica en los centros juveniles de Lima, Chiclayo, Piura, Trujillo, Huancayo, Cusco y Pucallpa.
+Asimismo, explicó que la defensa legal de los adolescentes constituye un derecho y puede acudir al centro juvenil previa coordinación con la dirección.
+En otro momento, manifestó que los menores cumplen su medida socioeducativa en los centros juveniles hasta el plazo establecido por el Poder Judicial, incluso si durante ese periodo alcanzan la mayoría de edad.
+“ Los jóvenes cumplen su medida socioeducativa o sentencia, como lo quieran llamar, hasta el último día que ha determinado el juez en un centro juvenil.
+Es decir, no son trasladados a un penal.
+Actualmente albergamos a 2059 infractores ”, precisó.
+De esta manera, agregó, si un juez determina una medida de cuatro, cinco u ocho años, esta se cumplirá en el centro juvenil conforme a lo dispuesto judicialmente.
+Lee también: Caso Liceo Naval: prohíben a denunciados usar redes sociales contra agraviado Respecto a la posibilidad de que algunos jóvenes mayores de edad sean trasladados a establecimientos penitenciarios, Vega señaló que actualmente la normativa establece su permanencia en los centros juveniles, aunque consideró necesaria una modificación del Código de Responsabilidad Penal del Adolescente.
+“ Hoy tenemos jóvenes de 25, 26 y de 27 años con niños de 14 que deberían tener un tratamiento distinto en base a su nivel de riesgo ”, sostuvo.
+Explicó que el Pronacej plantea que, en el futuro, aquellos jóvenes mayores de edad que presenten un nivel de riesgo alto y considerando la infracción cometida puedan ser trasladados a un penal, si la legislación es modificada.
+Oportunidades laborales Como parte de este proceso, Vega informó que algunos jóvenes que cumplieron medidas socioeducativas han logrado incorporarse al mercado laboral.
+“ Nosotros tenemos jóvenes incluso laborando en el Pronacej en la sede central en Lince, jóvenes laborando en el Ministerio de Justicia, en las tiendas OXXO, en las tiendas Adidas, en los grifos ”, señaló.
+Agregó que la institución viene cerrando un convenio con Kentucky para que los jóvenes puedan trabajar con autorización judicial y regresar posteriormente al centro juvenil para continuar cumpliendo su medida socioeducativa.
+Sin embargo, consideró que todavía son pocos los jóvenes que alcanzan este tipo de oportunidades y planteó la necesidad de una mayor participación del sector privado y de modificar la legislación para establecer tratamientos diferenciados de acuerdo con los niveles de riesgo.
+Lee también: Más de 11 mil casos de violencia escolar en lo que va del 2026: cifras por tipo y región Prevención Finalmente, sostuvo que, además del trabajo de rehabilitación y reinserción que desarrolla la institución, es necesario fortalecer la prevención para evitar que más adolescentes ingresen al sistema de justicia juvenil.
+“ Pienso que debemos fortalecer la prevención primaria, porque nosotros aquí hacemos terciaria.
+Pero la prevención primaria es para aquellos jóvenes que están en la calle, y que no queremos que estén aquí o en un penal ”, concluyó.
+Más en Andina : ?? Caso Liceo Naval: el Poder Judicial dictó medidas de protección para resguardar a la presunta víctima durante las investigaciones.
+Los adolescentes denunciados tienen prohibido utilizar plataformas digitales y redes sociales contra el agraviado y deberán recibir terapias… pic.twitter.com/OSlKDMZTQD — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/se-realiza-simulacro-de-incendio-forestal-en-santa-julia/</t>
+          <t>https://andina.pe/agencia/noticia-caso-liceo-naval-pronacej-ejecutara-medidas-determine-poder-judicial-1092487.aspx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sicarios en moto matan de 6 balazos a un ‘gota-a-gota’ en Veintiséis de Octubre</t>
+          <t>El Niño: Minsa prepara a más de 100 profesionales de la salud del norte frente al dengue</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sicarios motorizados, a plena luz del día, volvieron a desatar terror en las calles, luego de asesinar de seis balazos a un cobrador extranjero del “gota-a-gota”. Los gatilleros tras ver caer a su objetivo se dieron a la fuga en una motocicleta. El homicidio ocurrió cerca de las tres de la tarde de ayer en el asentamiento Rosa de Guadalupe, Mz. K, en Veintiséis de Octubre, cuando Julián Andrés Agudelo Rivera, de 22 años, de nacionalidad colombiana, se había estacionado, frente a una vivienda para realizar una cobranza, llegó una motocicleta. Lo acribillan El sujeto que iba como pasajero, con arma de fuego en mano, le descargó seis tiros en el pecho y espalda, que acabaron con la vida en contados minutos con el ciudadano colombiano. El estruendo de los disparos alarmó a los vecinos, los mismos que al salir a la calle encontraron el cuerpo del extranjero. Se dice que los gatilleros merodearon por la zona por varios minutos a la espera del cobrador a fin de perpetrar el feroz ataque. Todo fue ran rápido, que el cobrador dekl “gota-a-gota” no tuvo tiempo para ponerse a buen recaudo. Llega la Policía Peritos de la Oficina de Criminalística (Oficri) de la Divincri Piura y fiscal provincial Imazuma Córdova Reyes de la Fiscalía Provincial de Turno de Piura, alertados de lo ocurrido, llegaron hasta la zona para la diligencia del levantamiento del cuerpo y traslado a la morgue de Piura para la necropsia de ley. Aunque la Policía realizó un intenso operativo en busca de los gatilleros no fue posible su ubicación y captura. Se presume que el móvil del ataque sería por la pugna por el control de los préstamos infornales en la zona.</t>
+          <t>A través de la Dirección General de Intervenciones Estratégicas en Salud Pública (Dgiesp), equipos especializados del Minsa se desplazaron simultáneamente a estas cuatro regiones para capacitar a médicos y profesionales de enfermería en la detección temprana de signos de alarma, toma de decisiones clínicas, referencia oportuna y manejo adecuado de pacientes con dengue.
+La capacitación incluyó simulaciones de deterioro clínico, diagnóstico diferencial entre dengue y leptospirosis, manejo de pacientes con comorbilidades, organización del triaje, entrenamiento en establecimientos de salud y uso de Telesalud.
+Prepararnos antes para proteger vidas En representación del ministro de Salud, Luis Dyer Fernández, la viceministra de Salud Pública, María Cuba Fuentes, clausuró la jornada y destacó que el objetivo es fortalecer anticipadamente la capacidad de respuesta de los servicios de salud.
+“ Hemos decidido anticiparnos.
+El Minsa está dando un paso adelante, preparando desde ahora a nuestros profesionales de la salud para responder oportunamente ante un posible incremento de casos de dengue.
+Queremos reconocer tempranamente los signos de alarma, actuar antes de que el paciente se agrave y evitar muertes prevenibles.
+Esta preparación comienza en las regiones del norte y avanzará progresivamente para fortalecer nuestra capacidad de respuesta” , señaló la viceministra de Salud Pública, María Cuba Fuentes.
+Los profesionales capacitados tendrán, además, la misión de replicar los conocimientos adquiridos en sus establecimientos y regiones, permitiendo ampliar las capacidades del personal de salud para responder oportunamente frente al dengue.
+Estrategia continuará ampliándose La intervención desarrollada en Tumbes, Piura, Lambayeque y La Libertad constituye un primer paso para la conformación progresiva de la Red Nacional de Referentes Clínicos de Dengue, iniciativa que busca fortalecer la respuesta clínica descentralizada y extender estas capacidades de manera progresiva a otras regiones del país.
+De esta manera, el Minsa avanza en la preparación del sistema de salud frente al dengue, priorizando inicialmente las regiones del norte y fortaleciendo las capacidades del personal para detectar oportunamente los casos de riesgo, brindar una atención adecuada y prevenir complicaciones y muertes.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sicarios-en-moto-matan-de-6-balazos-a-un-gota-a-gota-en-veintiseis-de-octubre/</t>
+          <t>https://andina.pe/agencia/noticia-el-nino-minsa-prepara-a-mas-100-profesionales-de-salud-del-norte-frente-al-dengue-1092494.aspx</t>
         </is>
       </c>
     </row>
@@ -1217,28 +1311,28 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Detienen a un docente: lo acusan de presuntos tocamientos indebidos</t>
+          <t>¡Alerta en Piura! Bandas buscan infiltrarse en la Policía</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Un docente fue aprehendido por agentes de la comisaría de Talara Baja luego de ser denunciado por presuntos tocamientos indebidos contra una escolar del nivel secundario. El profesor fue conducido a la delegación donde es investigado en presencia de un representante del Ministerio Público. La intervención policial ocurrió cerca de las 11:30 de la mañana de ayer, luego que una madre de familia de la institución educativa Santa Rosa de Lima denunciara al profesor identificado con las iniciales A. V. S., de haber realizado tocamientos a su hija de 16 años cuando realizaba sus prácticas dentro del aula. NARRA LO SUCEDIDO La madre de la alumna, en el momento de sentar la denuncia, contó a los investigadores que su hija, quien cursa el cuarto año del nivel secundario en la conocida institución educativa talareña, le confesó lo ocurrido. También declaró que, tras informar del supuesto hecho a las autoridades de la escuela, el docente fue separado de inmediato de sus labores, emitiendo la dirección la advertencia, a través de un informe, a la UGEL Talara, para que tome cartas en el asunto. SINDICATO SEÑALA QUE ES INOCENTE Tras la intervención y las primeras diligencias, se tuvo conocimiento que el sindicado había sostenido en todo momento su inocencia ante las autoridades policiales y del Ministerio Público, indicando desconocer el por qué la escolar y la madre de familia lo habían denunciado, por el delito mencionado.</t>
+          <t>Alerta en Piura. El crimen organizado estaría intentando dar un paso más allá de las calles para penetrar una de las instituciones encargadas de combatirlo. Expertos en seguridad advirtieron que organizaciones criminales buscarían infiltrarse en la Policía Nacional desde las escuelas de formación, mediante la captación de jóvenes que posteriormente podrían convertirse en agentes al servicio de estructuras delictivas. La advertencia cobra especial importancia para Piura, una de las regiones del norte donde la criminalidad mantiene en alerta a las autoridades. El especialista en seguridad ciudadana Pedro Yaranga, explicó que el mecanismo de captación podría comenzar desde la etapa escolar. Según señaló, las estructuras criminales podrían financiar los estudios de menores y acompañar su preparación hasta que culminen la secundaria. Posteriormente, de acuerdo con su versión, recurrirían al pago de coimas para facilitar el ingreso de estos jóvenes a las escuelas de formación de la Policía Nacional. Una vez convertidos en suboficiales, podrían terminar trabajando para las organizaciones que financiaron su preparación. El objetivo sería contar con personal entrenado dentro de la institución policial, capaz de proteger los negocios ilícitos de las bandas y, eventualmente, proporcionar información que permita anticiparse a las acciones de las fuerzas del orden. En ese sentido, las bandas criminales no solo reclutan sicarios para ejecutar ataques, sino también reclutan policías, los forman. Yaranga, docente en Ciencia Política, consultor y analista en seguridad integral y gestión de riesgos, sostuvo que Trujillo se ha convertido en uno de los principales focos de criminalidad del país, pero advirtió que la problemática también alcanza a Tumbes y Piura. En ese contexto, llamó la atención sobre las escuelas policiales existentes en el norte y planteó la necesidad de revisar cuidadosamente quiénes ingresan a estos centros de formación. La preocupación no se limita al proceso de admisión. Una persona vinculada con una organización criminal que consiga convertirse en policía podría acceder a conocimientos, entrenamiento e información sensible durante su carrera. De acuerdo con el planteamiento de Yaranga, un agente infiltrado podría convertirse en una pieza estratégica para una banda, al conocer movimientos policiales, operativos, investigaciones y acciones de inteligencia. Esto permitiría a las estructuras criminales anticiparse o evadir los golpes de las autoridades. INFORMACIÓN POLICIAL La alerta también fue planteada por el exministro del Interior Ricardo Valdés, quien sostuvo que las organizaciones criminales muchas veces buscan infiltrarse en la Policía Nacional precisamente para asegurar información policial. Valdés señaló que esta estrategia no correspondería únicamente a una determinada banda, sino que podría ser utilizada por distintas organizaciones. Mencionó, entre otras, a “Los Pulpos” y “La Jauría”, aunque remarcó que se trata de un problema de alcance más amplio. Según el exministro, una de las vías para conseguirlo sería incorporar a las escuelas policiales a jóvenes, familiares o personas relacionadas con organizaciones criminales. La advertencia representa un nuevo desafío para Piura, donde la lucha contra homicidios, extorsiones y otras manifestaciones del crimen organizado exige reforzar la capacidad de respuesta de la Policía. FORTALECER FILTROS Para los especialistas, resulta fundamental fortalecer los filtros de ingreso, los controles durante la formación y los mecanismos de inteligencia interna. La prevención, sostienen, debe comenzar antes de que los futuros agentes reciban el uniforme y tengan acceso a información policial. El riesgo, finalmente, no estaría únicamente en las calles. Las bandas criminales buscarían entrar a las instituciones para convertir a futuros agentes del orden en piezas estratégicas de sus propias estructuras. Crimen organizado financiaría a postulantes a Policía El crimen organizado estaría encontrando una peligrosa puerta de entrada a la Policía Nacional: financiar a jóvenes de escasos recursos para que puedan ingresar a las escuelas de formación de suboficiales y, posteriormente, convertirse en agentes con acceso a información privilegiada. La advertencia fue formulada por el exviceministro del Interior Julio Corcuera, quien sostuvo que organizaciones criminales habrían comenzado a colocar a jóvenes vinculados con sus estructuras dentro de las escuelas policiales. Según explicó, el mecanismo aprovecharía las dificultades económicas que enfrentan algunas familias para cubrir los gastos exigidos durante la formación. Corcuera señaló que las denominadas garantías para los estudiantes pueden alcanzar entre 7 mil y 10 mil soles, monto que representaría una barrera para muchos postulantes provenientes de sectores populares. En ese escenario, las organizaciones criminales podrían asumir esos costos con la finalidad de obtener, a futuro, favores o información desde el interior de la institución. El exfuncionario consideró urgente reforzar los filtros de ingreso y revisar exhaustivamente los antecedentes familiares y las relaciones de los postulantes. También advirtió sobre policías cuyos bienes no guardarían correspondencia con sus ingresos y mencionó como ejemplo al agente Orlando Santos, a quien atribuyó la adquisición de costosas camionetas pese a percibir unos 2,900 soles mensuales. Este señalamiento requiere ser acreditado mediante una investigación oficial. Para Corcuera, no se trata de toda la Policía, sino de un sector que podría estar siendo contaminado por el poder económico del crimen organizado. La alerta cobra mayor importancia ante la expansión del crimen transnacional en Piura y Tumbes. “Hay una contaminación de la presencia del crimen transnacional organizado en el Perú. Un país tan lejano como Albania tiene presencia en Piura y Tumbes; como operan con narcotráfico en Ecuador lavan su dinero en Tumbes y Piura”, refirió.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/detienen-a-un-docente-lo-acusan-de-presuntos-tocamientos-indebidos/</t>
+          <t>https://eltiempo.pe/local/alerta-en-piura-bandas-buscan-infiltrarse-en-la-policia/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1246,24 +1340,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pronied continuará obra del colegio ‘Salaverry’ en Sullana</t>
+          <t>Ministro Vinelli: Gobierno atiende 536 puntos críticos del país ante fenómeno El Niño</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>El Gobierno Regional de Piura ya no tendrá a su cargo la culminación de la obra del colegio emblemático “Carlos Augusto Salaverry”, como se había anunciado meses atrás. El Programa Nacional de Infraestructura Educativa (Pronied) del Ministerio de Educación, decidió continuar el proyecto y será esta entidad la que culmine el proceso para hacer realidad la esperada infraestructura educativa, la misma que lleva 11 años El diputado sullanero Eduardo Castillo señaló que, tras una reunión con representantes de Pronied, se confirmó que la obra será ejecutada bajo la modalidad de diseño-construcción. Según explicó, actualmente se encuentra en la elaboración final de los términos de referencia, documento que permitirá avanzar con la convocatoria para la elaboración del nuevo expediente técnico y su posterior ejecución. Este cambio se produce luego de los inconvenientes registrados con el proceso anterior. La empresa que tenía a su cargo la elaboración del expediente técnico no cumplió con los plazos establecidos de los entregables, además éstos registraban observaciones, por lo que se tomó la decisión de resolver el contrato. El proyecto se deberá encaminar el evitar que la obra continúe paralizada.</t>
+          <t>Las labores son ejecutadas por el Ministerio de Desarrollo Agrario y Riego (Midagri), a través de la Autoridad Nacional del Agua (ANA), con maquinaria pesada que opera en doble turno (de día y de noche).
+Respecto al canal Chutuque, en la región Piura, señaló que se proyecta intervenir entre cinco y seis kilómetros con participación de los sectores público y privado.
+Esta medida permitirá evitar que el agua se represe y afecte a las zonas aledañas.
+Informó que, debido a un anuncio de lluvias en la zona costera, la Autoridad Nacional del Agua llegará este lunes a la región Tumbes para supervisar las acciones de descolmatación.
+Balance frente al FEN Durante su visita a Piura, el titular del Midagri también participó en la Segunda Sesión No Ordinaria Desconcentrada de la Comisión de Asuntos de Desarrollo Productivo, Energía y Minas, Infraestructura y Trabajo del Senado de la República, que preside el senador Daniel Barragán Coloma.
+En su exposición, Vinelli presentó un balance de las medidas adoptadas por el Gobierno frente al FEN.
+Informó que se han distribuido alrededor de 1,800 millones de soles y que el Ejecutivo atiende 536 puntos críticos a escala nacional.
+Detalló que el Instituto Nacional de Defensa Civil (Indeci) cuenta con 6,200 toneladas de ayuda humanitaria y proyecta alcanzar las 7,000 toneladas para la atención de las emergencias en el país.
+Asimismo, indicó que el Gobierno dispone de maquinaria, motobombas, puentes Bailey, aeronaves, embarcaciones y 13,400 efectivos de las Fuerzas Armadas preparados para responder ante una eventual emergencia.
+Por último, resaltó el mecanismo de Servicios por Impuestos como una herramienta para incorporar recursos privados a las medidas de preparación frente al fenómeno El Niño.
+Más en Andina: ?????? Virgilio Martínez recibió el Andorra Taste Award 2026 por su trabajo en favor de la biodiversidad peruana y una propuesta que conecta territorio, productos nativos, conocimientos ancestrales y comunidades.
+?? https://t.co/IBTubyPfkP pic.twitter.com/gOe894WSBw — Agencia Andina (@Agencia_Andina) September 19, 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/pronied-continuara-obra-del-colegio-salaverry-en-sullana/</t>
+          <t>https://andina.pe/agencia/noticia-ministro-vinelli-gobierno-atiende-536-puntos-criticos-del-pais-ante-fenomeno-nino-1092429.aspx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1271,217 +1376,284 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piura activa medidas de protección al turista ante posibles impactos del fenómeno El Niño</t>
+          <t>Misa del papa León XIV en Pimentel: delimitan áreas para trabajos de acondicionamiento</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Piura prepara una serie de medidas para proteger a los visitantes nacionales y extranjeros ante los posibles impactos del fenómeno El Niño. La estrategia fue acordada por la Red de Protección al Turista , a través de la Dirección Regional de Comercio Exterior y Turismo (Dircetur). El plan contempla acciones relacionadas con seguridad, atención sanitaria, comunicación de alertas, supervisión de embarcaciones, formalización de operadores y vigilancia en los principales puntos turísticos de la región. Según el Gobierno Regional de Piura, las medidas buscan reducir los riesgos que podrían afectar la actividad turística y establecer mecanismos de respuesta ante eventuales emergencias vinculadas a las condiciones climáticas. Piura prepara un plan de protección para los turistas Uno de los principales acuerdos consiste en implementar un plan de respuesta sanitaria coordinado con la Dirección Regional de Salud (Diresa). Esta medida permitirá establecer mecanismos de atención ante posibles emergencias que puedan presentarse durante episodios relacionados con el fenómeno El Niño. Para ello, se plantea reforzar la coordinación entre las instituciones responsables de la salud y los organismos vinculados con el turismo. El objetivo es que los visitantes puedan contar con atención ante una eventual contingencia durante su permanencia en la región. La estrategia también considera la creación de un sistema de comunicación oficial por provincias . La información será diferenciada para evitar confusiones entre los eventos climáticos propios de cada temporada y las alertas nacionales emitidas por las autoridades competentes. El Senamhi es una de las entidades oficiales que emite información y alertas relacionadas con las condiciones meteorológicas e hidrológicas del país. Seguridad para visitantes nacionales y extranjeros Dentro de las medidas previstas se encuentra la activación de brigadas de rescate rápido para atender situaciones de emergencia. Estas unidades tendrán como finalidad responder ante posibles incidentes que involucren a turistas en diferentes zonas de la región. La seguridad también será reforzada en los espacios vinculados con el turismo marítimo. La Dirección de Aeródromos y Puertos y la Capitanía de Puerto participarán en la supervisión de las embarcaciones que operan en las principales zonas balnearias de Piura . De acuerdo con lo planteado por la Red de Protección al Turista, esta vigilancia permitirá verificar las condiciones de operación de las embarcaciones y contribuir a reducir riesgos para quienes utilizan estos servicios. A estas acciones se sumará la participación de la Policía de Turismo y la Policía Nacional , que incrementarán la vigilancia en muelles, corredores turísticos y principales atractivos de la región. ¿Qué zonas turísticas tendrán mayor vigilancia? La vigilancia estará enfocada principalmente en espacios con concentración de visitantes, como muelles, corredores turísticos y atractivos de la región. También se contempla reforzar los controles en puntos relacionados con el ingreso y desplazamiento de turistas. La finalidad es que las instituciones involucradas puedan responder con mayor rapidez ante cualquier emergencia y brindar orientación a los visitantes. Piura busca aumentar la formalización de los operadores turísticos Otro de los componentes del plan está relacionado con la formalización y certificación de los servicios turísticos . La iniciativa contempla desarrollar capacitaciones dirigidas a los gremios de transporte local. Como parte de este proceso se prevé entregar distintivos oficiales a los operadores que cumplan con los estándares establecidos en materia de seguridad y atención. La identificación de los prestadores formales busca facilitar que los turistas puedan reconocer los servicios que cuentan con la documentación y las condiciones requeridas por las autoridades. Además, se habilitará un directorio público de operadores turísticos e intermediarios formales . Este registro tendrá una versión física y otra digital para que los visitantes puedan consultar información antes de contratar determinados servicios. Para el sector turístico, contar con información accesible sobre los prestadores formales resulta especialmente importante durante periodos en los que las condiciones climáticas pueden modificar el funcionamiento de determinadas actividades. Refuerzo del turismo procedente de Ecuador La estrategia de protección también considera el movimiento turístico procedente de Ecuador. La Red de Protección al Turista acordó fortalecer los mecanismos de fiscalización y recepción en los principales puntos de ingreso a la región. El mercado ecuatoriano es considerado uno de los mercados emisores relevantes para el turismo receptivo de Piura . Por ello, las autoridades plantean mejorar las condiciones de ingreso y permanencia de estos visitantes. La medida contempla una mayor coordinación en los puntos de ingreso, con el propósito de facilitar la orientación de los turistas y mantener el flujo de visitantes procedentes del vecino país. La información oficial sobre servicios y orientación turística puede ser consultada a través de Mincetur , entidad responsable de las políticas nacionales relacionadas con comercio exterior y turismo. Información sanitaria y alertas oficiales ante El Niño La Diresa Piura tendrá un papel central en la difusión de información sanitaria verificada. La entidad deberá coordinar la atención médica ante eventuales contingencias asociadas con el fenómeno El Niño. La estrategia incluye además la implementación de un directorio de emergencias disponible las 24 horas . Este recurso permitirá centralizar información de contacto para situaciones que requieran una respuesta inmediata. También se habilitará un canal digital oficial para difundir información diferenciada por provincia. La intención es que los turistas y operadores puedan acceder a datos verificados y evitar la circulación de información no confirmada durante eventuales emergencias. Según las autoridades, la comunicación será uno de los elementos centrales del plan, debido a que las condiciones pueden variar entre las distintas zonas de la región. ¿Qué instituciones participarán en la protección al turista? La respuesta contempla la participación coordinada de diferentes entidades públicas y privadas. Además del Gobierno Regional de Piura, Dircetur y Diresa, se considera la intervención de organismos relacionados con seguridad, transporte marítimo y atención de emergencias. La Red de Protección al Turista acordó ampliar su convocatoria a las cámaras de comercio locales, municipalidades provinciales, la Junta de Fiscales Superiores y gremios privados . La propuesta es establecer mesas de trabajo que permitan identificar las necesidades particulares de cada zona turística y definir acciones específicas frente a posibles escenarios derivados del fenómeno climático. ¿Para qué servirán las mesas de trabajo en Piura? Las mesas permitirán coordinar acciones entre autoridades, empresas y organizaciones vinculadas con la actividad turística. De acuerdo con la estrategia planteada, cada provincia podrá abordar sus propias necesidades en materia de seguridad, salud, información y atención a los visitantes. El enfoque busca que la respuesta no se limite a una sola institución y que los operadores turísticos también participen en las medidas preventivas. La información sobre alertas meteorológicas y condiciones climáticas deberá mantenerse vinculada a los reportes de las instituciones oficiales. En ese sentido, los visitantes pueden consultar los canales del Instituto Nacional de Defensa Civil (Indeci) y del Senamhi para conocer las recomendaciones y avisos emitidos por las autoridades.</t>
+          <t>La visita de campo permitió hoy identificar las zonas prioritarias de intervención y establecer las acciones que asumirá el sector empresarial para contribuir a la preparación del espacio que recibirá a miles de fieles durante la visita del santo padre.
+En la jornada participaron representantes de la Cancillería, el Gobierno Regional de Lambayeque, la Municipalidad Distrital de Pimentel, sector empresarial y diversas instituciones, quienes recorrieron el terreno para definir una hoja de ruta concreta y pasar de la planificación a la ejecución.
+El presidente de la Cámara de Comercio y Producción de Lambayeque (CCPL), Juan Manuel Scander Chikhani, reafirmó el compromiso del empresariado regional de sumar esfuerzos para que Pimentel se encuentre en condiciones adecuadas para este acontecimiento de alcance nacional.
+Centro de operaciones Como parte de este compromiso, la CCPL ha puesto a disposición sus instalaciones para el funcionamiento del centro de operaciones destinado a la prensa internacional y la Cancillería, que permitirá facilitar las labores de coordinación y cobertura durante la visita papal.
+Con la delimitación georreferenciada de los espacios y la definición de las primeras intervenciones, Pimentel entra así en una fase decisiva de preparación, en la que el trabajo conjunto entre autoridades y sector privado será clave para acondicionar el escenario de la celebración religiosa.
+Se informó que la Cámara de Comercio continuará acompañando las acciones de articulación institucional para contribuir a que Lambayeque esté preparado para recibir al papa León XIV y a los miles de peregrinos que llegarán a la región.
+Más en Andina: ????? El Gobierno atiende 536 puntos críticos del país como parte de las acciones de preparación frente al fenómeno El Niño 2026-2027.
+El ministro Marco Vinelli informó que la descolmatación del río Piura alcanza un 56% de avance en la zona de Los Ejidos.
+??… pic.twitter.com/0YymH6FkxL — Agencia Andina (@Agencia_Andina) September 19, 2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-activa-medidas-de-proteccion-al-turista-ante-posibles-impactos-del-fenomeno-el-nino/</t>
+          <t>https://andina.pe/agencia/noticia-misa-del-papa-leon-xiv-pimentel-delimitan-areas-para-trabajos-acondicionamiento-1092434.aspx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gas natural, más allá de Camisea y el ducto de TGP: ¿Qué alternativas existen para reducir la dependencia de una sola fuente?</t>
+          <t>Gobernadores regionales emiten pronunciamiento sobre presupuesto 2027</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Seis meses han transcurrido desde el último siniestro en el gasoducto de TGP, accidente – aún no aclarado - que ocasionó la catástrofe energética más grande en lo que va del siglo XXI en el Perú. Pasado ese lapso, sin embargo, no se ha tomado ninguna acción preventiva ni correctiva. Esto, “a pesar de que todos los expertos, incluyendo a los funcionarios del mismo Osinergmin” han señalado que la infraestructura que tenemos para el transporte de gas natural y líquidos de gas natural (LGN) es “precaria”, apunta Víctor Murillo, ex viceministro de Hidrocarburos. “Esta es la rotura número doce o trece en el ducto de TGP, y va a volver a ocurrir. ¿Pero, qué haremos con la siguiente?”, se pregunta Luis Espinoza, ex viceministro de Energía. Y es que lo acontecido en marzo pasado ha puesto de manifiesto que el país no puede depender de un solo gasoducto de transporte por los problemas que ya presenciamos durante esos trece aciagos días, empezando por la restricción a ‘cero’ del suministro de gas para industrias, plantas de generación térmica y taxis; siguiendo con la escasez de GLP (y hasta de diésel) registrada en ese lapso; y terminando con el retroceso que todo esto significó para el PBI, además de la escalada en la inflación. Igualmente importante, la tragedia ha develado que el Perú tampoco puede seguir dependiendo de un gran yacimiento de gas, en este caso, de Camisea (Cusco) - epicentro desde donde se despacha el 96% del gas natural y el 70% del GLP que se consume internamente – apunta Carlos Bianchi, presidente de la Sociedad Geológica del Perú. De allí, el llamamiento efectuado por el Instituto Peruano de Ingenieros de Gas, Petróleo y Energía (IPIGPE) en abril pasado para que adoptemos una estrategia de diversificación de fuentes (yacimientos) e infraestructura de transporte (ductos) de gas natural, aprovechando las importantes reservas y recursos prospectivos de hidrocarburos con que cuenta el país. Es el caso, de las cuencas de Tumbes y Talara; de las grandes cuencas amazónicas como el Huallaga, el Marañón, Ucayali y Madre de Dios; del off-shore en el norte del país, y hasta de la cuenca del Altiplano (Titicaca), apunta Víctor Sanz, vicepresidente del IPIGPE. No solo eso, Bianchi considera que existe una posibilidad muy interesante para el descubrimiento de gas en los lotes exploratorios Z-62, Z-63 y Z-64, frente a las costas de La Libertad, Lambayeque y Ancash, los cuales estuvieron hace muy poco en el ojo de la tormenta tras la decisión de Chevron de retirarse del área principal del proyecto. A entender del geólogo, el proyecto no ha sido abandonado pues sigue siendo liderado por Anadarko, empresa que se ha comprometido a perforar un pozo exploratorio en el lote Z-62, tras lo cual vendrían dos más. “Si es petróleo lo que descubren, lo sacarían en barcazas por Chiclayo. Y si, además, descubren gas, tendrían que implementar una pequeña planta en el litoral, la cual podría convertirse en una especie de nodo energético”, señala. Hasta que ello ocurra pasarán, sin embargo, varios años más. Mientras tanto, el país seguirá dependiendo de un solo yacimiento (Camisea) y de un solo gasoducto (de TGP). “¿Tenemos una situación distinta en términos de infraestructura y seguridad? No. Si hay otra situación parecida [a la de marzo] el riesgo es el mismo. Estamos siempre expuestos a eso y a las consecuencias que ya conocemos”, advierte Murillo. ¿Qué se debería hacer en el corto o mediano plazo? Cuando la rotura del ducto de TGP empezó a afectar a la capital, en marzo pasado, el gobierno transitorio de José Balcázar anunció que impulsaría la construcción de “una planta de regasificación en la costa, a fin de que nunca más tengamos estos problemas”. Una vez que se ‘apagó el incendio’, sin embargo, no se hizo más nada, y “así hasta que todo vuelva a explotar, porque se trata de una bomba de tiempo de un nivel similar al de El Fenómeno El Niño”, indica Freddy Morales, presidente del IPIGPE. A decir del especialista, este Gobierno tiene la posibilidad de concretar el planteamiento de Balcázar, pues se trata de una infraestructura que puede ser planificada y construida en un lapso de tres a cuatro años. La obra permitiría reconvertir a su estado original un porcentaje del gas natural líquido (GNL) almacenado en Pampa Melchorita, a fin de que pueda ser distribuido en Lima y Callo en situaciones de emergencia. “Este debe ser uno de los proyectos de hidrocarburos prioritarios para el Perú en el mediano y largo plazo en el país”, anota Morales. A decir de Murillo, se trata de un proyecto que puede ser costoso para el Estado pero que “siempre será menos caro que producir energía con diésel”. Espinoza considera, sin embargo, que la planta de regasificación solo resolverá la mitad de los problemas asociados a una nueva paralización del ducto de TGP, porque dicha solución apunta específicamente al tema del gas cuando “las estadísticas demuestran que todos los accidentes registrados en los últimos 22 años han ocurrido en el ducto de líquidos”. De allí, la necesidad de construir un nuevo tubo de LGN. Por lo pronto, lo que el Minem y el Gobierno vienen proponiendo para mitigar la dependencia del país en torno a Camisea es la exploración y desarrollo de fuentes alternativas de gas natural, empezando por el área del Cándamo (Puno-Madre de Dios) donde en la década de los 90’ la petrolera Mobil descubrió 3,6 trillones de pies cúbicos (TCF) del preciado hidrocarburo - equivalentes a ocho veces lo producido por Camisea en el 2025 -, los cuales siguen allí, dormidos. Más aún, el Minem apunta a poner en valor los 20,4 de TCF de recursos prospectivos identificados en la Cuenca Madre de Dios, lo cual representa “todo un reto”, manifestó Iris Cárdenas, viceministra de Hidrocarburos, en el Foro Gas Natural Perú 2026. En esa línea, el ministerio busca establecer un consenso con el Servicio de Áreas Naturales Protegidas (Sernanp) para poder realizar actividades exploratorias en áreas donde ya ha habido labores hidrocarburíferas, como la estructura del Candamo, circunscrita al parque nacional Bahuaja Sonene. “En el tema de las ANP, tenemos una propuesta para la modificación de dicha ley (Ley 26834) con el propósito de habilitar estas áreas donde ya ha habido intervención y se pueda desarrollar el gas natural”, expresó Cárdenas. Para apuntalar esta iniciativa, el Minem plantea transferir un porcentaje de lo producido en el Candamo al Sernanp, para que “pueda cuidar todas las áreas naturales protegidas”, particularmente, las expuestas a la tala y la minería ilegal. Mucho antes que el Candamo veremos, sin embargo, la puesta en marcha del lote 58 (Cusco) de la china CNPC, el cual alberga 3,56 TCF en recursos contingentes (3C). Se trata de un proyecto que debería entrar en producción hacia noviembre y que se añadiría al flujo proveniente de Camisea a través del gasoducto del mismo nombre. Y es que un escollo para la implementación de nueva infraestructura de transporte (Perú tiene menos tubos de hierro construidos que sus pares de la región) es la debilidad de la demanda interna, que desalienta la inversión en gasoductos. Así, ocurre que el 20% de la producción diaria del lote 88 (orientado al consumo interno) se reinyecta al subsuelo, según estadísticas de Pluspetrol. Y otro tanto ocurre en los lotes de hidrocarburos de Piura, cuyos operadores queman el gas natural que no pueden colocar en el mercado. Ello, a pesar del interesante potencial gasífero que alberga dicha región y que bien podría servir para atender la demanda de regiones vecinas como Lambayeque, La Libertad y Ancash, apunta Luis Fernández, socio director de Gas Energy Perú. “Lamentablemente, hay un problema por resolver en el Perú, que es la débil demanda de gas. Mientras esto no se resuelva, este recurso va a seguir satisfaciendo solamente a Lima y algunas ciudades de la costa, con el riesgo latente de que el ducto de TGP vuelva a fallar”, refiere Bianchi. Esa demanda existe, sin embargo, en el sur del Perú, y está constituida por las dos centrales térmicas de Ilo y Mollendo (nodo energético del sur), las cuales aguardan desde hace largos años el arribo del gas para empezar operar con dicho hidrocarburo (hoy lo hacen con diésel). A entender de Murillo, la mejor forma de plasmar esta esperanza es relanzando el SIT Gas (otro Gasoducto Surperuano), “proyecto viable, pero inmovilizado desde hace cinco años” que haría más seguro el sistema de ductos actual y masificaría el gas natural en el sur. Se trata, refiere, de una iniciativa necesaria por cuanto el COES acaba de alertar que los precios de la energía se incrementarán en adelante debido a que “dependeremos en mayor medida del diésel, el cual incrementa el costo de la electricidad en diez veces”. El SIT Gas no es, sin embargo, la única solución para llevar el gas de Camisea al sur. Pendiente de desarrollo también está el gasoducto costero o Extensión Sur, de TGP, proyecto que busca llegar también a las centrales de Ilo y Mollendo, además de a las industrias de Arequipa. Igualmente factible es, según Gas Energy, la construcción de un gasoducto entre Piura y Chiclayo, el cual tendría por ‘ancla’ las centrales térmicas de Eten, aprovechando, para ello, el potencial gasífero de los lotes de hidrocarburos del noroeste (aproximadamente 5,5 TCF). El desarrollo de este proyecto requiere, sin embargo, de un tipo de regulación diferente, que contemple una tarifa especial para el sector de generación eléctrica en el norte del país, similar al del nodo energético de Chilca. Solo, así, señala Fernández, las centrales de Eten podrán competir con sus pares de Lima y con el precio regulado del gas de Camisea.</t>
+          <t>En ese sentido, plantearon la necesidad de revisar su asignación para garantizar la continuidad de proyectos y la capacidad de respuesta de las nuevas autoridades.
+De acuerdo con el proyecto presupuestal para el año 2027, los gobiernos regionales son el único nivel de gobierno afectado por un recorte en su Presupuesto Institucional de Apertura (PIA) de inversiones , sufriendo una reducción del 19.12 % .
+“Nos preocupa que los gobiernos regionales enfrenten una reducción cercana al 20 % de su presupuesto de inversión, pese al alto nivel de ejecución que vienen demostrando en sus proyectos y obras”, señaló el titular de la ANGR, Luis Neyra.
+De igual modo, precisó que los gobiernos regionales mantuvieron de manera constante una eficiencia de ejecución presupuestal por encima del 90 % en los últimos años.
+Asimismo, refirió que esta reducción dejará a las nuevas autoridades regionales sin la capacidad financiera requerida para responder a la población, provocando la paralización de proyectos estratégicos destrabados, además de debilitar la gestión de riesgo ante la inminente llegada del fenómeno El Niño (FEN) .
+En el encuentro participaron junto al titular del Consejo de Ministros, Luis Galarreta ; el ministro de Economía y Finanzas, Elmer Cuba ; el viceministro de Hacienda, Erick Lahura ; el viceministro de Desarrollo de Agricultura Familiar e Infraestructura Agraria y Riego, José Tangherlini ; y el viceministro de Gobernanza Territorial, Enrique Vásquez.
+Las autoridades regionales que participaron corresponden a las regiones de Piura, Ayacucho, Lima, Huánuco, Huancavelica, Moquegua, Lambayeque, Pasco, Tumbes, Loreto, Callao, Cajamarca, Amazonas, La Libertad y Áncash.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/economia/gas-natural-mas-alla-de-camisea-y-el-ducto-de-tgp-que-alternativas-existen-para-reducir-la-dependencia-de-un-solo-gasoducto-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-gobernadores-regionales-emiten-pronunciamiento-sobre-presupuesto-2027-1092415.aspx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Esperan aprobación del Minsa sobre diseño de Hospital de Alta Complejidad e iniciar construcción</t>
+          <t>Inversión en infraestructura de transporte concesionada sumó US$ 895 millones a agosto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>El proyecto del Hospital de Alta Complejidad de Piura sigue en marcha. A la fecha ya se culminó su diseño integral y quedó a la espera de la aprobación del Ministerio de Salud (Minsa) para pasar enseguida a la fase de construcción. El proyecto, que prevé una inversión de S/3,201’976,925, busca ampliar la atención especializada para más de tres millones de habitantes de Piura y otras regiones del norte del país. La ejecución estará a cargo de Sinohydro Corporation Limited, empresa contratista seleccionada para desarrollar la obra bajo el mecanismo de Gobierno a Gobierno con el Reino Unido. El contrato contempla el diseño, la construcción, la instalación de equipos médicos y la puesta en marcha del hospital.</t>
+          <t>Las inversiones valorizadas en aeropuertos ascendieron a 484.7 millones de dólares, lo que significó un crecimiento de 53.6% en comparación con el mismo periodo del año anterior.
+ONP y AFP: ¿qué pasará con los aportes si un afiliado cambia de sistema previsional? Por su parte, las inversiones valorizadas en carreteras alcanzaron los 94 millones de dólares, cifra que superó en 188.5% a la registrada entre enero y agosto de 2025.
+En tanto, la concesión de la Línea 2 del Metro de Lima y Callao registró el mayor volumen de inversión acumulada durante el año, con 303.3 millones de dólares valorizados entre enero y agosto, monto superior en 2% al alcanzado en igual periodo de 2025.
+Inversiones valorizadas en agosto Solo en agosto de 2026, las inversiones valorizadas en las infraestructuras de transporte concesionadas sumaron 69.9 millones de dólares.
+En el sector aeroportuario, las inversiones valorizadas ascendieron a 49 millones de dólares.
+De ese total, Lima Airport Partners (LAP) concentró 47.4 millones en inversiones directas en mejoras por el proyecto de ampliación del aeropuerto Jorge Chávez.
+A su vez, el Primer Grupo de Aeropuertos registró valorizaciones por 1.59 millones, vinculadas principalmente al mantenimiento periódico al sistema eléctrico de los aeropuertos de Chiclayo, Piura, Talara y Tumbes.
+En la Red Vial se dinamizaron 13.2 millones de dólares.
+IIRSA Sur Tramo 4 registró inversiones valorizadas por 5.68 millones, destinadas principalmente en el avance de la ejecución de la obra accesoria por seguridad vial-mejoramiento del Sub-Tramo Asillo-San Antón y la ejecución de la obra accesoria inserción urbana y acondicionamiento de drenaje del Centro Poblado de Sangari.
+Asimismo, la concesión IIRSA Norte ejecutó inversiones valorizadas por 3.59 millones en el avance de obras accesorias.
+Por su parte, Autopista del Sol reportó inversiones valorizadas en 1.83 millones, asociadas al avance de la ejecución de las obras obligatorias Evitamiento Chiclayo Zona Norte, Puente Lambayeque e Intercambio Vial Lambayeque, así como de las obras de rehabilitación para la reconstrucción de los sectores afectados por el FEN 2023 en el tramo Trujillo-Chiclayo.
+De igual manera, la concesión Red Vial N.° 6 alcanzó inversiones valorizadas en 1.35 millones en el avance de la obra paso peatonal San Clemente.
+En la Línea 2 del Metro se valorizaron inversiones por 5.15 millones en equipamiento electromecánico, avances de la instalación de las puertas de andén y del sistema de control de pasajeros de las estaciones.
+En el ámbito portuario, la mayor valorización correspondió al Terminal Portuario de Paita, que ejecutó inversiones por 1.87 millones destinadas al sistema de contención de derrumbes del área colindante al terminal portuario y la ampliación de reefer racks.
+Avance de las inversiones Al 31 de agosto de 2026, la inversión valorizada acumulada en las infraestructuras de transporte concesionadas ascendió a 14,820.2 millones de dólares, cifra que representa un avance de 64.6% respecto al compromiso de inversión, que asciende a 22,944.7 millones.
+Más en Andina: La Superintendencia de Banca, Seguros y AFP ( @SBSPERU ) aprobó el Reglamento para la administración del riesgo de sobreendeudamiento de los socios deudores minoristas de las cooperativas de ahorro y crédito no autorizadas a captar recursos del público (Coopac).… pic.twitter.com/tdeeZApUpq — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/esperan-aprobacion-del-minsa-sobre-diseno-de-hospital-de-alta-complejidad-e-iniciar-construccion/</t>
+          <t>https://andina.pe/agencia/noticia-inversion-infraestructura-transporte-concesionada-sumo-895-millones-a-agosto-1092376.aspx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piura soportará temperaturas superiores a 36 °C por El Niño durante la primavera</t>
+          <t>El Niño: Impulsan red de 7 puertos para garantizar abastecimiento de alimentos y ayuda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>La llegada de la primavera traerá un incremento de las temperaturas en Piura y podría marcar uno de los primeros impactos asociados al desarrollo de El Niño : las olas de calor. De acuerdo con el especialista en meteorología del Senamhi, Héctor Yauri, las condiciones cálidas del océano, sumadas al cambio estacional, favorecerán episodios de temperaturas elevadas, principalmente entre noviembre y diciembre. El escenario climático previsto para los próximos meses mantiene la atención sobre la costa norte del país. Según información difundida por el Senamhi y la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno El Niño (ENFEN), las condiciones cálidas persistirán durante la temporada 2026-2027. Para la región Niño 1+2, que comprende el mar frente a la costa peruana, se prevé que el evento continúe hasta el próximo verano. El Niño favorecerá temperaturas más altas en Piura Yauri explicó que el calentamiento del océano frente a la costa peruana constituye uno de los factores que pueden contribuir al aumento de las temperaturas del aire. El especialista señaló que el comportamiento observado presenta características que requieren seguimiento durante la primavera. “Actualmente ya hemos superado los 3,5 grados en promedio en todo el mar frente a nuestra costa. Eso corresponde a una categoría extraordinaria, comparable con el nivel que tuvimos en 1997-1998”, señaló Yauri. De acuerdo con el especialista, la mayor intensidad del calentamiento podría presentarse durante noviembre, cuando las anomalías de la temperatura del mar alcanzarían alrededor de 4 °C en promedio. Este escenario tendría repercusiones sobre las condiciones meteorológicas de la costa norte. El Senamhi también ha advertido que las temperaturas del aire en la costa peruana se mantendrían por encima de sus valores climatológicos debido a la persistencia del calentamiento del mar. En su actualización de junio, el organismo señaló que el Niño Costero podría prolongarse hasta el verano de 2027. Chulucanas y Malacasí ya registraron temperaturas elevadas Las altas temperaturas ya comenzaron a manifestarse en algunas localidades de la región Piura. Según los datos mencionados por Yauri, Chulucanas registró 38,8 °C, mientras que Malacasí alcanzó 37,2 °C. En la ciudad de Piura, entretanto, todavía no se habían superado los 35 °C al momento de las declaraciones. El comportamiento no resulta extraño para una región acostumbrada a registrar temperaturas elevadas, pero adquiere especial importancia cuando se combina con un océano más cálido y una mayor humedad ambiental. “El primer impacto que vamos a tener de El Niño, antes de las lluvias para la costa norte, van a ser las olas de calor. Ya se han registrado, pero no han sido percibidas tanto porque todavía estábamos en la etapa invernal”, explicó el especialista. Los registros históricos del Senamhi muestran que Piura presenta condiciones naturalmente cálidas. En marzo de 2026, por ejemplo, la estación La Esperanza registró una temperatura máxima promedio de 32,4 °C, mientras que Bernal alcanzó 34,6 °C, ambos valores por encima de sus respectivas climatologías. Noviembre sería uno de los meses más críticos para el calor Actualmente, las temperaturas promedio en Piura se ubican alrededor de los 32 °C y 33 °C, con máximas que pueden alcanzar entre 35 °C y 36 °C. Sin embargo, la sensación térmica puede ser mayor cuando se combina el calor con elevados niveles de humedad. Con el avance de la primavera, esta situación podría intensificarse. Yauri sostuvo que durante noviembre podrían presentarse temperaturas superiores a los 36 °C durante varios días consecutivos, una situación que puede configurar condiciones de ola de calor. “En noviembre puede ser importante. Las temperaturas pueden llegar sostenidamente a más de 36 grados por cinco días y eso ya puede generar una ola de calor. Con el aumento de la humedad, este efecto puede ser mucho mayor”, sostuvo. Para febrero y marzo, meses que suelen registrar algunos de los valores más elevados del año en la región, existe la posibilidad de que determinados episodios se acerquen a los 38 °C o 39 °C. No obstante, la evolución dependerá de las condiciones atmosféricas y oceánicas que se presenten durante los siguientes meses. ¿Cuándo llegarían las lluvias a Piura? El aumento de las temperaturas no significa necesariamente que las lluvias comiencen de inmediato. Según el escenario explicado por el especialista, durante septiembre todavía no se esperaba un inicio generalizado de las precipitaciones en la costa norte. De acuerdo con el escenario climático manejado por las autoridades meteorológicas, las primeras precipitaciones asociadas al periodo lluvioso podrían presentarse con intensidad moderada en Tumbes durante noviembre y posteriormente avanzar hacia Piura en diciembre. El Senamhi ha señalado que la temporada de lluvias 2026-2027 debe ser seguida mediante los pronósticos y avisos meteorológicos vigentes, debido a la continuidad de El Niño Costero y al desarrollo de condiciones de El Niño en el Pacífico ecuatorial central. El impacto de El Niño no se limita al río Piura Yauri remarcó que los posibles efectos de El Niño en Piura no deben analizarse únicamente desde el riesgo de incremento del caudal del río Piura. Las precipitaciones pueden afectar distintos sectores de la región, especialmente aquellas zonas ubicadas en la sierra y en las partes altas de las cuencas. Asimismo, las condiciones cálidas y húmedas pueden favorecer otros fenómenos meteorológicos, entre ellos las tormentas eléctricas. Por ello, el seguimiento de los pronósticos resulta relevante tanto para las autoridades como para la población. La experiencia de anteriores eventos permite dimensionar la importancia de este escenario. Durante El Niño de 1997-1998 , entre enero y abril, Piura acumuló aproximadamente 2,5 metros de lluvia, mientras que en Chulucanas y otros sectores del Alto Piura los acumulados llegaron a entre 3 y 4 metros. En contraste, los acumulados registrados durante los eventos de 2017 y 2023 fueron considerablemente menores, según la comparación realizada por el especialista. ¿El aumento de temperaturas puede favorecer el dengue? Otro de los aspectos que genera preocupación está relacionado con la salud pública. Las temperaturas elevadas, combinadas posteriormente con lluvias y mayor humedad, pueden crear condiciones favorables para la reproducción del mosquito transmisor del dengue. Yauri explicó que normalmente los casos disminuyen durante los meses de invierno y tienden a incrementarse después de la temporada de lluvias. Sin embargo, durante este año se habría observado una situación distinta, debido a la presencia del mosquito transmisor incluso durante meses en los que habitualmente su actividad disminuye. “Si las temperaturas se mantienen altas y empieza la lluvia en octubre o noviembre, eso podría ser un gatillador para que el dengue empiece con una epidemia. Es inusual porque normalmente en los meses antes de la primavera no ocurren muchos casos”, advirtió. ¿Qué se debe vigilar durante los próximos meses? El comportamiento de las temperaturas, la humedad, las lluvias y las condiciones del océano serán algunos de los principales indicadores para conocer cómo evolucionará el escenario climático en Piura. Según el Senamhi, la población debe mantenerse informada mediante los pronósticos oficiales y los avisos meteorológicos, mientras que las autoridades deben considerar los escenarios de riesgo para adoptar medidas de preparación ante los posibles impactos de la temporada de lluvias. Para consultar información actualizada, los reportes oficiales pueden revisarse en el Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) y en la Comisión Multisectorial ENFEN , organismos encargados del monitoreo de las condiciones oceánicas y atmosféricas relacionadas con El Niño.</t>
+          <t>La red comprende a los puertos de Talara, Paita, Salaverry, Chimbote, Chancay, Callao y Pisco .
+Esta se articulará mediante transporte marítimo de cabotaje.
+[Lea también: Conoce a Juanpi Sicha, el guardián de recetas típicas de la cocina de la región Apurímac ] En esta red se movilizarán alimentos, medicinas, suministros estratégicos y otros bienes prioritarios cuando las lluvias intensas, la activación de quebradas o las crecidas de ríos afecten la conectividad terrestre, se informó desde el Ministerio de Transportes y Comunicaciones.
+Frente a ello, los puertos podrán contar con una vía adicional para acercar la carga a las zonas que requieran atención ante una eventual interrupción de las vías terrestres.
+Acciones de prevención En el marco de la preparación para afrontar los efectos del fenómeno El Niño, la APN evalúa las condiciones de los terminales portuarios, sus accesos y las rutas que los conectan con las zonas de abastecimiento.
+Además, la referida entidad coordina con administradores portuarios, la Marina de Guerra, Provías, gobiernos regionales y otras entidades para identificar las capacidades que podrían activarse ante una eventual emergencia.
+[Lea también: Denuncian pintas en roca sagrada inca del parque Sacsayhuamán ] Esto se enmarca en el Plan de Acción ante la ocurrencia del Fenómeno El Niño , aprobado mediante Resolución de Presidencia de Directorio de la APN 0078-2026-APN-PD.
+Las medidas comprenden el levantamiento de información técnica de terminales portuarios y embarcaderos, la evaluación de rutas de acceso y la identificación de puntos críticos asociados a ríos y quebradas para preservar la continuidad operativa y logística del Sistema Portuario Nacional.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-soportara-temperaturas-superiores-a-36-c-por-el-nino-durante-la-primavera/</t>
+          <t>https://andina.pe/agencia/noticia-el-nino-impulsan-red-7-puertos-para-garantizar-abastecimiento-alimentos-y-ayuda-1092359.aspx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ministro de Educación anuncia plan para continuidad de clases ante el fenómeno El Niño</t>
+          <t>Más de 11 mil casos de violencia escolar en lo que va del 2026: cifras por tipo y región</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>El ministro de Educación, José Antonio Chang, anunció ante la Comisión de Educación, Cultura y Deporte de la Cámara de Diputados un conjunto de medidas destinadas a reducir el impacto del Fenómeno El Niño en la infraestructura educativa y garantizar la continuidad de las clases en las zonas que podrían resultar afectadas por el evento climático. Durante su presentación, el titular del Ministerio de Educación (MINEDU) explicó que el plan contempla acciones preventivas y medidas que serán activadas en caso de que las condiciones climáticas provoquen daños en los colegios o dificulten el traslado de los estudiantes. ¿Qué regiones serán priorizadas para proteger las clases? Como parte de la primera etapa preventiva, el sector Educación priorizará la atención de instituciones educativas ubicadas en Lambayeque, Tumbes, Piura, La Libertad y Lima Provincias , regiones consideradas dentro de las zonas que podrían enfrentar mayores efectos asociados al Fenómeno El Niño. Según explicó Chang, la intervención alcanzará a miles de locales educativos y aulas, con el objetivo de reducir los riesgos para estudiantes y docentes y evitar que eventuales daños en la infraestructura terminen provocando una interrupción prolongada del servicio educativo. “Vamos a atender 7,998 locales educativos, 49,020 aulas en donde estudian un millón 237 mil estudiantes”, informó el ministro durante su intervención. Para estas acciones, el sector solicitó un crédito suplementario de S/ 304 millones . El plan contempla aulas prefabricadas ante posibles daños Una de las medidas previstas por el MINEDU consiste en disponer de 1,500 aulas prefabricadas modulares que podrían ser instaladas en las zonas donde los colegios sufran daños que impidan el desarrollo normal de las actividades escolares. La distribución de estos módulos dependerá de las necesidades que se presenten en las distintas regiones del país. El objetivo es contar con espacios alternativos que permitan mantener el servicio educativo mientras se realizan reparaciones o se recupera la infraestructura afectada. La medida busca evitar que los problemas estructurales de un colegio se conviertan automáticamente en una suspensión indefinida de las clases presenciales , especialmente en comunidades donde existen pocas alternativas para continuar con la educación. “Aula TV” busca mantener las clases durante las interrupciones El ministro también puso énfasis en un aspecto distinto a la infraestructura: la continuidad del aprendizaje. Para ello, el MINEDU trabaja en la propuesta denominada “Aula TV” , desarrollada mediante una alianza con el Instituto Nacional de Radio y Televisión del Perú (IRTP). La iniciativa está dirigida a los estudiantes que temporalmente no puedan acudir a sus colegios debido a las condiciones generadas por el Fenómeno El Niño. La televisión sería utilizada como una herramienta para transmitir contenidos educativos mientras se restablece la atención presencial. Chang señaló que la experiencia de la pandemia evidenció la necesidad de contar con alternativas previamente diseñadas para garantizar el acceso a la educación cuando los estudiantes no pueden acudir físicamente a las instituciones educativas. Cuatro escenarios para garantizar la continuidad educativa El Ministerio de Educación estableció cuatro escenarios que permitirían mantener el servicio educativo dependiendo de la magnitud de la emergencia y de las condiciones de cada localidad. 1. Mantener las escuelas operativas Cuando las condiciones permitan utilizar los colegios con seguridad, las clases continuarán de manera presencial, aunque podrían realizarse ajustes en los horarios para responder a las circunstancias provocadas por las lluvias u otros efectos del evento climático. 2. Utilizar la televisión ante interrupciones temporales Si los estudiantes no pueden asistir durante determinados periodos, se plantea implementar una franja diaria de clases por televisión . Esta alternativa permitiría mantener el contacto con los contenidos educativos mientras se normaliza la asistencia a los colegios. 3. Reubicar a los estudiantes en otros locales Cuando una institución educativa quede temporalmente inhabilitada, los estudiantes podrían ser trasladados a locales comunales o parroquias que reúnan las condiciones necesarias para desarrollar las actividades educativas. 4. Utilizar radio, televisión y material impreso Para las comunidades que queden aisladas debido a la emergencia, el plan contempla recurrir a diferentes medios de comunicación. En estos casos, la educación podría apoyarse en radio, televisión y materiales impresos , de acuerdo con las condiciones de cada localidad. MINEDU evalúa retomar el mantenimiento preventivo de colegios Otra de las medidas anunciadas está relacionada con el mantenimiento de las instituciones educativas. El sector evalúa retomar un esquema de mantenimiento preventivo que permita atender reparaciones necesarias antes de que las condiciones climáticas puedan agravarlas. Este tipo de intervención busca responder a problemas inmediatos de los colegios y reducir los riesgos asociados al deterioro de techos, aulas y otros espacios utilizados diariamente por estudiantes y docentes. De acuerdo con el Ministerio de Educación, las acciones preventivas serán importantes para determinar qué instituciones pueden continuar funcionando y cuáles necesitarían una intervención mayor ante una eventual emergencia. Congresistas preguntan por infraestructura educativa y clases virtuales Durante la sesión, presidida por el diputado Juan Castrejón, los integrantes de la Comisión de Educación, Cultura y Deporte solicitaron mayores detalles sobre las medidas previstas para enfrentar los efectos del Fenómeno El Niño y sobre el estado de los colegios en diferentes regiones. La diputada Rossana Alayza pidió conocer los criterios que empleará el sector para determinar qué instituciones educativas serán refaccionadas y cuáles necesitarán una nueva infraestructura. También planteó la necesidad de evitar que una emergencia climática derive en un retorno generalizado a las clases virtuales . Por su parte, el diputado José Yataco señaló que en Ica todavía existen solicitudes relacionadas con la reconstrucción de colegios afectados por el terremoto de 2007. El legislador consultó qué medidas se ejecutarán antes de la llegada del Fenómeno El Niño y si podrían utilizarse facultades legislativas para acelerar las intervenciones.</t>
+          <t>Ante la denuncia de un presunto abuso sexual contra un estudiante del Liceo Naval Almirante Guise, presuntamente cometido por un grupo de 10 escolares, vuelve a ponerse bajo la lupa la violencia que puede presentarse en los espacios educativos, donde niñas, niños y adolescentes deberían desarrollarse en un entorno seguro y de respeto.
+Lee también: Caso liceo naval: hoy vence plazo de retención en comisaría de escolares denunciados Los reportes del Minedu muestran que el colegio puede convertirse en un escenario de distintas formas de violencia.
+Entre el 1 de enero y el 31 de agosto del 2026, la plataforma SíseVe registró 11 805 reportes de violencia escolar a nivel nacional, que incluyen agresiones entre estudiantes y situaciones en las que estaría involucrado personal de las instituciones educativas.
+Del total de reportes, 5 187 corresponden a violencia física, 4 559 a violencia psicológica y 2 059 a violencia sexual.
+Estas cifras muestran la dimensión de la violencia en el ámbito escolar y evidencian que las agresiones sexuales también forman parte de los casos reportados ante el Minedu.
+A nivel regional A nivel regional, Lima Metropolitana concentra la mayor cantidad de reportes de violencia escolar, con 4 072 casos registrados entre enero y agosto de 2026.
+Le siguen Arequipa, Piura, Junín, Áncash y La Libertad, mientras que Madre de Dios, Huancavelica y Apurímac presentan las cifras más bajas del periodo.
+A continuación, el detalle por región: Lima Metropolitana: 4 072 Arequipa: 730 Piura: 683 Junín: 552 Áncash: 540 La Libertad: 530 Lambayeque: 490 Ica: 414 Cusco: 411 Callao: 423 Lima Provincia: 379 Huánuco: 353 Tacna: 354 San Martín: 322 Cajamarca: 246 Ucayali: 200 Amazonas: 199 Ayacucho: 197 Loreto: 123 Puno: 109 Pasco: 100 Tumbes: 102 Moquegua: 97 Apurímac: 67 Huancavelica: 57 Madre de Dios: 55 Clasificación de la violencia escolar Los reportes de SíseVe agrupan las situaciones de violencia escolar en tres categorías a nivel nacional: física, psicológica y sexual.
+La violencia física comprende el castigo físico, las agresiones que ocasionan lesiones o aquellas que no las generan, así como los casos en los que se utilizan armas.
+En tanto, la violencia psicológica incluye acoso escolar, aislamiento, ciberacoso, discriminación, intimidación, trato humillante, agresiones verbales y situaciones con uso de armas.
+Lee también: Primavera en Lima: más de 20 000 flores amarillas adornarán parques y plazas Por su parte, la violencia sexual contempla el acoso sexual, incluido aquel realizado mediante medios tecnológicos; el hostigamiento sexual; los tocamientos de carácter sexual; los actos de connotación sexual o libidinosos; y la violación sexual, incluso cuando se comete mediante medios tecnológicos.
+Violencia Física Castigo físico (816) Con lesiones (1859) Con uso de armas (64) Sin lesiones (2448) Violencia psicológica Acoso escolar (786) Aislamiento (49) Ciber acoso (564) Uso con armas (27) Discriminación (224) Intimidación (420) Trato humillante (1226) Verbal (1263) Violencia sexual Acoso sexual (92) Acoso sexual a través de medios tecnológicos (59) Hostigamiento sexual (213) Tocamientos, actos de connotación sexual o actos libidinosos (1423) Violación sexual (156) Violencia con fines sexuales a través de medios tecnológicos (116) Más en Andina ? El cardenal Carlos Castillo, arzobispo de Lima, anunció que se realizan gestiones para que la imagen del Señor de los Milagros se encuentre con el papa León XIV durante el último día de su visita a Lima.
+https://t.co/lg713AIZrF pic.twitter.com/S0sA4l1Pql — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ministro-de-educacion-anuncia-plan-para-continuidad-de-clases-ante-el-fenomeno-el-nino/</t>
+          <t>https://andina.pe/agencia/noticia-mas-11-mil-casos-violencia-escolar-lo-va-del-2026-cifras-tipo-y-region-1092355.aspx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>El Niño Costero podría generar lluvias de 100 mm por día durante el verano</t>
+          <t>Advierten de posibles riesgos ambientales en refinería de Petroperú por fenómeno El Niño</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>El desarrollo de un El Niño Costero de magnitud extraordinaria podría elevar considerablemente la intensidad de las lluvias durante el verano 2026-2027. De acuerdo con Rinia Gabriel, vocera de la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno “El Niño” (ENFEN), las precipitaciones en la costa norte podrían alcanzar entre 80 y 100 milímetros por día bajo un escenario de calentamiento excepcional del mar. La estimación fue difundida por la Agencia Andina el 16 de septiembre de 2026 y se produce en un contexto en el que el ENFEN mantiene la alerta por El Niño Costero y contempla una posible magnitud extraordinaria durante los próximos meses. El escenario tiene especial relevancia para regiones como Tumbes, Piura y Lambayeque, donde las lluvias intensas pueden generar impactos en ciudades, carreteras, ríos y zonas agrícolas. El Niño Costero podría llevar las lluvias hasta 100 milímetros diarios Según explicó Rinia Gabriel, una precipitación de entre 80 y 100 milímetros representa entre 80 y 100 litros de agua por cada metro cuadrado. Se trata de valores que pueden superar ampliamente los registros habituales de la costa norte peruana. La especialista recordó que durante el El Niño Costero de 2017 se registraron precipitaciones cercanas a los 75 milímetros en Piura. Bajo las condiciones oceánicas previstas para el próximo verano, ese nivel podría ser superado. El antecedente más fuerte corresponde a los eventos de 1997-1998 . De acuerdo con la información manejada por el ENFEN, durante aquellos años los acumulados mensuales de verano en Piura llegaron a estimarse entre 1,000 y 1,500 milímetros. Estos antecedentes permiten dimensionar la importancia de las actuales proyecciones, aunque los especialistas advierten que la intensidad exacta de las precipitaciones dependerá de la evolución de las condiciones del océano y de la atmósfera. ¿Por qué un mar más caliente puede generar lluvias más intensas? El factor central del actual escenario es la temperatura superficial del mar. El El Niño Costero se desarrolla cuando las aguas frente a la costa peruana presentan un calentamiento anómalo y persistente. Para los próximos meses se espera que amplias zonas del litoral puedan registrar temperaturas de 26, 27 e incluso 28 °C. Un océano más cálido favorece una mayor disponibilidad de humedad en la atmósfera y puede proporcionar las condiciones necesarias para el desarrollo de lluvias más intensas. Sin embargo, Rinia Gabriel aclaró que no basta con que un punto determinado del océano alcance 26 o 27 °C. Para que el efecto sobre las precipitaciones sea mayor, las temperaturas elevadas deben mantenerse durante un periodo prolongado y abarcar una superficie suficientemente extensa. Actualmente ya se observan sectores frente al litoral peruano con temperaturas de 26 y 27 °C, aunque todavía se trata de áreas relativamente pequeñas. El escenario cambiaría si ese calentamiento se extendiera sobre una mayor superficie del mar frente al norte peruano. Las lluvias podrían aumentar de manera gradual El posible escenario extraordinario no significa que las lluvias extremas vayan a aparecer de manera inmediata. Según la explicación proporcionada por la vocera del ENFEN, las precipitaciones podrían incrementarse progresivamente conforme avance la primavera y se aproxime el verano. Incluso existe la posibilidad de que la temporada de lluvias se adelante y que desde noviembre comiencen a observarse mayores precipitaciones. Sin embargo, un incremento de las lluvias durante octubre o noviembre no necesariamente significa que desde esos meses se presenten episodios extremos. El mayor potencial para precipitaciones intensas se concentraría durante los meses de verano, especialmente cuando las condiciones oceánicas y atmosféricas alcancen una combinación favorable para la formación y persistencia de sistemas de lluvia. ¿El Niño Costero podría superar al evento de 1997-1998? La evolución actual presenta algunas características que recuerdan al El Niño de 1997-1998 . No obstante, la diferencia señalada por los especialistas está relacionada con las temperaturas proyectadas para el océano. Rinia Gabriel indicó que el actual evento presenta similitudes en su evolución con el registrado entre 1997 y 1998, pero las proyecciones apuntan a un escenario más cálido. Un océano con temperaturas excepcionalmente altas puede aportar mayor humedad a la atmósfera. Por ello, bajo determinadas condiciones, las lluvias podrían superar los niveles registrados en episodios anteriores, especialmente en la costa norte y central del país. La zona bajo vigilancia comprende principalmente el norte y centro del litoral peruano. Lima también forma parte del área donde podrían registrarse efectos asociados al incremento de las precipitaciones. Para Ica y regiones más al sur, el comportamiento de las lluvias todavía requiere una evaluación más detallada. ¿Qué significa que El Niño Costero sea extraordinario? La categoría extraordinario corresponde al nivel máximo de magnitud contemplado para el El Niño Costero . Su clasificación no depende directamente de la cantidad de lluvia registrada, sino principalmente de las anomalías de la temperatura superficial del mar en la región Niño 1+2. Según información difundida por el ENFEN, un escenario extraordinario está asociado con anomalías superiores a 3.5 °C durante un periodo prolongado. El análisis considera el comportamiento promedio de una zona amplia y no solamente registros aislados. Por esa razón, que un punto específico del mar presente una anomalía de 5, 6 o incluso 7 °C no significa por sí solo que el evento sea clasificado como extraordinario. Lo determinante es la persistencia y extensión del calentamiento. El más reciente reporte del ENFEN señala que entre septiembre de 2026 y enero de 2027 existe una alta probabilidad de que El Niño Costero alcance magnitud extraordinaria, mientras que para febrero y marzo se contempla una magnitud entre fuerte y extraordinaria. Lluvias de varias horas podrían repetirse Otro elemento importante es la posibilidad de que los episodios de lluvia tengan una duración considerable. Cuando existe un adecuado acoplamiento entre el océano y la atmósfera, el mar caliente puede continuar aportando humedad incluso después de una primera descarga. Esto puede favorecer un comportamiento caracterizado por periodos de lluvia, pausas y nuevas precipitaciones. La formación de nubes puede reactivarse mientras las condiciones cálidas y húmedas continúen presentes. En términos sencillos, una lluvia intensa no necesariamente terminaría después de una sola descarga. Si el océano continúa proporcionando humedad, podrían generarse nuevas etapas de precipitación durante el mismo episodio. ¿Qué regiones del Perú podrían recibir más lluvias? El impacto de El Niño Costero no sería uniforme en todo el territorio nacional. El calentamiento frente al litoral peruano favorece principalmente la ocurrencia de lluvias por encima de lo normal en la costa norte y central. Entre las regiones que concentran mayor atención se encuentran Tumbes, Piura y Lambayeque , aunque el escenario también comprende otros sectores de la costa central, incluida Lima. El Senamhi también ha señalado que durante los próximos meses la costa norte podría registrar precipitaciones superiores a lo normal, con posibles episodios de lluvia desde noviembre. Para el periodo septiembre-noviembre de 2026, además, se prevén temperaturas del aire muy superiores a los valores habituales en la costa peruana. El Niño también puede generar condiciones diferentes en la sierra sur Mientras el calentamiento frente a la costa puede favorecer lluvias por encima de lo normal en el norte y centro, las condiciones cálidas en el Pacífico Ecuatorial Central pueden tener un comportamiento distinto sobre otras zonas del país. Según la explicación proporcionada por el ENFEN, existe la posibilidad de que algunas zonas de la sierra sur presenten precipitaciones por debajo de lo habitual. Entre las regiones mencionadas figuran Puno, Cusco, Apurímac, Ayacucho y Arequipa, además de posibles efectos en Madre de Dios. De esta manera, el territorio peruano podría enfrentar simultáneamente escenarios diferenciados: mayor disponibilidad de lluvias en sectores de la costa norte y central y déficit de precipitaciones en determinadas áreas de la sierra sur. ¿Hasta cuándo podría durar El Niño Costero? El escenario previsto no se limita al inicio del verano. De acuerdo con el último reporte citado por el ENFEN, el El Niño Costero podría continuar hasta mediados del otoño de 2027, aproximadamente hasta abril, antes de iniciar una transición gradual hacia condiciones neutras. Para el verano, correspondiente al periodo diciembre de 2026-marzo de 2027, el comportamiento de las lluvias dependerá de cómo evolucionen las temperaturas del mar y el acoplamiento entre el océano y la atmósfera. El seguimiento de estos indicadores continuará a cargo del ENFEN y del Senamhi , cuyos comunicados y pronósticos permitirán actualizar el escenario conforme se acerquen los meses de mayor actividad lluviosa.</t>
+          <t>Precisó que, de acuerdo al Informe de Visita de Control n.° 015-2026-OCI/0084-SVC, cuyo período de evaluación fue del 19 al 25 de agosto de 2026, se identificó la presencia de aguas oleosas en la zona del rack principal de la Casa de Bombas 5 y del ex Separador API de la refinería de Talara, cuyas acciones previstas para su limpieza y recuperación se encuentran pendientes de culminación, lo que podría retrasar su atención.
+La comisión de control advirtió que, si no se realizan las labores de limpieza oportunamente, existe el riesgo de que el área con la contaminación por hidrocarburos podría expandirse hacia otras zonas de trabajo de la refinería ante la ocurrencia de lluvias intensas asociadas al fenómeno El Niño, con la consiguiente contaminación ambiental y posible afectación económica a la entidad.
+Lea también: Senamhi Piura advierte alta probabilidad de lluvias intensas desde noviembre por El Niño Tuberías en riesgo Los auditores de Contraloría también inspeccionaron el Oleoducto Overales, construido en 1975, correspondiente a una línea de transporte de crudo conformada por tuberías de acero instaladas en tramos sucesivos, con una longitud de 9340 metros, identificándose condiciones que requieren atención para preservar la integridad mecánica del ducto, relacionadas principalmente con el deterioro de soportes y bases de concreto, soportes parcialmente enterrados por acumulación de material, así como tramos de tubería sin apoyo visible sobre los elementos de soporte instalados, entre otras condiciones advertidas durante la inspección.
+El informe subraya que la falta de atención de las condiciones advertidas en el Oleoducto Overales podría incrementar la vulnerabilidad de la infraestructura frente a eventos climáticos asociados al FEN, debido a que la erosión, socavación o pérdida de capacidad de soporte del suelo podrían generar mayores desplazamientos, deformaciones o esfuerzos adicionales en los tramos con deficiencias en su sistema de apoyo.
+Esta situación afectaría la integridad mecánica del oleoducto y podría ocasionar restricciones operativas, fugas de crudo y consecuentes impactos ambientales y económicos.
+Infraestructura deteriorada Otra alerta de la Contraloría es que durante la inspección de la refinería se identificaron infraestructuras que presentan condiciones susceptibles de verse afectadas ante la ocurrencia de eventos asociados al FEN, con el consiguiente riesgo de afectar su operatividad y generar eventuales impactos económicos y ambientales para Petroperú.
+Lea también: Fenómeno El Niño: temperatura y sensación de calor en Piura superaría los 40 grados °C Al respecto, se visualizó que la infraestructura correspondiente a la nueva línea submarina cuenta con dos muros de contención a sus costados, los cuales presentan deterioro en su parte superior, evidenciándose fisuras y desprendimiento superficial del concreto, condición que podría afectar su función de protección ante la ocurrencia de eventos climáticos adversos.
+También se evidenciaron tramos de los canales de evacuación de aguas pluviales con presencia de lodos y vegetación en su interior.
+Además, se advierte que no se han adoptado acciones necesarias para el efectivo mantenimiento de las motobombas de la refinería, ya que el servicio contratado fue resuelto por incumplimientos del contratista.
+Esta situación podría comprometer la disponibilidad operativa de estos equipos para la atención de eventuales emergencias durante la ocurrencia del fenómeno El Niño, así como afectar la duración de la vida útil de las motobombas.
+La Contraloría recomendó comunicar estas situaciones adversas al presidente de Petroperú, con el objetivo de adoptar acciones que permitan proteger la infraestructura de la refinería de Talara ante los efectos climáticos del fenómeno El Niño.
+Más en Andina: #AndinaEnglish Peru: Inca closure ritual with 18 vessels and sacred huanca found in Wancasanga, Cajamarca https://t.co/oC5Wzw0Ohz pic.twitter.com/qQeSsRV6nz — Agencia Andina (@Agencia_Andina) September 18, 2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/el-nino-costero-podria-generar-lluvias-de-100-mm-por-dia-durante-el-verano/</t>
+          <t>https://andina.pe/agencia/noticia-advierten-posibles-riesgos-ambientales-refineria-petroperu-fenomeno-nino-1092334.aspx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Más de 10 mil casos de dengue en Piura; centros de salud, jalados</t>
+          <t>Incautan 100 armas y más de mil kilos de explosivos y pirotécnicos en 13 regiones</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aún no se inician las lluvias y el reporte de casos de dengue en la región es preocupante. Y es que hasta la semana epidemiológica 35, que finalizó el 5 setiembre, nuestra región registraba un acumulado de más de 10 mil casos en lo que va del año, posicionando a Piura como la región con más casos de dengue en el país, por encima de La Libertad, San Martín y Lambayeque. Lo más alarmante es que, de acuerdo al análisis realizado por la Red de Estudios para el Desarrollo (REDES) en el “Diagnóstico de Brechas de Infraestructura o Acceso a Servicios del Sector Salud 2028-2030”, hallaron que un 98% de establecimientos de salud del primer nivel de atención tiene capacidad instalada inadecuada. CIFRAS PREOCUPANTES Este porcentaje representa a los 440 establecimientos, de salud de un total de 449, que no cuentan con una infraestructura adecuada y de calidad para atender a sus pacientes. Según el informe, se trata principalmente de puestos, postas y centros de salud locales, que constituyen el primer punto de atención y los servicios más cercanos y accesibles para las distintas localidades de nuestra región. A ello se suma que 37 establecimientos del primer nivel de atención aún están pendientes de implementación. Germán Vega, economista de REDES, considera que en lo más importante es proteger la vida y salud de los pobladores, por lo que plantea tres prioridades: identificar las localidades más afectadas, fortalecer la prevención y reforzar el primer nivel de atención. “Desde una mirada económica, actuar a tiempo también permite evitar que los casos se agraven, reducir costos para las familias y aliviar la presión sobre el sistema de salud”, comentó el economista quien hizo énfasis en la prioridad que se le debe dar a Piura y Morropón, “donde ya se han registrado defunciones por dengue”. En la actualidad, la provincia de Piura es la que tiene más casos acumulados, es decir, es en donde más se está propagando esta enfermedad viral transmitida por la picadura de mosquitos infectados. Le sigue Morropón, Sullana, Ayabaca, Paita, Talara, Sechura y Huancabamba. Ante el incremento de casos Vega considera que se debe seguir fortaleciendo la capacidad de respuesta de los servicios de salud, especialmente para garantizar una atención oportuna y adecuada a los pacientes.</t>
+          <t>Estas intervenciones se realizaron en Áncash, Apurímac, Arequipa, Cajamarca, Cusco, Ica, Junín, La Libertad, Lambayeque, Loreto, Piura, Puno y Ucayali.
+Estas han permitido verificar las condiciones de seguridad en la tenencia de armas de fuego y prevenir la fabricación, almacenamiento, comercialización y uso de productos pirotécnicos y explosivos sin la autorización correspondiente.
+Como parte de este despliegue, las jefaturas zonales de Sucamec realizaron intervenciones a empresas de seguridad privada, usuarios de armas de fuego y establecimientos vinculados a las actividades de explosivos y productos pirotécnicos.
+Las incautaciones allí realziadas comprendieron 100 armas de fuego y 604 municiones, además de 734 kilos de productos pirotécnicos y 450 kilos de explosivos, informó el Ministerio del Interior.
+“Estamos intensificando la fiscalización en todo el país para detectar situaciones irregulares y evitar que armas, municiones, explosivos o productos pirotécnicos sean utilizados fuera de las condiciones establecidas por ley”, señaló el titular de la Sucamec, Eswin Manay Guerrero.
+[Lea también: Impulsan red de 7 puertos para garantizar abastecimiento de alimentos y ayuda ] El armamento intervenido en las empresas de seguridad presentaba que comprometían las condiciones exigidas para su custodia, entre ellas fallas en los sistemas de videovigilancia y alarmas, así como deficiencias en los registros de control y custodia.
+Asimismo, las fiscalizaciones a usuarios permitieron detectar armas vinculadas a licencias canceladas y vencidas.
+Asimismo, acciones que Sucamec efectuó junto a la Policía Nacional y la Superintendencia Nacional de Aduanas y de Administración Tributaria, permitieron detectar talleres que operaban de manera informal y materiales que eran trasladados clandestinamente.
+En ese contexto, se decomisaron 694 kilos de productos pirotécnicos en Junín y Áncash; además de 40 kilos en Lambayeque , durante una acción a una empresa que los iba a trasladar como encomienda.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/mas-de-10-mil-casos-de-dengue-en-piura-centros-de-salud-jalados/</t>
+          <t>https://andina.pe/agencia/noticia-incautan-100-armas-y-mas-mil-kilos-explosivos-y-pirotecnicos-13-regiones-1092369.aspx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cuidado con la automedicación en niños con dengue: podría agravar la enfermedad</t>
+          <t>El Niño: mar frente a Paita registra hasta 7 °C más de temperatura de lo normal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>El incremento de casos de dengue en la región ha encendido las alertas en los hogares, sobre todo por el caso de los menores de edad, donde muchas veces los padres de familias automedican a sus pequeños sin considerar que podrían agravar la enfermedad. Ante esta situación, el pediatra del Hospital III José Cayetano Heredia de la Red Asistencial Piura de EsSalud, Ricardo Olea Zapata, exhortó a los padres de familia a no automedicar a los niños. Explicó que, tras la picadura del mosquito transmisor, los síntomas pueden aparecer entre 7 y 14 días después del contagio, por ello recomendó estar atentos a cualquier signo de alarma. “Lo más importante es mantener al niño en reposo, brindarle abundantes líquidos y sueros rehidratantes para evitar la deshidratación”, señaló el médico, quien agregó que cuando un menor presenta fiebre asociada al dengue, el único medicamento recomendado es el paracetamol, ya que otros fármacos pueden generar complicaciones y no están indicados para estos casos. ACUDIR AL MÉDICO Olea Zapata indicó que si la fiebre no disminuye, se debe administrar la dosis de paracetamol prescrita por el médico y complementar el manejo con baños de agua tibia durante periodos prolongados, que pueden llegar hasta una hora, con el fin de ayudar a controlar la temperatura corporal. Advirtió que los padres deben acudir de inmediato al establecimiento de salud más cercano si el niño presenta signos de alarma.</t>
+          <t>Las consecuencias de El Fenómeno de El Niño ya se sienten en Piura. La temperatura del mar frente a Paita continúa por encima de sus valores normales y genera preocupación por el escenario de lluvias que podría enfrentar el norte del país durante el próximo verano. Rodolfo Rodríguez Arisméndiz, especialista de la Universidad de Piura (UDEP) y director de la Estación Científica Ramón Mugica, informó a la Agencia Andina que actualmente el mar frente a Paita registra entre 24 °C y 25 °C, cuando lo habitual para esta época del año es encontrar temperaturas de entre 17 °C y 18 °C. Esto representa una anomalía positiva de entre 6 y 7 grados, una diferencia considerable que, de mantenerse, podría tener efectos sobre las condiciones climáticas de los próximos meses. Según explicó el especialista, cuando la temperatura del mar supera los 25 °C se genera un escenario más favorable para la formación de lluvias, aunque la ocurrencia e intensidad de las precipitaciones también depende de otros factores atmosféricos. El punto de preocupación está en que estas temperaturas elevadas se están registrando todavía durante el invierno. Rodríguez advirtió que, con la llegada del verano, el calentamiento propio de la temporada podría sumarse a las actuales condiciones del mar y elevar aún más las anomalías. “Probablemente tengamos lluvias fuertes, principalmente en los meses del verano del 2027”, señaló. El especialista explicó que el comportamiento actual debe ser tomado como una señal de alerta y seguimiento frente a un posible escenario de lluvias intensas asociado a las condiciones cálidas del mar propias del desarrollo del Fenómeno El Niño. Rodríguez consideró que las autoridades ya no deberían concentrarse únicamente en el diagnóstico, sino avanzar en medidas de prevención y mitigación a los efectos adversos de intensas lluvias. En su opinión, la preparación debe involucrar acciones a nivel vecinal, municipal, Gobierno Regional y Gobierno Nacional, con acciones destinadas a reducir los posibles impactos de un periodo lluvioso intenso. La preocupación también se refleja en la sensación térmica que experimenta la población. Piura viene atravesando un invierno inusualmente cálido, con temperaturas que generan una sensación más propia de los meses de verano. Sostuvo que las próximas semanas serán importantes para conocer cómo evoluciona la temperatura del mar y, con ello, evaluar con mayor precisión el escenario que podría presentarse durante el verano de 2027.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/cuidado-con-la-automedicacion-en-ninos-con-dengue-podria-agravar-la-enfermedad/</t>
+          <t>https://gestion.pe/peru/el-nino-en-piura-mar-frente-a-paita-registra-hasta-7-c-mas-de-temperatura-de-lo-normal-noticia/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Descolmatación no reduce riesgo de una inundación en Piura, cuestiona ingeniero hidráulico</t>
+          <t>Piura implementará medidas para proteger a turistas ante posibles impactos del fenómeno El Niño</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Andrés Farfán, ingeniero hidráulico, no solo cuestionó la lentitud con la que avanzan los trabajos de descolmatación en el río Piura sino que los más de 600 mil metros cúbicos que se proyectan retirar de sedimentación no reduce el riesgo de una posible inundación. En esa línea cuestionó que el Ejecutivo se proyecte recuperar una capacidad de caja hidráulica de 3,900 metros cúbicos por segundo (m3/s). “Ellos están hablando de 3,900. El gran error es que por aquí pasan 4,000 m3 cuando el cauce está totalmente descolmatado. Con esta mitigación, ¿qué pasa? Entre 1,900 y 2,000. Yo le calculo máximo puede ser 2,200. Estamos condenados a inundarnos si las labores continúan en las condiciones actuales”, afirmó. Finalmente advirtió que entre la represa Los Ejidos y el puente Bolognesi se ha previsto realizar trabajos de descolmatación en una distancia de 4.8 kilómetros; sin embargo, dijo que como van solo llegarían al 50%.</t>
+          <t>La Red de Protección al Turista de Piura acordó implementar una serie de medidas para proteger el flujo de visitantes y reducir los posibles impactos del fenómeno El Niño en la región. La estrategia es encabezada por el Gobierno Regional de Piura, a través de la Dirección Regional de Comercio Exterior y Turismo (Dircetur). Entre las acciones previstas se encuentra un plan de respuesta sanitaria coordinado con la Dirección Regional de Salud (Diresa), que permitirá atender eventuales emergencias asociadas al fenómeno climático. También se implementará un sistema de comunicación oficial por provincias, con información diferenciada entre eventos climáticos estacionales y alertas nacionales. En materia de seguridad, se contempla la activación de brigadas de rescate rápido para atender emergencias y reforzar la protección de visitantes nacionales y extranjeros. Además, la Dirección de Aeródromos y Puertos y la Capitanía de Puerto participarán en la supervisión de las embarcaciones que operan en las zonas balnearias. La Policía de Turismo y la Policía Nacional del Perú incrementarán la vigilancia en muelles, corredores turísticos y principales atractivos de la región. Estas acciones se complementarán con medidas para fortalecer la seguridad marítima. Otro de los ejes será la formalización y certificación de los servicios turísticos. Para ello, se iniciará un proceso de capacitación dirigido a los gremios de transporte local y se entregarán distintivos oficiales a los operadores que cumplan con los estándares establecidos de seguridad y atención. Asimismo, se habilitará un directorio público, tanto físico como digital, con información de los operadores turísticos e intermediarios formales. La herramienta permitirá a los visitantes identificar los servicios disponibles en la región. La Red también acordó reforzar los mecanismos de fiscalización y recepción en los puntos de ingreso a Piura, con especial atención al mercado ecuatoriano, uno de los mercados emisores relevantes para el turismo receptivo de la región. La medida busca contribuir a mantener el flujo de visitantes procedentes de Ecuador y brindar condiciones de seguridad durante su ingreso y permanencia. Por su parte, la Diresa tendrá a su cargo la difusión de alertas sanitarias verificadas y la coordinación para garantizar atención médica ante eventuales contingencias relacionadas con el fenómeno El Niño. También se implementará un directorio de emergencias disponible las 24 horas y un canal digital oficial con información verificada por provincia. Finalmente, la Red de Protección al Turista acordó ampliar su convocatoria a las cámaras de comercio locales, municipalidades provinciales, la Junta de Fiscales Superiores y gremios privados. La finalidad es establecer mesas de trabajo técnicas para atender las necesidades específicas de cada zona turística de Piura.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/descolmatacion-no-reduce-riesgo-de-una-inundacion-en-piura-cuestiona-ingeniero-hidraulico/</t>
+          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-piura-implementara-medidas-para-proteger-a-turistas-ante-posibles-impactos-ultimas-noticia/</t>
         </is>
       </c>
     </row>
@@ -1492,21 +1664,21 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Con protesta, piuranos exigen a Keiko cumplir con transferencias</t>
+          <t>Piura es la tercera región del país con más violencia escolar con 135 casos</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>El 3 de setiembre pasado, la presidenta de la República, Keiko Fujimori, se comprometió a “destrabar” cinco proyectos paralizados en Piura, debido al incumplimiento de una transferencia de 41 millones de soles por parte del Ministerio de Vivienda, y hasta la fecha no se cumple con el ofrecimiento. Ello ha conllevado a que aún no se puedan reactivar los proyectos de las avenidas avenida B-D, Los Educadores, Túpac Amaru, Los Almendros y Urb. Piura. Ante esta situación, ayer dirigentes de los sectores afectados realizaron una protesta en los exteriores de las oficinas del Ministerio de Vivienda, en la Urb. Los Cocos en Piura, para exigir a la mandataria cumpla con su palabra y las obras puedan ser culminadas antes del inicio de las lluvias. Milagros Orihuela, secretaria general del asentamiento 4 de Octubre, indicó que de persistir la demora convocarán a toda la población a una masiva marcha de protesta en las calles.</t>
+          <t>La presunta agresión sexual que habría sufrido un escolar de 16 años en un colegio de Lima, con implicación de diez compañeros del quinto de secundaria, ha encendido las alertas en diversas regiones: Piura, por ejemplo, se encuentra entre las tres regiones de todo el país con más casos de violencia sexual y escolar. El diputado por Piura, Miguel Huamán Cornejo, informó que entre enero a agosto de 2026, según el reporte del sistema SíseVe del Ministerio de Educación, en Piura se han registrado 692 reportes de violencia escolar, ubicándola en el tercer lugar nacional, después de Lima Metropolitana y Arequipa. El diputado señala que estas cifras corresponden a reportes registrados en la plataforma y no necesariamente equivalen al mismo número de víctimas o hechos distintos. Advierte también sobre los 135 reportes de violencia sexual escolar registrados en Piura durante el mismo periodo, de acuerdo con las cifras proporcionadas. “135 reportes de violencia sexual contra escolares no pueden convertirse en una estadística más. Detrás de cada denuncia existe un menor que necesita protección y una respuesta inmediata del Estado. Tenemos que saber dónde están ocurriendo estos hechos, qué protocolos se están aplicando y si realmente están funcionando”, señaló. PIDE INFORMES Ante esta situación, el diputado anunció que solicitará información oficial a la Dirección Regional de Educación y a las UGEL Piura sobre las instituciones educativas con mayor incidencia de reportes, los protocolos activados, las medidas de prevención implementadas y el seguimiento de los casos. Asimismo, planteó fortalecer la articulación entre el Ministerio de Educación (Minedu), Ministerio de Salud (Minsa) y Ministerio de la Mujer y Poblaciones Vulnerables (MIMP)para reforzar la prevención y atención de la violencia contra niños y adolescentes. “Lo ocurrido en Lima podría estar ocurriendo también en algún colegio de Piura sin que todavía lo sepamos. Ningún estudiante debe sentirse desprotegido dentro de una institución educativa. Los colegios tienen que ser espacios seguros, no lugares donde el miedo y el silencio terminen protegiendo la violencia”, enfatizó Miguel Huamán Cornejo.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/con-protesta-piuranos-exigen-a-keiko-cumplir-con-transferencias/</t>
+          <t>https://eltiempo.pe/local/reportan-135-casos-de-violencia-sexual-escolar-en-piura/</t>
         </is>
       </c>
     </row>
@@ -1517,21 +1689,21 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vecinos de Consuelo de Velasco padecen por agua: exigen solución a EPS Grau</t>
+          <t>Pronied continuará obra del colegio ‘Salaverry’ en Sullana</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cansados de estar fungiendo de “topos” o acudir a los domicilios de vecinos o familiares para abastecerse de agua potable, ayer un grupo de vecinos del asentamiento Consuelo de Velasco realizaron una protesta en su jurisdicción para exigir a la EPS Grau una solución inmediata a la falta de agua en el lugar. Señalan que el agua no les llega a sus caños; en otros casos llega, pero solo por media hora; y en otros casos tienen que hacer huecos o comprar bidones de agua dada la falta de agua. Refieren que, en los últimos 15 días, la situación ha sido más crítica, por ello exigen la intervención de las autoridades. Además, denuncian que los recibos siguen llegando y encima les cobran reposición del servicio, pese a no contar con el mismo.</t>
+          <t>El Gobierno Regional de Piura ya no tendrá a su cargo la culminación de la obra del colegio emblemático “Carlos Augusto Salaverry”, como se había anunciado meses atrás. El Programa Nacional de Infraestructura Educativa (Pronied) del Ministerio de Educación, decidió continuar el proyecto y será esta entidad la que culmine el proceso para hacer realidad la esperada infraestructura educativa, la misma que lleva 11 años El diputado sullanero Eduardo Castillo señaló que, tras una reunión con representantes de Pronied, se confirmó que la obra será ejecutada bajo la modalidad de diseño-construcción. Según explicó, actualmente se encuentra en la elaboración final de los términos de referencia, documento que permitirá avanzar con la convocatoria para la elaboración del nuevo expediente técnico y su posterior ejecución. Este cambio se produce luego de los inconvenientes registrados con el proceso anterior. La empresa que tenía a su cargo la elaboración del expediente técnico no cumplió con los plazos establecidos de los entregables, además éstos registraban observaciones, por lo que se tomó la decisión de resolver el contrato. El proyecto se deberá encaminar el evitar que la obra continúe paralizada.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/vecinos-de-consuelo-de-velasco-padecen-por-agua-exigen-solucion-a-eps-grau/</t>
+          <t>https://eltiempo.pe/local/pronied-continuara-obra-del-colegio-salaverry-en-sullana/</t>
         </is>
       </c>
     </row>
@@ -1542,21 +1714,21 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Piura será un horno por El Niño: soportará 42°C de sensación de calor</t>
+          <t>Detienen a un docente: lo acusan de presuntos tocamientos indebidos</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Los piuranos deberán tomar sus precauciones para las altas temperaturas que se avecinan. Y es que el especialista en Vigilancia Meteorológica del Senamhi, Nelson Quispe Gutiérrez, informó que la temperatura en Piura podría llegar a los 40 grados Celsius (104 grados Fahrenheit) de temperatura real. Explicó que el incremento de la temperatura es propiciado por el Fenómeno El Niño (FEN), el cual se dará con mayor intensidad en la costa norte. “Y no solamente eso, sino que, aunada a la humedad que va a haber, la sensación de calor que uno podrá percibir en esta zona sería alrededor de los 42 grados Celsius”, refirió Quispe en declaraciones a Andina. SERÁ UN ‘HORNO’ Quispe proyectó que las temperaturas seguirán en aumento hacia finales de año y comienzos del 2027, con los registros más altos esperados entre los meses de febrero y marzo, según indicó a la agencia estatal. Por ello consideró que los niños y adultos mayores deben merecer especial atención en aras de evitar consecuencias negativas en su salud durante los próximos meses. “Esto definitivamente creará un shock”, advirtió el especialista del Senamhi, quien precisó que dicho efecto puede manifestarse con solo caminar por las calles en medio del calor, con las consecuencias perjudiciales que ello implica para la salud de la población. EXTRAORDINARIA Mientras tanto, el Enfen a través de Comunicado Oficial N.° 16-2026, emitido el 14 de setiembre, establece que El Niño Costero, correspondiente a la región Niño 1+2, presenta la mayor probabilidad de alcanzar una magnitud extraordinaria entre setiembre de 2026 y enero de 2027. Para febrero y marzo, según señalan, sería el escenario más probable y se ubica entre una magnitud fuerte y extraordinaria. LLUVIAS FUERTES El pronóstico del Enfen ubica a la costa norte como una de las zonas con mayor probabilidad de precipitaciones superiores a lo normal. Desde noviembre podrían registrarse episodios de lluvias de moderada a fuerte intensidad, donde incluso podría superar los promedios históricos. CERCA DE 9 MIL CASOS Con el anuncio se lluvias se teme el incremento de casos de dengue. A la fecha, se registran en Piura un total de 8,958 casos de dengue y 6 defunciones en lo que va del año, según el reporte de la Semana Epidemiológica 33. Por ello, la Defensoría del Pueblo demandó con carácter de urgencia al gobernador Luis Neyra priorizar acciones urgentes contra el dengue.</t>
+          <t>Un docente fue aprehendido por agentes de la comisaría de Talara Baja luego de ser denunciado por presuntos tocamientos indebidos contra una escolar del nivel secundario. El profesor fue conducido a la delegación donde es investigado en presencia de un representante del Ministerio Público. La intervención policial ocurrió cerca de las 11:30 de la mañana de ayer, luego que una madre de familia de la institución educativa Santa Rosa de Lima denunciara al profesor identificado con las iniciales A. V. S., de haber realizado tocamientos a su hija de 16 años cuando realizaba sus prácticas dentro del aula. NARRA LO SUCEDIDO La madre de la alumna, en el momento de sentar la denuncia, contó a los investigadores que su hija, quien cursa el cuarto año del nivel secundario en la conocida institución educativa talareña, le confesó lo ocurrido. También declaró que, tras informar del supuesto hecho a las autoridades de la escuela, el docente fue separado de inmediato de sus labores, emitiendo la dirección la advertencia, a través de un informe, a la UGEL Talara, para que tome cartas en el asunto. SINDICATO SEÑALA QUE ES INOCENTE Tras la intervención y las primeras diligencias, se tuvo conocimiento que el sindicado había sostenido en todo momento su inocencia ante las autoridades policiales y del Ministerio Público, indicando desconocer el por qué la escolar y la madre de familia lo habían denunciado, por el delito mencionado.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-sera-un-horno-por-el-nino-soportara-42c-de-sensacion-de-calor/</t>
+          <t>https://eltiempo.pe/local/detienen-a-un-docente-lo-acusan-de-presuntos-tocamientos-indebidos/</t>
         </is>
       </c>
     </row>
@@ -1567,44 +1739,444 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bajo Piura en riesgo: reportan 14 puntos críticos sin obras</t>
+          <t>Piura activa medidas de protección al turista ante posibles impactos del fenómeno El Niño</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Víctor Chunga, del Frente de reconstrucción de los pueblos afectados del Bajo Piura por el Niño Costero, lamentó que, según información del Ministerio de Defensa, solo se esté considerando atender ocho puntos críticos en Piura, cuando solo el Bajo Piura tiene 14 puntos críticos por atender. Explicó que esa situación pone en riesgo al Bajo Piura dado que no cuentan con obras de prevención frente al riesgo de desborde e inundación en el marco del anuncio de un Fenómeno El Niño de magnitud “extraordinaria”. Entre los puntos críticos desprotegidos estarían Las Dos Ánimas, Chato Chico, La Joya, entre otros. Asimismo, lamentó que a la fecha solo sigan trabajando siete máquinas, lo cual considera insuficiente.</t>
+          <t>Piura prepara una serie de medidas para proteger a los visitantes nacionales y extranjeros ante los posibles impactos del fenómeno El Niño. La estrategia fue acordada por la Red de Protección al Turista , a través de la Dirección Regional de Comercio Exterior y Turismo (Dircetur). El plan contempla acciones relacionadas con seguridad, atención sanitaria, comunicación de alertas, supervisión de embarcaciones, formalización de operadores y vigilancia en los principales puntos turísticos de la región. Según el Gobierno Regional de Piura, las medidas buscan reducir los riesgos que podrían afectar la actividad turística y establecer mecanismos de respuesta ante eventuales emergencias vinculadas a las condiciones climáticas. Piura prepara un plan de protección para los turistas Uno de los principales acuerdos consiste en implementar un plan de respuesta sanitaria coordinado con la Dirección Regional de Salud (Diresa). Esta medida permitirá establecer mecanismos de atención ante posibles emergencias que puedan presentarse durante episodios relacionados con el fenómeno El Niño. Para ello, se plantea reforzar la coordinación entre las instituciones responsables de la salud y los organismos vinculados con el turismo. El objetivo es que los visitantes puedan contar con atención ante una eventual contingencia durante su permanencia en la región. La estrategia también considera la creación de un sistema de comunicación oficial por provincias . La información será diferenciada para evitar confusiones entre los eventos climáticos propios de cada temporada y las alertas nacionales emitidas por las autoridades competentes. El Senamhi es una de las entidades oficiales que emite información y alertas relacionadas con las condiciones meteorológicas e hidrológicas del país. Seguridad para visitantes nacionales y extranjeros Dentro de las medidas previstas se encuentra la activación de brigadas de rescate rápido para atender situaciones de emergencia. Estas unidades tendrán como finalidad responder ante posibles incidentes que involucren a turistas en diferentes zonas de la región. La seguridad también será reforzada en los espacios vinculados con el turismo marítimo. La Dirección de Aeródromos y Puertos y la Capitanía de Puerto participarán en la supervisión de las embarcaciones que operan en las principales zonas balnearias de Piura . De acuerdo con lo planteado por la Red de Protección al Turista, esta vigilancia permitirá verificar las condiciones de operación de las embarcaciones y contribuir a reducir riesgos para quienes utilizan estos servicios. A estas acciones se sumará la participación de la Policía de Turismo y la Policía Nacional , que incrementarán la vigilancia en muelles, corredores turísticos y principales atractivos de la región. ¿Qué zonas turísticas tendrán mayor vigilancia? La vigilancia estará enfocada principalmente en espacios con concentración de visitantes, como muelles, corredores turísticos y atractivos de la región. También se contempla reforzar los controles en puntos relacionados con el ingreso y desplazamiento de turistas. La finalidad es que las instituciones involucradas puedan responder con mayor rapidez ante cualquier emergencia y brindar orientación a los visitantes. Piura busca aumentar la formalización de los operadores turísticos Otro de los componentes del plan está relacionado con la formalización y certificación de los servicios turísticos . La iniciativa contempla desarrollar capacitaciones dirigidas a los gremios de transporte local. Como parte de este proceso se prevé entregar distintivos oficiales a los operadores que cumplan con los estándares establecidos en materia de seguridad y atención. La identificación de los prestadores formales busca facilitar que los turistas puedan reconocer los servicios que cuentan con la documentación y las condiciones requeridas por las autoridades. Además, se habilitará un directorio público de operadores turísticos e intermediarios formales . Este registro tendrá una versión física y otra digital para que los visitantes puedan consultar información antes de contratar determinados servicios. Para el sector turístico, contar con información accesible sobre los prestadores formales resulta especialmente importante durante periodos en los que las condiciones climáticas pueden modificar el funcionamiento de determinadas actividades. Refuerzo del turismo procedente de Ecuador La estrategia de protección también considera el movimiento turístico procedente de Ecuador. La Red de Protección al Turista acordó fortalecer los mecanismos de fiscalización y recepción en los principales puntos de ingreso a la región. El mercado ecuatoriano es considerado uno de los mercados emisores relevantes para el turismo receptivo de Piura . Por ello, las autoridades plantean mejorar las condiciones de ingreso y permanencia de estos visitantes. La medida contempla una mayor coordinación en los puntos de ingreso, con el propósito de facilitar la orientación de los turistas y mantener el flujo de visitantes procedentes del vecino país. La información oficial sobre servicios y orientación turística puede ser consultada a través de Mincetur , entidad responsable de las políticas nacionales relacionadas con comercio exterior y turismo. Información sanitaria y alertas oficiales ante El Niño La Diresa Piura tendrá un papel central en la difusión de información sanitaria verificada. La entidad deberá coordinar la atención médica ante eventuales contingencias asociadas con el fenómeno El Niño. La estrategia incluye además la implementación de un directorio de emergencias disponible las 24 horas . Este recurso permitirá centralizar información de contacto para situaciones que requieran una respuesta inmediata. También se habilitará un canal digital oficial para difundir información diferenciada por provincia. La intención es que los turistas y operadores puedan acceder a datos verificados y evitar la circulación de información no confirmada durante eventuales emergencias. Según las autoridades, la comunicación será uno de los elementos centrales del plan, debido a que las condiciones pueden variar entre las distintas zonas de la región. ¿Qué instituciones participarán en la protección al turista? La respuesta contempla la participación coordinada de diferentes entidades públicas y privadas. Además del Gobierno Regional de Piura, Dircetur y Diresa, se considera la intervención de organismos relacionados con seguridad, transporte marítimo y atención de emergencias. La Red de Protección al Turista acordó ampliar su convocatoria a las cámaras de comercio locales, municipalidades provinciales, la Junta de Fiscales Superiores y gremios privados . La propuesta es establecer mesas de trabajo que permitan identificar las necesidades particulares de cada zona turística y definir acciones específicas frente a posibles escenarios derivados del fenómeno climático. ¿Para qué servirán las mesas de trabajo en Piura? Las mesas permitirán coordinar acciones entre autoridades, empresas y organizaciones vinculadas con la actividad turística. De acuerdo con la estrategia planteada, cada provincia podrá abordar sus propias necesidades en materia de seguridad, salud, información y atención a los visitantes. El enfoque busca que la respuesta no se limite a una sola institución y que los operadores turísticos también participen en las medidas preventivas. La información sobre alertas meteorológicas y condiciones climáticas deberá mantenerse vinculada a los reportes de las instituciones oficiales. En ese sentido, los visitantes pueden consultar los canales del Instituto Nacional de Defensa Civil (Indeci) y del Senamhi para conocer las recomendaciones y avisos emitidos por las autoridades.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/bajo-piura-en-riesgo-reportan-14-puntos-criticos-sin-obras/</t>
+          <t>https://eltiempo.pe/local/piura-activa-medidas-de-proteccion-al-turista-ante-posibles-impactos-del-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sicarios en moto matan de 6 balazos a un ‘gota-a-gota’ en Veintiséis de Octubre</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sicarios motorizados, a plena luz del día, volvieron a desatar terror en las calles, luego de asesinar de seis balazos a un cobrador extranjero del “gota-a-gota”. Los gatilleros tras ver caer a su objetivo se dieron a la fuga en una motocicleta. El homicidio ocurrió cerca de las tres de la tarde de ayer en el asentamiento Rosa de Guadalupe, Mz. K, en Veintiséis de Octubre, cuando Julián Andrés Agudelo Rivera, de 22 años, de nacionalidad colombiana, se había estacionado, frente a una vivienda para realizar una cobranza, llegó una motocicleta. Lo acribillan El sujeto que iba como pasajero, con arma de fuego en mano, le descargó seis tiros en el pecho y espalda, que acabaron con la vida en contados minutos con el ciudadano colombiano. El estruendo de los disparos alarmó a los vecinos, los mismos que al salir a la calle encontraron el cuerpo del extranjero. Se dice que los gatilleros merodearon por la zona por varios minutos a la espera del cobrador a fin de perpetrar el feroz ataque. Todo fue ran rápido, que el cobrador dekl “gota-a-gota” no tuvo tiempo para ponerse a buen recaudo. Llega la Policía Peritos de la Oficina de Criminalística (Oficri) de la Divincri Piura y fiscal provincial Imazuma Córdova Reyes de la Fiscalía Provincial de Turno de Piura, alertados de lo ocurrido, llegaron hasta la zona para la diligencia del levantamiento del cuerpo y traslado a la morgue de Piura para la necropsia de ley. Aunque la Policía realizó un intenso operativo en busca de los gatilleros no fue posible su ubicación y captura. Se presume que el móvil del ataque sería por la pugna por el control de los préstamos infornales en la zona.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sicarios-en-moto-matan-de-6-balazos-a-un-gota-a-gota-en-veintiseis-de-octubre/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Se realiza Simulacro de incendio forestal en Santa Julia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>La Oficina Regional de Seguridad y Defensa Nacional anunció que hoy se realizará el segundo simulacro regional de incendio forestal a partir de las 11:00 en Santa Julia. Informaron que este simulacro tiene como propósito sensibilizar a la población que vive en sectores aledaños a la zona cero, respecto al tratamiento y quema de basura y la contaminación que genera al ecosistema. Cabe señalar que la ejecución de este ejercicio está normado por la resolución N° 001-2025 de la Secretaría de Gestión del Riesgo de Desastres de la PCM, que establece que durante los años 2025 – 2027, los gobiernos regionales deben programar dos simulacros regionales para la ocurrencia de un incendio forestal. ECOSISTEMA FRÁGIL Los humedales de Santa Julia, ubicados en el distrito Veintiséis de Octubre, son un ecosistema costero frágil caracterizado por la presencia de uno o varios espejos de agua, abundante vegetación, así como una alta diversidad de aves. Se estima que un incendio en esta zona afectaría la flora, la fauna el medio ambiente así como a las familias que han levantado sus viviendas en las zonas adyacentes.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/se-realiza-simulacro-de-incendio-forestal-en-santa-julia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cura Mori exige obras de emergencia: responsabilizarán a autoridades de daños</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ante la falta de obras de mitigación y el riesgo existente por posibles inundaciones, la Plataforma Distrital de Defensa Civil de Cura Mori, así como el Grupo de trabajo de gestión del riesgo de desastres y la sociedad civil emitieron un pronunciamiento público para denunciar que los trabajos de descolmatación y protección del río Piura continúan siendo insuficientes en puntos críticos del Bajo Piura, especialmente en Cura Mori. Advierten que los sectores de la margen izquierda del río Piura se encuentran en peligro debido al colapso y deterioro de las geobolsas instaladas anteriormente y a la falta de reforzamiento de las defensas ribereñas. Por ello exigen una intervención integral e inmediata para proteger a la población, “incluyendo descolmatación” en puntos críticos, reforzamiento de la margen izquierda; y ampliación y recuperación de la caja hidráulica del cauce, entre otras demandas. Finalmente advierten que de producirse daños y pérdidas humanas por la falta de atención oportuna, evaluarán el inicio de acciones legales contra las autoridades responsables.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cura-mori-exige-obras-de-emergencia-responsabilizaran-a-autoridades-de-danos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>La zona más calurosa del Perú: emblemática localidad del norte rozó los 40 °C por El Niño Costero</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>En Perú, diversos distritos de Lima y otras regiones experimentan altas temperaturas con presencia de humedad, lloviznas y fuertes vientos vinculados al Fenómeno El Niño. Así, en medio del impacto de este evento climático, el Centro Nacional de Estimación, Prevención y Reducción del Riesgo de Desastres (Cenepred) alertó que más de 20 millones de peruanos se encuentran en grave riesgo ante posibles desastres que podrían arrasar con viviendas y otras infraestructuras. En ese sentido, el Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que una zona costera del país registró una temperatura máxima y con una mayor exposición a la radiación ultravioleta que puso en alerta a tanto a las autoridades locales como a los pobladores. En el desarrollo de esta nota, te contamos mayores detalles al respecto. A través de sus plataformas oficiales, el Servicio Nacional de Meteorología e Hidrología del Perú anunció que la ciudad de Chulucanas, en Piura, registró el pasado 15 de septiembre temperaturas de hasta 38 °C, asociadas a la presencia del Fenómeno El Niño. De hecho, durante una jornada marcada por un calor extremo, otras regiones como Tumbes, Piura, Lambayeque, La Libertad, Áncash, Lima, Ica, Arequipa y Moquegua también registraron altas temperaturas. Así, de acuerdo con el Senamhi, las temperaturas diurnas elevadas se mantendrán hasta el sábado 19 de septiembre, con niveles de moderados a extremos de 29 °C y 36 °C en la costa y de moderados a fuertes en la sierra. A través del Decreto Supremo n.° 124-2026-PCM, publicado en el diario oficial El Peruano, el Poder Ejecutivo aprobó el estado de emergencia en 893 distritos del país ante el riesgo de intensas lluvias asociadas al Fenómeno El Niño. Esta medida, que tendrá una vigencia de 60 días calendario, responde a las evaluaciones del ENFEN, que proyectan un escenario con características similares a las registradas durante el fenómeno de 1997. En este contexto, se espera que las precipitaciones alcancen niveles críticos en la costa y la sierra entre noviembre y diciembre de este año. Por consiguiente, la declaratoria comprende a distritos de Amazonas, Áncash, Apurímac, Arequipa, Ayacucho, Cajamarca, Huancavelica, Huánuco, Ica, Junín, La Libertad, Lambayeque, Lima, Loreto, Madre de Dios, Moquegua, Pasco, Piura, San Martín, Tacna, Tumbes, Ucayali y Callao. Así, durante el periodo que dure la emergencia, las autoridades regionales y locales del país podrán implementar medidas destinadas a reducir los riesgos y atender eventuales daños. Según el decreto, estas acciones serán financiadas con sus propios presupuestos, sin contar con recursos adicionales provenientes del Tesoro Público, conforme comparte Perú 21.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/respuestas/donde/la-zona-mas-calurosa-del-peru-emblematica-localidad-del-norte-rozo-los-40-c-por-el-nino-costero-tdpe-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gas natural, más allá de Camisea y el ducto de TGP: ¿Qué alternativas existen para reducir la dependencia de una sola fuente?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Seis meses han transcurrido desde el último siniestro en el gasoducto de TGP, accidente – aún no aclarado - que ocasionó la catástrofe energética más grande en lo que va del siglo XXI en el Perú. Pasado ese lapso, sin embargo, no se ha tomado ninguna acción preventiva ni correctiva. Esto, “a pesar de que todos los expertos, incluyendo a los funcionarios del mismo Osinergmin” han señalado que la infraestructura que tenemos para el transporte de gas natural y líquidos de gas natural (LGN) es “precaria”, apunta Víctor Murillo, ex viceministro de Hidrocarburos. “Esta es la rotura número doce o trece en el ducto de TGP, y va a volver a ocurrir. ¿Pero, qué haremos con la siguiente?”, se pregunta Luis Espinoza, ex viceministro de Energía. Y es que lo acontecido en marzo pasado ha puesto de manifiesto que el país no puede depender de un solo gasoducto de transporte por los problemas que ya presenciamos durante esos trece aciagos días, empezando por la restricción a ‘cero’ del suministro de gas para industrias, plantas de generación térmica y taxis; siguiendo con la escasez de GLP (y hasta de diésel) registrada en ese lapso; y terminando con el retroceso que todo esto significó para el PBI, además de la escalada en la inflación. Igualmente importante, la tragedia ha develado que el Perú tampoco puede seguir dependiendo de un gran yacimiento de gas, en este caso, de Camisea (Cusco) - epicentro desde donde se despacha el 96% del gas natural y el 70% del GLP que se consume internamente – apunta Carlos Bianchi, presidente de la Sociedad Geológica del Perú. De allí, el llamamiento efectuado por el Instituto Peruano de Ingenieros de Gas, Petróleo y Energía (IPIGPE) en abril pasado para que adoptemos una estrategia de diversificación de fuentes (yacimientos) e infraestructura de transporte (ductos) de gas natural, aprovechando las importantes reservas y recursos prospectivos de hidrocarburos con que cuenta el país. Es el caso, de las cuencas de Tumbes y Talara; de las grandes cuencas amazónicas como el Huallaga, el Marañón, Ucayali y Madre de Dios; del off-shore en el norte del país, y hasta de la cuenca del Altiplano (Titicaca), apunta Víctor Sanz, vicepresidente del IPIGPE. No solo eso, Bianchi considera que existe una posibilidad muy interesante para el descubrimiento de gas en los lotes exploratorios Z-62, Z-63 y Z-64, frente a las costas de La Libertad, Lambayeque y Ancash, los cuales estuvieron hace muy poco en el ojo de la tormenta tras la decisión de Chevron de retirarse del área principal del proyecto. A entender del geólogo, el proyecto no ha sido abandonado pues sigue siendo liderado por Anadarko, empresa que se ha comprometido a perforar un pozo exploratorio en el lote Z-62, tras lo cual vendrían dos más. “Si es petróleo lo que descubren, lo sacarían en barcazas por Chiclayo. Y si, además, descubren gas, tendrían que implementar una pequeña planta en el litoral, la cual podría convertirse en una especie de nodo energético”, señala. Hasta que ello ocurra pasarán, sin embargo, varios años más. Mientras tanto, el país seguirá dependiendo de un solo yacimiento (Camisea) y de un solo gasoducto (de TGP). “¿Tenemos una situación distinta en términos de infraestructura y seguridad? No. Si hay otra situación parecida [a la de marzo] el riesgo es el mismo. Estamos siempre expuestos a eso y a las consecuencias que ya conocemos”, advierte Murillo. ¿Qué se debería hacer en el corto o mediano plazo? Cuando la rotura del ducto de TGP empezó a afectar a la capital, en marzo pasado, el gobierno transitorio de José Balcázar anunció que impulsaría la construcción de “una planta de regasificación en la costa, a fin de que nunca más tengamos estos problemas”. Una vez que se ‘apagó el incendio’, sin embargo, no se hizo más nada, y “así hasta que todo vuelva a explotar, porque se trata de una bomba de tiempo de un nivel similar al de El Fenómeno El Niño”, indica Freddy Morales, presidente del IPIGPE. A decir del especialista, este Gobierno tiene la posibilidad de concretar el planteamiento de Balcázar, pues se trata de una infraestructura que puede ser planificada y construida en un lapso de tres a cuatro años. La obra permitiría reconvertir a su estado original un porcentaje del gas natural líquido (GNL) almacenado en Pampa Melchorita, a fin de que pueda ser distribuido en Lima y Callo en situaciones de emergencia. “Este debe ser uno de los proyectos de hidrocarburos prioritarios para el Perú en el mediano y largo plazo en el país”, anota Morales. A decir de Murillo, se trata de un proyecto que puede ser costoso para el Estado pero que “siempre será menos caro que producir energía con diésel”. Espinoza considera, sin embargo, que la planta de regasificación solo resolverá la mitad de los problemas asociados a una nueva paralización del ducto de TGP, porque dicha solución apunta específicamente al tema del gas cuando “las estadísticas demuestran que todos los accidentes registrados en los últimos 22 años han ocurrido en el ducto de líquidos”. De allí, la necesidad de construir un nuevo tubo de LGN. Por lo pronto, lo que el Minem y el Gobierno vienen proponiendo para mitigar la dependencia del país en torno a Camisea es la exploración y desarrollo de fuentes alternativas de gas natural, empezando por el área del Cándamo (Puno-Madre de Dios) donde en la década de los 90’ la petrolera Mobil descubrió 3,6 trillones de pies cúbicos (TCF) del preciado hidrocarburo - equivalentes a ocho veces lo producido por Camisea en el 2025 -, los cuales siguen allí, dormidos. Más aún, el Minem apunta a poner en valor los 20,4 de TCF de recursos prospectivos identificados en la Cuenca Madre de Dios, lo cual representa “todo un reto”, manifestó Iris Cárdenas, viceministra de Hidrocarburos, en el Foro Gas Natural Perú 2026. En esa línea, el ministerio busca establecer un consenso con el Servicio de Áreas Naturales Protegidas (Sernanp) para poder realizar actividades exploratorias en áreas donde ya ha habido labores hidrocarburíferas, como la estructura del Candamo, circunscrita al parque nacional Bahuaja Sonene. “En el tema de las ANP, tenemos una propuesta para la modificación de dicha ley (Ley 26834) con el propósito de habilitar estas áreas donde ya ha habido intervención y se pueda desarrollar el gas natural”, expresó Cárdenas. Para apuntalar esta iniciativa, el Minem plantea transferir un porcentaje de lo producido en el Candamo al Sernanp, para que “pueda cuidar todas las áreas naturales protegidas”, particularmente, las expuestas a la tala y la minería ilegal. Mucho antes que el Candamo veremos, sin embargo, la puesta en marcha del lote 58 (Cusco) de la china CNPC, el cual alberga 3,56 TCF en recursos contingentes (3C). Se trata de un proyecto que debería entrar en producción hacia noviembre y que se añadiría al flujo proveniente de Camisea a través del gasoducto del mismo nombre. Y es que un escollo para la implementación de nueva infraestructura de transporte (Perú tiene menos tubos de hierro construidos que sus pares de la región) es la debilidad de la demanda interna, que desalienta la inversión en gasoductos. Así, ocurre que el 20% de la producción diaria del lote 88 (orientado al consumo interno) se reinyecta al subsuelo, según estadísticas de Pluspetrol. Y otro tanto ocurre en los lotes de hidrocarburos de Piura, cuyos operadores queman el gas natural que no pueden colocar en el mercado. Ello, a pesar del interesante potencial gasífero que alberga dicha región y que bien podría servir para atender la demanda de regiones vecinas como Lambayeque, La Libertad y Ancash, apunta Luis Fernández, socio director de Gas Energy Perú. “Lamentablemente, hay un problema por resolver en el Perú, que es la débil demanda de gas. Mientras esto no se resuelva, este recurso va a seguir satisfaciendo solamente a Lima y algunas ciudades de la costa, con el riesgo latente de que el ducto de TGP vuelva a fallar”, refiere Bianchi. Esa demanda existe, sin embargo, en el sur del Perú, y está constituida por las dos centrales térmicas de Ilo y Mollendo (nodo energético del sur), las cuales aguardan desde hace largos años el arribo del gas para empezar operar con dicho hidrocarburo (hoy lo hacen con diésel). A entender de Murillo, la mejor forma de plasmar esta esperanza es relanzando el SIT Gas (otro Gasoducto Surperuano), “proyecto viable, pero inmovilizado desde hace cinco años” que haría más seguro el sistema de ductos actual y masificaría el gas natural en el sur. Se trata, refiere, de una iniciativa necesaria por cuanto el COES acaba de alertar que los precios de la energía se incrementarán en adelante debido a que “dependeremos en mayor medida del diésel, el cual incrementa el costo de la electricidad en diez veces”. El SIT Gas no es, sin embargo, la única solución para llevar el gas de Camisea al sur. Pendiente de desarrollo también está el gasoducto costero o Extensión Sur, de TGP, proyecto que busca llegar también a las centrales de Ilo y Mollendo, además de a las industrias de Arequipa. Igualmente factible es, según Gas Energy, la construcción de un gasoducto entre Piura y Chiclayo, el cual tendría por ‘ancla’ las centrales térmicas de Eten, aprovechando, para ello, el potencial gasífero de los lotes de hidrocarburos del noroeste (aproximadamente 5,5 TCF). El desarrollo de este proyecto requiere, sin embargo, de un tipo de regulación diferente, que contemple una tarifa especial para el sector de generación eléctrica en el norte del país, similar al del nodo energético de Chilca. Solo, así, señala Fernández, las centrales de Eten podrán competir con sus pares de Lima y con el precio regulado del gas de Camisea.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/economia/gas-natural-mas-alla-de-camisea-y-el-ducto-de-tgp-que-alternativas-existen-para-reducir-la-dependencia-de-un-solo-gasoducto-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Esperan aprobación del Minsa sobre diseño de Hospital de Alta Complejidad e iniciar construcción</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>El proyecto del Hospital de Alta Complejidad de Piura sigue en marcha. A la fecha ya se culminó su diseño integral y quedó a la espera de la aprobación del Ministerio de Salud (Minsa) para pasar enseguida a la fase de construcción. El proyecto, que prevé una inversión de S/3,201’976,925, busca ampliar la atención especializada para más de tres millones de habitantes de Piura y otras regiones del norte del país. La ejecución estará a cargo de Sinohydro Corporation Limited, empresa contratista seleccionada para desarrollar la obra bajo el mecanismo de Gobierno a Gobierno con el Reino Unido. El contrato contempla el diseño, la construcción, la instalación de equipos médicos y la puesta en marcha del hospital.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/esperan-aprobacion-del-minsa-sobre-diseno-de-hospital-de-alta-complejidad-e-iniciar-construccion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cuidado con la automedicación en niños con dengue: podría agravar la enfermedad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>El incremento de casos de dengue en la región ha encendido las alertas en los hogares, sobre todo por el caso de los menores de edad, donde muchas veces los padres de familias automedican a sus pequeños sin considerar que podrían agravar la enfermedad. Ante esta situación, el pediatra del Hospital III José Cayetano Heredia de la Red Asistencial Piura de EsSalud, Ricardo Olea Zapata, exhortó a los padres de familia a no automedicar a los niños. Explicó que, tras la picadura del mosquito transmisor, los síntomas pueden aparecer entre 7 y 14 días después del contagio, por ello recomendó estar atentos a cualquier signo de alarma. “Lo más importante es mantener al niño en reposo, brindarle abundantes líquidos y sueros rehidratantes para evitar la deshidratación”, señaló el médico, quien agregó que cuando un menor presenta fiebre asociada al dengue, el único medicamento recomendado es el paracetamol, ya que otros fármacos pueden generar complicaciones y no están indicados para estos casos. ACUDIR AL MÉDICO Olea Zapata indicó que si la fiebre no disminuye, se debe administrar la dosis de paracetamol prescrita por el médico y complementar el manejo con baños de agua tibia durante periodos prolongados, que pueden llegar hasta una hora, con el fin de ayudar a controlar la temperatura corporal. Advirtió que los padres deben acudir de inmediato al establecimiento de salud más cercano si el niño presenta signos de alarma.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cuidado-con-la-automedicacion-en-ninos-con-dengue-podria-agravar-la-enfermedad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Más de 10 mil casos de dengue en Piura; centros de salud, jalados</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Aún no se inician las lluvias y el reporte de casos de dengue en la región es preocupante. Y es que hasta la semana epidemiológica 35, que finalizó el 5 setiembre, nuestra región registraba un acumulado de más de 10 mil casos en lo que va del año, posicionando a Piura como la región con más casos de dengue en el país, por encima de La Libertad, San Martín y Lambayeque. Lo más alarmante es que, de acuerdo al análisis realizado por la Red de Estudios para el Desarrollo (REDES) en el “Diagnóstico de Brechas de Infraestructura o Acceso a Servicios del Sector Salud 2028-2030”, hallaron que un 98% de establecimientos de salud del primer nivel de atención tiene capacidad instalada inadecuada. CIFRAS PREOCUPANTES Este porcentaje representa a los 440 establecimientos, de salud de un total de 449, que no cuentan con una infraestructura adecuada y de calidad para atender a sus pacientes. Según el informe, se trata principalmente de puestos, postas y centros de salud locales, que constituyen el primer punto de atención y los servicios más cercanos y accesibles para las distintas localidades de nuestra región. A ello se suma que 37 establecimientos del primer nivel de atención aún están pendientes de implementación. Germán Vega, economista de REDES, considera que en lo más importante es proteger la vida y salud de los pobladores, por lo que plantea tres prioridades: identificar las localidades más afectadas, fortalecer la prevención y reforzar el primer nivel de atención. “Desde una mirada económica, actuar a tiempo también permite evitar que los casos se agraven, reducir costos para las familias y aliviar la presión sobre el sistema de salud”, comentó el economista quien hizo énfasis en la prioridad que se le debe dar a Piura y Morropón, “donde ya se han registrado defunciones por dengue”. En la actualidad, la provincia de Piura es la que tiene más casos acumulados, es decir, es en donde más se está propagando esta enfermedad viral transmitida por la picadura de mosquitos infectados. Le sigue Morropón, Sullana, Ayabaca, Paita, Talara, Sechura y Huancabamba. Ante el incremento de casos Vega considera que se debe seguir fortaleciendo la capacidad de respuesta de los servicios de salud, especialmente para garantizar una atención oportuna y adecuada a los pacientes.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/mas-de-10-mil-casos-de-dengue-en-piura-centros-de-salud-jalados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>El Niño Costero podría generar lluvias de 100 mm por día durante el verano</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>El desarrollo de un El Niño Costero de magnitud extraordinaria podría elevar considerablemente la intensidad de las lluvias durante el verano 2026-2027. De acuerdo con Rinia Gabriel, vocera de la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno “El Niño” (ENFEN), las precipitaciones en la costa norte podrían alcanzar entre 80 y 100 milímetros por día bajo un escenario de calentamiento excepcional del mar. La estimación fue difundida por la Agencia Andina el 16 de septiembre de 2026 y se produce en un contexto en el que el ENFEN mantiene la alerta por El Niño Costero y contempla una posible magnitud extraordinaria durante los próximos meses. El escenario tiene especial relevancia para regiones como Tumbes, Piura y Lambayeque, donde las lluvias intensas pueden generar impactos en ciudades, carreteras, ríos y zonas agrícolas. El Niño Costero podría llevar las lluvias hasta 100 milímetros diarios Según explicó Rinia Gabriel, una precipitación de entre 80 y 100 milímetros representa entre 80 y 100 litros de agua por cada metro cuadrado. Se trata de valores que pueden superar ampliamente los registros habituales de la costa norte peruana. La especialista recordó que durante el El Niño Costero de 2017 se registraron precipitaciones cercanas a los 75 milímetros en Piura. Bajo las condiciones oceánicas previstas para el próximo verano, ese nivel podría ser superado. El antecedente más fuerte corresponde a los eventos de 1997-1998 . De acuerdo con la información manejada por el ENFEN, durante aquellos años los acumulados mensuales de verano en Piura llegaron a estimarse entre 1,000 y 1,500 milímetros. Estos antecedentes permiten dimensionar la importancia de las actuales proyecciones, aunque los especialistas advierten que la intensidad exacta de las precipitaciones dependerá de la evolución de las condiciones del océano y de la atmósfera. ¿Por qué un mar más caliente puede generar lluvias más intensas? El factor central del actual escenario es la temperatura superficial del mar. El El Niño Costero se desarrolla cuando las aguas frente a la costa peruana presentan un calentamiento anómalo y persistente. Para los próximos meses se espera que amplias zonas del litoral puedan registrar temperaturas de 26, 27 e incluso 28 °C. Un océano más cálido favorece una mayor disponibilidad de humedad en la atmósfera y puede proporcionar las condiciones necesarias para el desarrollo de lluvias más intensas. Sin embargo, Rinia Gabriel aclaró que no basta con que un punto determinado del océano alcance 26 o 27 °C. Para que el efecto sobre las precipitaciones sea mayor, las temperaturas elevadas deben mantenerse durante un periodo prolongado y abarcar una superficie suficientemente extensa. Actualmente ya se observan sectores frente al litoral peruano con temperaturas de 26 y 27 °C, aunque todavía se trata de áreas relativamente pequeñas. El escenario cambiaría si ese calentamiento se extendiera sobre una mayor superficie del mar frente al norte peruano. Las lluvias podrían aumentar de manera gradual El posible escenario extraordinario no significa que las lluvias extremas vayan a aparecer de manera inmediata. Según la explicación proporcionada por la vocera del ENFEN, las precipitaciones podrían incrementarse progresivamente conforme avance la primavera y se aproxime el verano. Incluso existe la posibilidad de que la temporada de lluvias se adelante y que desde noviembre comiencen a observarse mayores precipitaciones. Sin embargo, un incremento de las lluvias durante octubre o noviembre no necesariamente significa que desde esos meses se presenten episodios extremos. El mayor potencial para precipitaciones intensas se concentraría durante los meses de verano, especialmente cuando las condiciones oceánicas y atmosféricas alcancen una combinación favorable para la formación y persistencia de sistemas de lluvia. ¿El Niño Costero podría superar al evento de 1997-1998? La evolución actual presenta algunas características que recuerdan al El Niño de 1997-1998 . No obstante, la diferencia señalada por los especialistas está relacionada con las temperaturas proyectadas para el océano. Rinia Gabriel indicó que el actual evento presenta similitudes en su evolución con el registrado entre 1997 y 1998, pero las proyecciones apuntan a un escenario más cálido. Un océano con temperaturas excepcionalmente altas puede aportar mayor humedad a la atmósfera. Por ello, bajo determinadas condiciones, las lluvias podrían superar los niveles registrados en episodios anteriores, especialmente en la costa norte y central del país. La zona bajo vigilancia comprende principalmente el norte y centro del litoral peruano. Lima también forma parte del área donde podrían registrarse efectos asociados al incremento de las precipitaciones. Para Ica y regiones más al sur, el comportamiento de las lluvias todavía requiere una evaluación más detallada. ¿Qué significa que El Niño Costero sea extraordinario? La categoría extraordinario corresponde al nivel máximo de magnitud contemplado para el El Niño Costero . Su clasificación no depende directamente de la cantidad de lluvia registrada, sino principalmente de las anomalías de la temperatura superficial del mar en la región Niño 1+2. Según información difundida por el ENFEN, un escenario extraordinario está asociado con anomalías superiores a 3.5 °C durante un periodo prolongado. El análisis considera el comportamiento promedio de una zona amplia y no solamente registros aislados. Por esa razón, que un punto específico del mar presente una anomalía de 5, 6 o incluso 7 °C no significa por sí solo que el evento sea clasificado como extraordinario. Lo determinante es la persistencia y extensión del calentamiento. El más reciente reporte del ENFEN señala que entre septiembre de 2026 y enero de 2027 existe una alta probabilidad de que El Niño Costero alcance magnitud extraordinaria, mientras que para febrero y marzo se contempla una magnitud entre fuerte y extraordinaria. Lluvias de varias horas podrían repetirse Otro elemento importante es la posibilidad de que los episodios de lluvia tengan una duración considerable. Cuando existe un adecuado acoplamiento entre el océano y la atmósfera, el mar caliente puede continuar aportando humedad incluso después de una primera descarga. Esto puede favorecer un comportamiento caracterizado por periodos de lluvia, pausas y nuevas precipitaciones. La formación de nubes puede reactivarse mientras las condiciones cálidas y húmedas continúen presentes. En términos sencillos, una lluvia intensa no necesariamente terminaría después de una sola descarga. Si el océano continúa proporcionando humedad, podrían generarse nuevas etapas de precipitación durante el mismo episodio. ¿Qué regiones del Perú podrían recibir más lluvias? El impacto de El Niño Costero no sería uniforme en todo el territorio nacional. El calentamiento frente al litoral peruano favorece principalmente la ocurrencia de lluvias por encima de lo normal en la costa norte y central. Entre las regiones que concentran mayor atención se encuentran Tumbes, Piura y Lambayeque , aunque el escenario también comprende otros sectores de la costa central, incluida Lima. El Senamhi también ha señalado que durante los próximos meses la costa norte podría registrar precipitaciones superiores a lo normal, con posibles episodios de lluvia desde noviembre. Para el periodo septiembre-noviembre de 2026, además, se prevén temperaturas del aire muy superiores a los valores habituales en la costa peruana. El Niño también puede generar condiciones diferentes en la sierra sur Mientras el calentamiento frente a la costa puede favorecer lluvias por encima de lo normal en el norte y centro, las condiciones cálidas en el Pacífico Ecuatorial Central pueden tener un comportamiento distinto sobre otras zonas del país. Según la explicación proporcionada por el ENFEN, existe la posibilidad de que algunas zonas de la sierra sur presenten precipitaciones por debajo de lo habitual. Entre las regiones mencionadas figuran Puno, Cusco, Apurímac, Ayacucho y Arequipa, además de posibles efectos en Madre de Dios. De esta manera, el territorio peruano podría enfrentar simultáneamente escenarios diferenciados: mayor disponibilidad de lluvias en sectores de la costa norte y central y déficit de precipitaciones en determinadas áreas de la sierra sur. ¿Hasta cuándo podría durar El Niño Costero? El escenario previsto no se limita al inicio del verano. De acuerdo con el último reporte citado por el ENFEN, el El Niño Costero podría continuar hasta mediados del otoño de 2027, aproximadamente hasta abril, antes de iniciar una transición gradual hacia condiciones neutras. Para el verano, correspondiente al periodo diciembre de 2026-marzo de 2027, el comportamiento de las lluvias dependerá de cómo evolucionen las temperaturas del mar y el acoplamiento entre el océano y la atmósfera. El seguimiento de estos indicadores continuará a cargo del ENFEN y del Senamhi , cuyos comunicados y pronósticos permitirán actualizar el escenario conforme se acerquen los meses de mayor actividad lluviosa.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/el-nino-costero-podria-generar-lluvias-de-100-mm-por-dia-durante-el-verano/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ministro de Educación anuncia plan para continuidad de clases ante el fenómeno El Niño</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>El ministro de Educación, José Antonio Chang, anunció ante la Comisión de Educación, Cultura y Deporte de la Cámara de Diputados un conjunto de medidas destinadas a reducir el impacto del Fenómeno El Niño en la infraestructura educativa y garantizar la continuidad de las clases en las zonas que podrían resultar afectadas por el evento climático. Durante su presentación, el titular del Ministerio de Educación (MINEDU) explicó que el plan contempla acciones preventivas y medidas que serán activadas en caso de que las condiciones climáticas provoquen daños en los colegios o dificulten el traslado de los estudiantes. ¿Qué regiones serán priorizadas para proteger las clases? Como parte de la primera etapa preventiva, el sector Educación priorizará la atención de instituciones educativas ubicadas en Lambayeque, Tumbes, Piura, La Libertad y Lima Provincias , regiones consideradas dentro de las zonas que podrían enfrentar mayores efectos asociados al Fenómeno El Niño. Según explicó Chang, la intervención alcanzará a miles de locales educativos y aulas, con el objetivo de reducir los riesgos para estudiantes y docentes y evitar que eventuales daños en la infraestructura terminen provocando una interrupción prolongada del servicio educativo. “Vamos a atender 7,998 locales educativos, 49,020 aulas en donde estudian un millón 237 mil estudiantes”, informó el ministro durante su intervención. Para estas acciones, el sector solicitó un crédito suplementario de S/ 304 millones . El plan contempla aulas prefabricadas ante posibles daños Una de las medidas previstas por el MINEDU consiste en disponer de 1,500 aulas prefabricadas modulares que podrían ser instaladas en las zonas donde los colegios sufran daños que impidan el desarrollo normal de las actividades escolares. La distribución de estos módulos dependerá de las necesidades que se presenten en las distintas regiones del país. El objetivo es contar con espacios alternativos que permitan mantener el servicio educativo mientras se realizan reparaciones o se recupera la infraestructura afectada. La medida busca evitar que los problemas estructurales de un colegio se conviertan automáticamente en una suspensión indefinida de las clases presenciales , especialmente en comunidades donde existen pocas alternativas para continuar con la educación. “Aula TV” busca mantener las clases durante las interrupciones El ministro también puso énfasis en un aspecto distinto a la infraestructura: la continuidad del aprendizaje. Para ello, el MINEDU trabaja en la propuesta denominada “Aula TV” , desarrollada mediante una alianza con el Instituto Nacional de Radio y Televisión del Perú (IRTP). La iniciativa está dirigida a los estudiantes que temporalmente no puedan acudir a sus colegios debido a las condiciones generadas por el Fenómeno El Niño. La televisión sería utilizada como una herramienta para transmitir contenidos educativos mientras se restablece la atención presencial. Chang señaló que la experiencia de la pandemia evidenció la necesidad de contar con alternativas previamente diseñadas para garantizar el acceso a la educación cuando los estudiantes no pueden acudir físicamente a las instituciones educativas. Cuatro escenarios para garantizar la continuidad educativa El Ministerio de Educación estableció cuatro escenarios que permitirían mantener el servicio educativo dependiendo de la magnitud de la emergencia y de las condiciones de cada localidad. 1. Mantener las escuelas operativas Cuando las condiciones permitan utilizar los colegios con seguridad, las clases continuarán de manera presencial, aunque podrían realizarse ajustes en los horarios para responder a las circunstancias provocadas por las lluvias u otros efectos del evento climático. 2. Utilizar la televisión ante interrupciones temporales Si los estudiantes no pueden asistir durante determinados periodos, se plantea implementar una franja diaria de clases por televisión . Esta alternativa permitiría mantener el contacto con los contenidos educativos mientras se normaliza la asistencia a los colegios. 3. Reubicar a los estudiantes en otros locales Cuando una institución educativa quede temporalmente inhabilitada, los estudiantes podrían ser trasladados a locales comunales o parroquias que reúnan las condiciones necesarias para desarrollar las actividades educativas. 4. Utilizar radio, televisión y material impreso Para las comunidades que queden aisladas debido a la emergencia, el plan contempla recurrir a diferentes medios de comunicación. En estos casos, la educación podría apoyarse en radio, televisión y materiales impresos , de acuerdo con las condiciones de cada localidad. MINEDU evalúa retomar el mantenimiento preventivo de colegios Otra de las medidas anunciadas está relacionada con el mantenimiento de las instituciones educativas. El sector evalúa retomar un esquema de mantenimiento preventivo que permita atender reparaciones necesarias antes de que las condiciones climáticas puedan agravarlas. Este tipo de intervención busca responder a problemas inmediatos de los colegios y reducir los riesgos asociados al deterioro de techos, aulas y otros espacios utilizados diariamente por estudiantes y docentes. De acuerdo con el Ministerio de Educación, las acciones preventivas serán importantes para determinar qué instituciones pueden continuar funcionando y cuáles necesitarían una intervención mayor ante una eventual emergencia. Congresistas preguntan por infraestructura educativa y clases virtuales Durante la sesión, presidida por el diputado Juan Castrejón, los integrantes de la Comisión de Educación, Cultura y Deporte solicitaron mayores detalles sobre las medidas previstas para enfrentar los efectos del Fenómeno El Niño y sobre el estado de los colegios en diferentes regiones. La diputada Rossana Alayza pidió conocer los criterios que empleará el sector para determinar qué instituciones educativas serán refaccionadas y cuáles necesitarán una nueva infraestructura. También planteó la necesidad de evitar que una emergencia climática derive en un retorno generalizado a las clases virtuales . Por su parte, el diputado José Yataco señaló que en Ica todavía existen solicitudes relacionadas con la reconstrucción de colegios afectados por el terremoto de 2007. El legislador consultó qué medidas se ejecutarán antes de la llegada del Fenómeno El Niño y si podrían utilizarse facultades legislativas para acelerar las intervenciones.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/ministro-de-educacion-anuncia-plan-para-continuidad-de-clases-ante-el-fenomeno-el-nino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Piura soportará temperaturas superiores a 36 °C por El Niño durante la primavera</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>La llegada de la primavera traerá un incremento de las temperaturas en Piura y podría marcar uno de los primeros impactos asociados al desarrollo de El Niño : las olas de calor. De acuerdo con el especialista en meteorología del Senamhi, Héctor Yauri, las condiciones cálidas del océano, sumadas al cambio estacional, favorecerán episodios de temperaturas elevadas, principalmente entre noviembre y diciembre. El escenario climático previsto para los próximos meses mantiene la atención sobre la costa norte del país. Según información difundida por el Senamhi y la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno El Niño (ENFEN), las condiciones cálidas persistirán durante la temporada 2026-2027. Para la región Niño 1+2, que comprende el mar frente a la costa peruana, se prevé que el evento continúe hasta el próximo verano. El Niño favorecerá temperaturas más altas en Piura Yauri explicó que el calentamiento del océano frente a la costa peruana constituye uno de los factores que pueden contribuir al aumento de las temperaturas del aire. El especialista señaló que el comportamiento observado presenta características que requieren seguimiento durante la primavera. “Actualmente ya hemos superado los 3,5 grados en promedio en todo el mar frente a nuestra costa. Eso corresponde a una categoría extraordinaria, comparable con el nivel que tuvimos en 1997-1998”, señaló Yauri. De acuerdo con el especialista, la mayor intensidad del calentamiento podría presentarse durante noviembre, cuando las anomalías de la temperatura del mar alcanzarían alrededor de 4 °C en promedio. Este escenario tendría repercusiones sobre las condiciones meteorológicas de la costa norte. El Senamhi también ha advertido que las temperaturas del aire en la costa peruana se mantendrían por encima de sus valores climatológicos debido a la persistencia del calentamiento del mar. En su actualización de junio, el organismo señaló que el Niño Costero podría prolongarse hasta el verano de 2027. Chulucanas y Malacasí ya registraron temperaturas elevadas Las altas temperaturas ya comenzaron a manifestarse en algunas localidades de la región Piura. Según los datos mencionados por Yauri, Chulucanas registró 38,8 °C, mientras que Malacasí alcanzó 37,2 °C. En la ciudad de Piura, entretanto, todavía no se habían superado los 35 °C al momento de las declaraciones. El comportamiento no resulta extraño para una región acostumbrada a registrar temperaturas elevadas, pero adquiere especial importancia cuando se combina con un océano más cálido y una mayor humedad ambiental. “El primer impacto que vamos a tener de El Niño, antes de las lluvias para la costa norte, van a ser las olas de calor. Ya se han registrado, pero no han sido percibidas tanto porque todavía estábamos en la etapa invernal”, explicó el especialista. Los registros históricos del Senamhi muestran que Piura presenta condiciones naturalmente cálidas. En marzo de 2026, por ejemplo, la estación La Esperanza registró una temperatura máxima promedio de 32,4 °C, mientras que Bernal alcanzó 34,6 °C, ambos valores por encima de sus respectivas climatologías. Noviembre sería uno de los meses más críticos para el calor Actualmente, las temperaturas promedio en Piura se ubican alrededor de los 32 °C y 33 °C, con máximas que pueden alcanzar entre 35 °C y 36 °C. Sin embargo, la sensación térmica puede ser mayor cuando se combina el calor con elevados niveles de humedad. Con el avance de la primavera, esta situación podría intensificarse. Yauri sostuvo que durante noviembre podrían presentarse temperaturas superiores a los 36 °C durante varios días consecutivos, una situación que puede configurar condiciones de ola de calor. “En noviembre puede ser importante. Las temperaturas pueden llegar sostenidamente a más de 36 grados por cinco días y eso ya puede generar una ola de calor. Con el aumento de la humedad, este efecto puede ser mucho mayor”, sostuvo. Para febrero y marzo, meses que suelen registrar algunos de los valores más elevados del año en la región, existe la posibilidad de que determinados episodios se acerquen a los 38 °C o 39 °C. No obstante, la evolución dependerá de las condiciones atmosféricas y oceánicas que se presenten durante los siguientes meses. ¿Cuándo llegarían las lluvias a Piura? El aumento de las temperaturas no significa necesariamente que las lluvias comiencen de inmediato. Según el escenario explicado por el especialista, durante septiembre todavía no se esperaba un inicio generalizado de las precipitaciones en la costa norte. De acuerdo con el escenario climático manejado por las autoridades meteorológicas, las primeras precipitaciones asociadas al periodo lluvioso podrían presentarse con intensidad moderada en Tumbes durante noviembre y posteriormente avanzar hacia Piura en diciembre. El Senamhi ha señalado que la temporada de lluvias 2026-2027 debe ser seguida mediante los pronósticos y avisos meteorológicos vigentes, debido a la continuidad de El Niño Costero y al desarrollo de condiciones de El Niño en el Pacífico ecuatorial central. El impacto de El Niño no se limita al río Piura Yauri remarcó que los posibles efectos de El Niño en Piura no deben analizarse únicamente desde el riesgo de incremento del caudal del río Piura. Las precipitaciones pueden afectar distintos sectores de la región, especialmente aquellas zonas ubicadas en la sierra y en las partes altas de las cuencas. Asimismo, las condiciones cálidas y húmedas pueden favorecer otros fenómenos meteorológicos, entre ellos las tormentas eléctricas. Por ello, el seguimiento de los pronósticos resulta relevante tanto para las autoridades como para la población. La experiencia de anteriores eventos permite dimensionar la importancia de este escenario. Durante El Niño de 1997-1998 , entre enero y abril, Piura acumuló aproximadamente 2,5 metros de lluvia, mientras que en Chulucanas y otros sectores del Alto Piura los acumulados llegaron a entre 3 y 4 metros. En contraste, los acumulados registrados durante los eventos de 2017 y 2023 fueron considerablemente menores, según la comparación realizada por el especialista. ¿El aumento de temperaturas puede favorecer el dengue? Otro de los aspectos que genera preocupación está relacionado con la salud pública. Las temperaturas elevadas, combinadas posteriormente con lluvias y mayor humedad, pueden crear condiciones favorables para la reproducción del mosquito transmisor del dengue. Yauri explicó que normalmente los casos disminuyen durante los meses de invierno y tienden a incrementarse después de la temporada de lluvias. Sin embargo, durante este año se habría observado una situación distinta, debido a la presencia del mosquito transmisor incluso durante meses en los que habitualmente su actividad disminuye. “Si las temperaturas se mantienen altas y empieza la lluvia en octubre o noviembre, eso podría ser un gatillador para que el dengue empiece con una epidemia. Es inusual porque normalmente en los meses antes de la primavera no ocurren muchos casos”, advirtió. ¿Qué se debe vigilar durante los próximos meses? El comportamiento de las temperaturas, la humedad, las lluvias y las condiciones del océano serán algunos de los principales indicadores para conocer cómo evolucionará el escenario climático en Piura. Según el Senamhi, la población debe mantenerse informada mediante los pronósticos oficiales y los avisos meteorológicos, mientras que las autoridades deben considerar los escenarios de riesgo para adoptar medidas de preparación ante los posibles impactos de la temporada de lluvias. Para consultar información actualizada, los reportes oficiales pueden revisarse en el Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) y en la Comisión Multisectorial ENFEN , organismos encargados del monitoreo de las condiciones oceánicas y atmosféricas relacionadas con El Niño.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-soportara-temperaturas-superiores-a-36-c-por-el-nino-durante-la-primavera/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Descolmatación no reduce riesgo de una inundación en Piura, cuestiona ingeniero hidráulico</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Andrés Farfán, ingeniero hidráulico, no solo cuestionó la lentitud con la que avanzan los trabajos de descolmatación en el río Piura sino que los más de 600 mil metros cúbicos que se proyectan retirar de sedimentación no reduce el riesgo de una posible inundación. En esa línea cuestionó que el Ejecutivo se proyecte recuperar una capacidad de caja hidráulica de 3,900 metros cúbicos por segundo (m3/s). “Ellos están hablando de 3,900. El gran error es que por aquí pasan 4,000 m3 cuando el cauce está totalmente descolmatado. Con esta mitigación, ¿qué pasa? Entre 1,900 y 2,000. Yo le calculo máximo puede ser 2,200. Estamos condenados a inundarnos si las labores continúan en las condiciones actuales”, afirmó. Finalmente advirtió que entre la represa Los Ejidos y el puente Bolognesi se ha previsto realizar trabajos de descolmatación en una distancia de 4.8 kilómetros; sin embargo, dijo que como van solo llegarían al 50%.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/descolmatacion-no-reduce-riesgo-de-una-inundacion-en-piura-cuestiona-ingeniero-hidraulico/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vecinos de Consuelo de Velasco padecen por agua: exigen solución a EPS Grau</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Cansados de estar fungiendo de “topos” o acudir a los domicilios de vecinos o familiares para abastecerse de agua potable, ayer un grupo de vecinos del asentamiento Consuelo de Velasco realizaron una protesta en su jurisdicción para exigir a la EPS Grau una solución inmediata a la falta de agua en el lugar. Señalan que el agua no les llega a sus caños; en otros casos llega, pero solo por media hora; y en otros casos tienen que hacer huecos o comprar bidones de agua dada la falta de agua. Refieren que, en los últimos 15 días, la situación ha sido más crítica, por ello exigen la intervención de las autoridades. Además, denuncian que los recibos siguen llegando y encima les cobran reposición del servicio, pese a no contar con el mismo.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/vecinos-de-consuelo-de-velasco-padecen-por-agua-exigen-solucion-a-eps-grau/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Con protesta, piuranos exigen a Keiko cumplir con transferencias</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>El 3 de setiembre pasado, la presidenta de la República, Keiko Fujimori, se comprometió a “destrabar” cinco proyectos paralizados en Piura, debido al incumplimiento de una transferencia de 41 millones de soles por parte del Ministerio de Vivienda, y hasta la fecha no se cumple con el ofrecimiento. Ello ha conllevado a que aún no se puedan reactivar los proyectos de las avenidas avenida B-D, Los Educadores, Túpac Amaru, Los Almendros y Urb. Piura. Ante esta situación, ayer dirigentes de los sectores afectados realizaron una protesta en los exteriores de las oficinas del Ministerio de Vivienda, en la Urb. Los Cocos en Piura, para exigir a la mandataria cumpla con su palabra y las obras puedan ser culminadas antes del inicio de las lluvias. Milagros Orihuela, secretaria general del asentamiento 4 de Octubre, indicó que de persistir la demora convocarán a toda la población a una masiva marcha de protesta en las calles.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/con-protesta-piuranos-exigen-a-keiko-cumplir-con-transferencias/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Piura será un horno por El Niño: soportará 42°C de sensación de calor</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Los piuranos deberán tomar sus precauciones para las altas temperaturas que se avecinan. Y es que el especialista en Vigilancia Meteorológica del Senamhi, Nelson Quispe Gutiérrez, informó que la temperatura en Piura podría llegar a los 40 grados Celsius (104 grados Fahrenheit) de temperatura real. Explicó que el incremento de la temperatura es propiciado por el Fenómeno El Niño (FEN), el cual se dará con mayor intensidad en la costa norte. “Y no solamente eso, sino que, aunada a la humedad que va a haber, la sensación de calor que uno podrá percibir en esta zona sería alrededor de los 42 grados Celsius”, refirió Quispe en declaraciones a Andina. SERÁ UN ‘HORNO’ Quispe proyectó que las temperaturas seguirán en aumento hacia finales de año y comienzos del 2027, con los registros más altos esperados entre los meses de febrero y marzo, según indicó a la agencia estatal. Por ello consideró que los niños y adultos mayores deben merecer especial atención en aras de evitar consecuencias negativas en su salud durante los próximos meses. “Esto definitivamente creará un shock”, advirtió el especialista del Senamhi, quien precisó que dicho efecto puede manifestarse con solo caminar por las calles en medio del calor, con las consecuencias perjudiciales que ello implica para la salud de la población. EXTRAORDINARIA Mientras tanto, el Enfen a través de Comunicado Oficial N.° 16-2026, emitido el 14 de setiembre, establece que El Niño Costero, correspondiente a la región Niño 1+2, presenta la mayor probabilidad de alcanzar una magnitud extraordinaria entre setiembre de 2026 y enero de 2027. Para febrero y marzo, según señalan, sería el escenario más probable y se ubica entre una magnitud fuerte y extraordinaria. LLUVIAS FUERTES El pronóstico del Enfen ubica a la costa norte como una de las zonas con mayor probabilidad de precipitaciones superiores a lo normal. Desde noviembre podrían registrarse episodios de lluvias de moderada a fuerte intensidad, donde incluso podría superar los promedios históricos. CERCA DE 9 MIL CASOS Con el anuncio se lluvias se teme el incremento de casos de dengue. A la fecha, se registran en Piura un total de 8,958 casos de dengue y 6 defunciones en lo que va del año, según el reporte de la Semana Epidemiológica 33. Por ello, la Defensoría del Pueblo demandó con carácter de urgencia al gobernador Luis Neyra priorizar acciones urgentes contra el dengue.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-sera-un-horno-por-el-nino-soportara-42c-de-sensacion-de-calor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bajo Piura en riesgo: reportan 14 puntos críticos sin obras</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Víctor Chunga, del Frente de reconstrucción de los pueblos afectados del Bajo Piura por el Niño Costero, lamentó que, según información del Ministerio de Defensa, solo se esté considerando atender ocho puntos críticos en Piura, cuando solo el Bajo Piura tiene 14 puntos críticos por atender. Explicó que esa situación pone en riesgo al Bajo Piura dado que no cuentan con obras de prevención frente al riesgo de desborde e inundación en el marco del anuncio de un Fenómeno El Niño de magnitud “extraordinaria”. Entre los puntos críticos desprotegidos estarían Las Dos Ánimas, Chato Chico, La Joya, entre otros. Asimismo, lamentó que a la fecha solo sigan trabajando siete máquinas, lo cual considera insuficiente.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/bajo-piura-en-riesgo-reportan-14-puntos-criticos-sin-obras/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Gestión</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B58" s="2" t="n">
         <v>46281</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Petroperú dejará de operar el Lote Z-69: Perupetro busca nuevo inversionista</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Perupetro puso en marcha el proceso para seleccionar al nuevo operador del Lote Z-69, ubicado frente a las costas de Talara, Paita y Sechura, en Piura. El contrato tendrá una vigencia de 30 años y busca asegurar la continuidad de las operaciones petroleras, además de incorporar nuevas inversiones para elevar la producción de hidrocarburos. El cambio de operador se producirá tras el vencimiento del actual contrato de licencia, que está a cargo de la empresa pública Petroperú. Según se informa, este vence el 15 de mayo de 2027 o en la fecha efectiva de un nuevo contrato, “lo que ocurra primero”. “A diciembre de 2025, el Lote Z-69 reporta una producción fiscalizada promedio de 3,369 barriles diarios de petróleo (BOPD) y 8.59 millones de pies cúbicos de gas natural (MPCD). Sin embargo, dicho lote podría incrementar significativamente su producción con la incorporación de nuevas inversiones. El Lote Z-69 tiene una extensión de 127,056.1 hectáreas”, se precisa en el documento oficial. La convocatoria plantea que el nuevo operador no solo continúe con las actividades existentes, sino que asuma compromisos de inversión para el reconocimiento y la perforación de pozos de desarrollo y exploratorios. La propuesta que contemple el mejor programa de trabajo será la ganadora del proceso. “De acuerdo con el cronograma, las empresas podrán presentar sus cartas de interés hasta el 11 de diciembre de 2026. Posteriormente, Perupetro remitirá las cartas de admisión hasta el 18 de diciembre, mientras que la entrega de documentos para la etapa de calificación vencerá el 30 de diciembre de 2026″, se puede leer. “Solo las empresas que obtengan la calificación correspondiente estarán habilitadas para presentar ofertas técnicas. La presentación de propuestas correspondientes a los Paquetes N° 1 y N° 2, así como la apertura del Paquete N° 1, se realizará en acto público el 3 de febrero de 2027. Asimismo, la apertura del Paquete N° 2, la evaluación de las ofertas y el otorgamiento de la buena pro se llevarán a cabo el 8 de febrero de 2027, también en acto público”, se acota. Las bases del proceso contemplan la participación de Petroperú con hasta un 25% de participación en el contrato de licencia, sujeto a la obtención de una calificación favorable y a la suscripción de un compromiso de asociación conjunta con el postor ganador de la buena pro. Además, establecen la venta de activos de propiedad de Petroperú valorizados en US$ 15.1 millones, bajo la modalidad “como están y donde están”, con pago en cinco cuotas anuales. Asimismo, siete activos de propiedad de Petroperú permanecerán bajo su titularidad y estarán sujetos a un esquema de uso compartido con el futuro operador. A ellos se suma un activo de propiedad de Perupetro que también será administrado bajo este régimen.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>https://gestion.pe/economia/petroperu-dejara-de-operar-el-lote-z-69-perupetro-busca-nuevo-inversionista-para-los-proximos-30-anos-noticia/</t>
         </is>
